--- a/resources/data-imports/Core Imports/class-specials.xlsx
+++ b/resources/data-imports/Core Imports/class-specials.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fanatical Heretical Magic</t>
   </si>
   <si>
-    <t xml:space="preserve">Gives you 5% towards your base damage stat. As you level this specialty over time you can raise this % to 500% towards your damage stat, therefore doing more damage.</t>
+    <t xml:space="preserve">Twist forbidden doctrine through Fanatical Heretical Magic and let the heresy follow your hand. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2.5% damage stat per level, reaching 250% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">any</t>
@@ -94,37 +94,37 @@
     <t xml:space="preserve">Ancestral Witchcraft</t>
   </si>
   <si>
-    <t xml:space="preserve">Using the magics of your ancestors, you are able to do 2% more damage. leveling this specialty, over time you will eventually do 200% extra damage with this equipped.</t>
+    <t xml:space="preserve">Twist forbidden doctrine through Ancestral Witchcraft and let the heresy follow your hand. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% weapon and ring damage per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Bones of the craft</t>
   </si>
   <si>
-    <t xml:space="preserve">Call upon the bones of your craft to raise your armour class by 1%. Level this specialty and over time you will have 100% more AC.</t>
+    <t xml:space="preserve">Twist forbidden doctrine through Bones of the craft and let the heresy follow your hand. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% armour class per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Spellcraft</t>
   </si>
   <si>
-    <t xml:space="preserve">Cast your spells with more damage! As you use any cast attack such as, Cast, Attack and Cast or Cast and Attack and your spell damage hits, it will do 5% more damage. Level this specialty to then do 500% more damage!</t>
+    <t xml:space="preserve">Cast your spells with more damage! The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2.5% spell damage per level, reaching 250% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Life of the Magic Circle</t>
   </si>
   <si>
-    <t xml:space="preserve">Draw upon the magic of the circles you create to do your secret rituals to gain 1.5% towards your health. level this specialty to get 150% extra health!</t>
+    <t xml:space="preserve">Twist forbidden doctrine through Life of the Magic Circle and let the heresy follow your hand! The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% health per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Heretical Rage</t>
   </si>
   <si>
-    <t xml:space="preserve">Conjure the power of your magics to gain 2.5% more towards your damage stat. level this specialty to gain 250% more towards your damage stat.</t>
+    <t xml:space="preserve">Twist forbidden doctrine through Heretical Rage and let the heresy follow your hand. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2.5% damage stat per level, reaching 250% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Heretics Fire</t>
   </si>
   <si>
-    <t xml:space="preserve">Call upon the fire of your own soul to do 5000 damage with 5% of your damage stat added to the damage. Over time the specialty will add 50, for a maximum of 5000 to the damage as you level the specialty.</t>
+    <t xml:space="preserve">Twist forbidden doctrine through Heretics Fire and let the heresy follow your hand. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when casting, gains 50 damage per level, and reaches 10,000 damage at level 100, adding 5% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">cast</t>
@@ -133,19 +133,19 @@
     <t xml:space="preserve">Star Crushing Death</t>
   </si>
   <si>
-    <t xml:space="preserve">Using the power of the cosmos, call upon a star to do crush the enemy by doing 10,000 damage with 10% of your damage stat added on top. Over time, as you level this specialty, it will do an extra 100 damage for a maximum of 10,000 damage.</t>
+    <t xml:space="preserve">Twist forbidden doctrine through Star Crushing Death and let the heresy follow your hand. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when casting, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 10% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">Clock of End Times</t>
   </si>
   <si>
-    <t xml:space="preserve">Conjure up a clock that counts down to the end times. Does 50,000 damage with 25% of your damage stat added on top. As you level this specialty, over time it will do 500 extra damage for a maximum amount of 50,000</t>
+    <t xml:space="preserve">Conjure up a clock that counts down to the end times. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when casting, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 25% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">Shield Bash</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash the enemy after you take a defensive stand! will do 1000 damage to the enemy, growing in power over time to 10,000 damage. Also increases Armour Class by 1.5%, growing overtime to raise your AC to 150%. Will use 15% of your Strength for damage at level 100. [Must use DEFEND for the damage to fire.]</t>
+    <t xml:space="preserve">Bash the enemy after you take a defensive stand! The lesson can still be carried into another class when equipped. As you level this specialty, it deals 1,000 specialty damage when defending, gains 90 damage per level, and reaches 10,000 damage at level 100, adding 15% of your damage stat; it also adds 1.5% armour class per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">defend</t>
@@ -154,37 +154,37 @@
     <t xml:space="preserve">Fight for courage</t>
   </si>
   <si>
-    <t xml:space="preserve">Will increase your base damage modifier by 1% growing over time to 100% extra damage. This will also increase your base damage stat by 1.5%, growing over time to 150%.</t>
+    <t xml:space="preserve">Temper battlefield discipline into Fight for courage and carry that training into every fight. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% weapon and ring damage per level, reaching 100% at level 100; it also adds 1.5% damage stat per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Soldiers Stance</t>
   </si>
   <si>
-    <t xml:space="preserve">Will increase your base AC by 3% growing to a total of 300% increase in Armour over time.</t>
+    <t xml:space="preserve">Temper battlefield discipline into Soldiers Stance and carry that training into every fight. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 3% armour class per level, reaching 300% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Earth and Hearbs</t>
   </si>
   <si>
-    <t xml:space="preserve">Even a fighter need to learn the ways to heal them selves. Will increase your healing modifier for healing spells by 1% growing to 100% over time. Only while using Healing Spells and using Cast and Attack or Attack and Cast or Cast.</t>
+    <t xml:space="preserve">Even a fighter need to learn the ways to heal them selves. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% healing per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Spell Blade</t>
   </si>
   <si>
-    <t xml:space="preserve">Learn the art of magic, will give you a 1% boost to spell damage and grows to 100% over time. Only while using Damaging Spells and using Cast and Attack or Attack and Cast or Cast.</t>
+    <t xml:space="preserve">Temper battlefield discipline into Spell Blade and carry that training into every fight. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% spell damage per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Fighters Courage</t>
   </si>
   <si>
-    <t xml:space="preserve">Durability is the life line of a good soldier. Live longer, fight harder! Gives 2% to health will grow to 200% over time</t>
+    <t xml:space="preserve">Durability is the life line of a good soldier. Live longer, fight harder! The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% health per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Soldiers Slash</t>
   </si>
   <si>
-    <t xml:space="preserve">Slash at the foes for 1,000 damage which will use 15% of your base damage stat and grows by 100 per level of this specialty to a max of an total of 110,000 damage at level 100. This attack only triggers only when you use ATTACK.</t>
+    <t xml:space="preserve">Temper battlefield discipline into Soldiers Slash and carry that training into every fight. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when using an attack, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 15% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">attack</t>
@@ -193,13 +193,13 @@
     <t xml:space="preserve">Deep Cut</t>
   </si>
   <si>
-    <t xml:space="preserve">Will do 25,000 damage and grow by 250 extra damage over time doing a total of 50,000 damage plus 20% of your damage stat at level 100. This attack only triggers when you use ATTACK.</t>
+    <t xml:space="preserve">Temper battlefield discipline into Deep Cut and carry that training into every fight. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 25,000 specialty damage when using an attack, gains 250 damage per level, and reaches 50,000 damage at level 100, adding 20% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">Magical Swing</t>
   </si>
   <si>
-    <t xml:space="preserve">Your weapons will glow with magic! Does 50,000 damage growing by 500 per level for a total of 100,000 with an additional 25% of your weapon damage at level 100. This special will also increase your Spell damage by 150% (1.5% per level) at level 100. The damage of this special only triggers when you use ATTACK AND CAST</t>
+    <t xml:space="preserve">Your weapons will glow with magic! The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when attacking and casting, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 25% of your damage stat; it also adds 1.5% spell damage per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">attack_and_cast</t>
@@ -208,91 +208,91 @@
     <t xml:space="preserve">Health Craving</t>
   </si>
   <si>
-    <t xml:space="preserve">Your health will raise by 5% to a maximum of 500% over time.</t>
+    <t xml:space="preserve">Draw on blood, hunger, and night through Health Craving. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 5% health per level, reaching 500% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Vampiric Attack</t>
   </si>
   <si>
-    <t xml:space="preserve">Increase your damage stat by 0.02% for a total of 200% over time.</t>
+    <t xml:space="preserve">Draw on blood, hunger, and night through Vampiric Attack. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Spell Weaving Vampire</t>
   </si>
   <si>
-    <t xml:space="preserve">Increases the damage of your spells by 1.5% to 150% overtime. Also grow your health and damage by 250% at level 100.</t>
+    <t xml:space="preserve">Draw on blood, hunger, and night through Spell Weaving Vampire. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 1.5% spell damage per level, reaching 150% at level 100; and it also adds 2.5% health per level, reaching 250% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Clerical Vampire</t>
   </si>
   <si>
-    <t xml:space="preserve">Increase your healing spells ability to heal by 1.5% over time increasing it to 150% extra healing. Increase health by 200% as well as your damage stat by 150%</t>
+    <t xml:space="preserve">Draw on blood, hunger, and night through Clerical Vampire. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% healing per level, reaching 150% at level 100; it also adds 2% health per level, reaching 200% at level 100; and it also adds 1.5% damage stat per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Honed Blood Lust</t>
   </si>
   <si>
-    <t xml:space="preserve">Hone your blood lust to do more damage over time raising your base damage by 2% for a total of 200% at level 100 as well as growing your damage stat by 1.5% over time to a total of 150%</t>
+    <t xml:space="preserve">Hone your blood lust to do more damage. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 1.5% damage stat per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Armour of the night</t>
   </si>
   <si>
-    <t xml:space="preserve">Increase your Armour defense by 1.5% to a maximum of 150% as well as your health by an additional 250% at level 100.</t>
+    <t xml:space="preserve">Draw on blood, hunger, and night through Armour of the night. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% armour class per level, reaching 150% at level 100; it also adds 2.5% health per level, reaching 250% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Raging Hatred</t>
   </si>
   <si>
-    <t xml:space="preserve">Rages out at the enemy doing 5,000 Damage growing by 50 to a max of 10,000 damage using 20% of your damage stat. [Must use ATTACK for the damage to fire.]</t>
+    <t xml:space="preserve">[Must use ATTACK for the damage to fire.]. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when using an attack, gains 50 damage per level, and reaches 10,000 damage at level 100, adding 20% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Blood Drain</t>
   </si>
   <si>
-    <t xml:space="preserve">Take a defensive stance doing 15,000 damage growing by 300 over time for an additional 30,000 damage as well as 25% of your damage stat. Your health will also grow by 2% to a maximum of an extra 200% and finally your Armour Class will grow by 2.5% for a total of 250% at level 100. [Must use DEFEND for the damage to fire.]</t>
+    <t xml:space="preserve">Draw on blood, hunger, and night through Defensive Blood Drain. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 15,000 specialty damage when defending, gains 300 damage per level, and reaches 45,000 damage at level 100, adding 25% of your damage stat; it also adds 2.5% armour class per level, reaching 250% at level 100; and it also adds 2% health per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Vampires Shield</t>
   </si>
   <si>
-    <t xml:space="preserve">Raise your defense by 5% over time to 500% extra defense while doing 50,000 damage that grows by 500 over time to do an additional 50,000 damage plus 30% of your damage stat on top. [Must use DEFEND for the damage to fire.]</t>
+    <t xml:space="preserve">Draw on blood, hunger, and night through Vampires Shield. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when defending, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 25% of your damage stat; it also adds 5% armour class per level, reaching 500% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Natures Wrath</t>
   </si>
   <si>
-    <t xml:space="preserve">As you level this special over time you will do 150% more damage and 150% more healing</t>
+    <t xml:space="preserve">As you level this special. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% weapon and ring damage per level, reaching 150% at level 100; it also adds 1.5% health per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Earth Quake</t>
   </si>
   <si>
-    <t xml:space="preserve">Conjure the earth and do 10,000 damage increasing by 100 for an additional 10,000 damage over time using 15% of your damage stat. this special will also increase your armor class by 30% at level 100.</t>
+    <t xml:space="preserve">Let the wilds guide Earth Quake, even when you walk another road. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when using an attack, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 15% of your damage stat; it also adds 0.3% armour class per level, reaching 30% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Natures Insight</t>
   </si>
   <si>
-    <t xml:space="preserve">Gather insight into the way nature works, in the process you will get: 200% Base Damage, 100% base healing and 200% Damage Stat Increase at level 100 of this specialty.</t>
+    <t xml:space="preserve">Let the wilds guide Natures Insight, even when you walk another road. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 1% healing per level, reaching 100% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Healing Rivers</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain an additional 150% health and healing when this special is level 100.</t>
+    <t xml:space="preserve">Let the wilds guide Healing Rivers, even when you walk another road. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% healing per level, reaching 150% at level 100; it also adds 1.5% health per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Natures Balancing Bliss</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain an extra 100% in Damage, Ac, Healing, Health and Damage Stat by level 100 of this specialty.</t>
+    <t xml:space="preserve">Let the wilds guide Natures Balancing Bliss, even when you walk another road. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% weapon and ring damage per level, reaching 100% at level 100; it also adds 1% healing per level, reaching 100% at level 100; it also adds 1% armour class per level, reaching 100% at level 100; it also adds 1% health per level, reaching 100% at level 100; and it also adds 1% damage stat per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Rangers Tangled Roots</t>
   </si>
   <si>
-    <t xml:space="preserve">Do 10,000 Damage growing by 100 over time for an additional 10,000 damage using 30% of your damage stat. You will also grow your healing to 300% and your base damage stat to 200% at level 100 of this special. Damage only works for Cast and Attack.</t>
+    <t xml:space="preserve">Let the wilds guide Rangers Tangled Roots, even when you walk another road. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when casting and attacking, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 25% of your damage stat; it also adds 2.5% healing per level, reaching 250% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">cast_and_attack</t>
@@ -301,661 +301,661 @@
     <t xml:space="preserve">Blinding Arrow</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 15,000 damage growing by 200 per level for a maximum of an additional 20,000 damage. You will also use 15% of your damage stat and increase your base damage by 150% at level 100 of this special.</t>
+    <t xml:space="preserve">Let the wilds guide Blinding Arrow, even when you walk another road. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 15,000 specialty damage when using an attack, gains 200 damage per level, and reaches 35,000 damage at level 100, adding 15% of your damage stat; it also adds 1.5% weapon and ring damage per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Raging Winds</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 30,000 damage growing by 300 per level to a maximum of 30,000 additional damage. You will use 25% of your damage stat. This special's damage will only fire on Cast attacks and increase spell damage by 50% at level 100.</t>
+    <t xml:space="preserve">Let the wilds guide Raging Winds, even when you walk another road. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 30,000 specialty damage when casting, gains 300 damage per level, and reaches 60,000 damage at level 100, adding 25% of your damage stat; it also adds 0.5% spell damage per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Shadows of the Bow</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 60,000 damage growing by 600 over time for an additional 60,000 damage, while also applying 20% of your damage stat towards the damage. You will also increase your Armour class and healing by 100% at level 100 of this special. This specials damage will only fire for Attack based attacks.</t>
+    <t xml:space="preserve">Let the wilds guide Shadows of the Bow, even when you walk another road. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 60,000 specialty damage when using an attack, gains 600 damage per level, and reaches 120,000 damage at level 100, adding 20% of your damage stat; it also adds 1% healing per level, reaching 100% at level 100; and it also adds 1% armour class per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Churches Faith</t>
   </si>
   <si>
-    <t xml:space="preserve">Grows your Healing by 200% at level 100 of this special.</t>
+    <t xml:space="preserve">Call on visions and prophecy through Churches Faith. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% healing per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Hardened Church Records</t>
   </si>
   <si>
-    <t xml:space="preserve">Through your studies you will grow your AC by 150%, Healing by 300% and Spell Damage by 50% when this special is level 100.</t>
+    <t xml:space="preserve">Call on visions and prophecy through Hardened Church Records. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.5% spell damage per level, reaching 50% at level 100; it also adds 2.5% healing per level, reaching 250% at level 100; and it also adds 1.5% armour class per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Raging Prayer</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 5,000 Damage and grows by 50 over time to do an additional 5,000 damage. Will use 15% of your damage stat but also grows your damage stat to +150% by level 100.</t>
+    <t xml:space="preserve">Call on visions and prophecy through Raging Prayer. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when casting, gains 50 damage per level, and reaches 10,000 damage at level 100, adding 15% of your damage stat; it also adds 1.5% damage stat per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Prayer of Strength</t>
   </si>
   <si>
-    <t xml:space="preserve">Grows Damage by 100%, AC by 100%, Healing by 300%, Health by 250% and Damage Stat by 250% at level 100.</t>
+    <t xml:space="preserve">Call on visions and prophecy through Prayer of Strength. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% weapon and ring damage per level, reaching 100% at level 100; it also adds 2.5% healing per level, reaching 250% at level 100; it also adds 1% armour class per level, reaching 100% at level 100; it also adds 2.5% health per level, reaching 250% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Prophets Curse</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 10,000 Damage growing by 100 over time for a max of an additional 10,000 damage. This specials damage will only fire when using Cast and Attack. This special will also grow your damage stat by 200% at level 100</t>
+    <t xml:space="preserve">Call on visions and prophecy through Prophets Curse. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when casting and attacking, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 20% of your damage stat; it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Heretical Research</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 15,000 damage growing by 150 over time for an additional 15,000 damage while also using 20% of your damage stat on top. Will only fire the damage if you use Attack and Cast. Will grow your damage by 100% and your spell damage by 150% when at level 100.</t>
+    <t xml:space="preserve">Call on visions and prophecy through Heretical Research. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 15,000 specialty damage when attacking and casting, gains 150 damage per level, and reaches 30,000 damage at level 100, adding 20% of your damage stat; it also adds 1% weapon and ring damage per level, reaching 100% at level 100; and it also adds 1.5% spell damage per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Prophetic Visions of Death</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 20,000 damage growing by 200 over time for an additional 20,000 damage using 22% of your damage stat on top. Only fires for Cast attacks. Will grow your healing by 400% at level 100.</t>
+    <t xml:space="preserve">Call on visions and prophecy through Prophetic Visions of Death. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 20,000 specialty damage when casting, gains 200 damage per level, and reaches 40,000 damage at level 100, adding 22% of your damage stat; it also adds 2.5% healing per level, reaching 250% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Ray of Judgement</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 50,000 damage growing by 500 over time to do an additional 50,00 damage using 30% of your damage stat only when using Cast and Attack. This will also grow your healing by 400% at level 100 and your damage stat by 200% at level 100.</t>
+    <t xml:space="preserve">Call on visions and prophecy through Ray of Judgement. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when casting and attacking, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 25% of your damage stat; it also adds 2.5% healing per level, reaching 250% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Prophets Holy Spell</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 60,000 Damage growing by 600 over time for an additional 60,000 damage +30% of your damage stat.</t>
+    <t xml:space="preserve">Call on visions and prophecy through Prophets Holy Spell. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 60,000 specialty damage when casting, gains 600 damage per level, and reaches 120,000 damage at level 100, adding 30% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">Back Stab</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1,000 Damage growing by 10 for an additional 1,000 damage at level 100. will apply 10% of your damage stat. Can only be used with the "Attack" attack. Will grow your damage and damage stat by an additional 100% at level 100</t>
+    <t xml:space="preserve">Turn shadows, speed, and dirty tricks into Back Stab. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 1,000 specialty damage when using an attack, gains 10 damage per level, and reaches 2,000 damage at level 100, adding 10% of your damage stat; it also adds 1% weapon and ring damage per level, reaching 100% at level 100; and it also adds 1% damage stat per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Shadow Attack</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal damage from the shadows doing 2,000 damage, growing over time by 200, for an additional 2000 damage using 10% of your damage stat. Can only be used with Attack and Cast and will increase your damage stat by 100% while growing your spell damage by 50% at level 100.</t>
+    <t xml:space="preserve">Turn shadows, speed, and dirty tricks into Shadow Attack. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 2,000 specialty damage when casting and attacking, gains 20 damage per level, and reaches 4,000 damage at level 100, adding 10% of your damage stat; it also adds 0.5% spell damage per level, reaching 50% at level 100; and it also adds 1% damage stat per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Thieves Guild</t>
   </si>
   <si>
-    <t xml:space="preserve">Grows damage by 250%, health by 150% and your damage stat by 250% at level 100</t>
+    <t xml:space="preserve">Turn shadows, speed, and dirty tricks into Thieves Guild. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 1.5% health per level, reaching 150% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Throat Slit</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 5,000 damage, growing by 50 for an additional 5,000 damage using 14% of your total damage stat. Only fires for "Attack" attacks. Grows your damage by 200% at level 100.</t>
+    <t xml:space="preserve">Only fires for "Attack" attacks. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when using an attack, gains 50 damage per level, and reaches 10,000 damage at level 100, adding 14% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Light Footed</t>
   </si>
   <si>
-    <t xml:space="preserve">Grows Damage by 260%, AC by 50%, health by 100% and Damage Stat by 120% when the level of this special is 100.</t>
+    <t xml:space="preserve">Turn shadows, speed, and dirty tricks into Light Footed. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 0.5% armour class per level, reaching 50% at level 100; it also adds 1% health per level, reaching 100% at level 100; and it also adds 1.2% damage stat per level, reaching 120% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Throwing Knives</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 10,000 damage growing by 100 over time for an additional 10,000 damage using 18% of your damage stat for additional damage. Only fires when using Attack.</t>
+    <t xml:space="preserve">Turn shadows, speed, and dirty tricks into Throwing Knives. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when using an attack, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 18% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">Heart Stopper</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 30,000 Damage growing by 300 over time for an additional 30,000 damage using 22% of your damage stat. Only fires for the "Attack" attack. Will grow your Damage Stat by 300% at level 100.</t>
+    <t xml:space="preserve">Turn shadows, speed, and dirty tricks into Heart Stopper. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 30,000 specialty damage when using an attack, gains 300 damage per level, and reaches 60,000 damage at level 100, adding 22% of your damage stat; it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Violent Robbery</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 45,000 damage growing by 450 over time for an additional 45,000 damage and applies 25% of your damage stat on top. Only fires for Attack. grow your damage, health and damage stat by 100% at level 100.</t>
+    <t xml:space="preserve">Turn shadows, speed, and dirty tricks into Violent Robbery. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 45,000 specialty damage when using an attack, gains 450 damage per level, and reaches 90,000 damage at level 100, adding 25% of your damage stat; it also adds 1% weapon and ring damage per level, reaching 100% at level 100; it also adds 1% health per level, reaching 100% at level 100; and it also adds 1% damage stat per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Final Wishes</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 50,000 damage growing by 500 over time to do an additional 50,000 damage. Will apply 26% of your damage stat to the damage. Only fires for Attack. Grows your damage stat by 400% at level 100.</t>
+    <t xml:space="preserve">Turn shadows, speed, and dirty tricks into Final Wishes. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when using an attack, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 25% of your damage stat; it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Smithies Strength</t>
   </si>
   <si>
-    <t xml:space="preserve">Grow your damage to an additional 300% at level 100 of this specialty.</t>
+    <t xml:space="preserve">Forge the heat of the anvil into Smithies Strength. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2.5% weapon and ring damage per level, reaching 250% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Smiths Hammer</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain 250% AC and Health as well as 300% Damage Stat Increase when this special is level 100.</t>
+    <t xml:space="preserve">Forge the heat of the anvil into Smiths Hammer. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2.5% armour class per level, reaching 250% at level 100; it also adds 2.5% health per level, reaching 250% at level 100; and it also adds 2.5% damage stat per level, reaching 250% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Hammer Quake</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 15,000 Damage doing 150 extra damage per level for a total of an extra 15,000 damage at level 100. Uses 25% of your damage stat and grows your damage to +300% at level 100. Must use Attack to get the special damage to fire.</t>
+    <t xml:space="preserve">Forge the heat of the anvil into Hammer Quake. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 15,000 specialty damage when using an attack, gains 150 damage per level, and reaches 30,000 damage at level 100, adding 25% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Smithies Furnace</t>
   </si>
   <si>
-    <t xml:space="preserve">Increase your AC to 500% when this specialty is level 100</t>
+    <t xml:space="preserve">Forge the heat of the anvil into Smithies Furnace. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 5% armour class per level, reaching 500% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Magical Hammer</t>
   </si>
   <si>
-    <t xml:space="preserve">Using the magic of Purgatory, when you Attack and Cast you will do 18,000 damage growing by 180 per level, for an additional 18,000 damage + 16% of your damage stat. You will also grow your damage by 200%, your spell damage by 100% and your damage stat by 300% at level 100.</t>
+    <t xml:space="preserve">Forge the heat of the anvil into Magical Hammer. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 18,000 specialty damage when attacking and casting, gains 180 damage per level, and reaches 36,000 damage at level 100, adding 16% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 1% spell damage per level, reaching 100% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Clerics Light</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 20,000 Damage growing by 200 over time to a maximum of an additional 20,000 damage while using 20% of your damage stat as additional damage. The special's damage will only fire during Cast and Attack. Grow your Healing, health and damage stat by 200% by level 100.</t>
+    <t xml:space="preserve">Forge the heat of the anvil into Clerics Light. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 20,000 specialty damage when attacking and casting, gains 200 damage per level, and reaches 40,000 damage at level 100, adding 20% of your damage stat; it also adds 2% healing per level, reaching 200% at level 100; it also adds 2% health per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Brace For Impact!</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 50,000 damage growing it by 500 over time for an additional 50,000 damage. We will also use 25% of your damage stat as additional damage. Only fires during Defend and will help you grow your AC by 400% at level 100.</t>
+    <t xml:space="preserve">Forge the heat of the anvil into Brace For Impact. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when defending, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 25% of your damage stat; it also adds 4% armour class per level, reaching 400% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Judgment Hammer</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 60,000 damage growing by 600 over time for an additional 60,000 damage while also using 28% of your damage stat for additional damage. Will grow your base damage stat by 600% at level 100. Damage only fires during "Attack" attacks.</t>
+    <t xml:space="preserve">Forge the heat of the anvil into Judgment Hammer. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 60,000 specialty damage when using an attack, gains 600 damage per level, and reaches 120,000 damage at level 100, adding 25% of your damage stat; it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Skull Crusher</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 70,000 Damage growing by 700 over time for an additional 70,000 damage and will use 10% of your damage stat for traditional damage. Only fires during Attack. Will grow damage and damage stat by 400% at level 100.</t>
+    <t xml:space="preserve">Forge the heat of the anvil into Skull Crusher. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 70,000 specialty damage when using an attack, gains 700 damage per level, and reaches 140,000 damage at level 100, adding 10% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Arcane Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Grows Damage, Spell Damage and Damage Stat by 200% at level 100.</t>
+    <t xml:space="preserve">Mix unstable power and arcane craft into Arcane Studies. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 2% spell damage per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Arcane Bolt</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 1,000 damage growing by 50, for an additional 5,000 damage + 25% of your damage stat. The damage only fires during Cast attacks. Will grow your spell damage and damage stat by 250% at level 100. [Must use CAST for the damage to fire.]</t>
+    <t xml:space="preserve">The damage only fires during Cast attacks. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 1,000 specialty damage when casting, gains 50 damage per level, and reaches 6,000 damage at level 100, adding 25% of your damage stat; it also adds 2% spell damage per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Black and White</t>
   </si>
   <si>
-    <t xml:space="preserve">Grow Ac by 150% and healing by 90% at level 100. Health and spell damage will also grow by 250% at level 100.</t>
+    <t xml:space="preserve">Mix unstable power and arcane craft into Black and White. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2.5% spell damage per level, reaching 250% at level 100; it also adds 0.9% healing per level, reaching 90% at level 100; it also adds 1.5% armour class per level, reaching 150% at level 100; and it also adds 2.5% health per level, reaching 250% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Winters Blast</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 5,000 Damage growing by 250 to an additional 25,000 damage adding an additional 30% of your damage stat to the damage of this special which only fires during Cast and Attack. Will also grow your damage and spell damage by 200%.</t>
+    <t xml:space="preserve">Mix unstable power and arcane craft into Winters Blast. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when casting and attacking, gains 250 damage per level, and reaches 30,000 damage at level 100, adding 25% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; and it also adds 2% spell damage per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Arcane Strike</t>
   </si>
   <si>
-    <t xml:space="preserve">Will deal 8,000 damage doing an additional 500 damage growing to 50,000 additional damage. Will use 30% of your damage stat as bonus damage. Will also grow your damage and damage stat by 200% at level 100. [Must use ATTACK AND CAST for the damage to fire.]</t>
+    <t xml:space="preserve">Mix unstable power and arcane craft into Arcane Strike. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 8,000 specialty damage when attacking and casting, gains 500 damage per level, and reaches 58,000 damage at level 100, adding 25% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Arcane Cast</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 15,000 damage growing by 500 to an additional 50,000 damage adding an additional 25% of your damage stat on top. Will also grow your damage and AC mod by 200%</t>
+    <t xml:space="preserve">Mix unstable power and arcane craft into Arcane Cast. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 15,000 specialty damage, gains 500 damage per level, and reaches 65,000 damage at level 100, adding 25% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; and it also adds 2% armour class per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Surge of magic</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 25,000 damage and grows by 500 for an additional 50,000 damage while applying 25% of your damage stat as damage while casting. Will increase your Spell Damage by 400% at level 100</t>
+    <t xml:space="preserve">Mix unstable power and arcane craft into Surge of magic. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 25,000 specialty damage when casting, gains 500 damage per level, and reaches 75,000 damage at level 100, adding 25% of your damage stat; it also adds 2% spell damage per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Faith's Magic</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 50,000 Damage and grows by 500 for an additional 50,000 damage. Will apply 20% of your damage stat to the damage dealt. Will increase healing and health by 400% and your damage stat by 400% at level 100. [Must use CAST AND ATTACK for the damage to fire.]</t>
+    <t xml:space="preserve">Mix unstable power and arcane craft into Faith's Magic. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when casting and attacking, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 20% of your damage stat; it also adds 2.5% healing per level, reaching 250% at level 100; it also adds 3% health per level, reaching 300% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Meteor</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 60,000 Damage growing by 600 for an additional 60,000 damage while also applying 30% of your damage stat. Will grow your spell damage and damage stat by 500% at level 100. [Must use CAST for the damage to fire.]</t>
+    <t xml:space="preserve">Mix unstable power and arcane craft into Meteor. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 60,000 specialty damage when casting, gains 600 damage per level, and reaches 120,000 damage at level 100, adding 25% of your damage stat; it also adds 2% spell damage per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Sickening Hatred</t>
   </si>
   <si>
-    <t xml:space="preserve">While your enemy is having a hard time healing them selves (Healing reduction), you will increase your AC making you harder to hit. (Healing Reduction will be 100% be level 100, and Base AC will be +100% by level 100.)</t>
+    <t xml:space="preserve">While your enemy is having a hard time healing them selves, you will increase your AC making you harder to hit. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% armour class per level, reaching 100% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Casters Death</t>
   </si>
   <si>
-    <t xml:space="preserve">Increase your spell evasion by 100% at level 100 as well as increasing your damage by 200% at level 100</t>
+    <t xml:space="preserve">Drag chains, grit, and desperate freedom into Casters Death. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 0.5% spell evasion per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Magical Body Slam</t>
   </si>
   <si>
-    <t xml:space="preserve">Decrease the affix damage an enemy can do by 100% at level 100. Delve into spell casting and do an additional 75% damage with spells at level 100. Become less squishy with 100% extra health by level 100.</t>
+    <t xml:space="preserve">Drag chains, grit, and desperate freedom into Magical Body Slam. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.75% spell damage per level, reaching 75% at level 100; it also adds 1% health per level, reaching 100% at level 100; and it also adds 0.5% affix damage reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Skillful Rage</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1000 damage, growing by 10 per level for an additional 1000 damage using 25% of your base damage stat. Increases base damage by 200%, Armour class by 100%, health by 200% and damage stat by 100%. All while reducing the enemies skills by 100% at level 100.</t>
+    <t xml:space="preserve">Drag chains, grit, and desperate freedom into Skillful Rage. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 1,000 specialty damage when using an attack, gains 10 damage per level, and reaches 2,000 damage at level 100, adding 25% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 1% armour class per level, reaching 100% at level 100; it also adds 2% health per level, reaching 200% at level 100; it also adds 1% damage stat per level, reaching 100% at level 100; and it also adds 0.5% skill reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Prisoners Defense</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 5000 damage growing by 50 for an additional 5000 damage at level 100 (only while defending). Uses 25% of your damage stat. Increases damage mod by 100% and your Armour class by 300%</t>
+    <t xml:space="preserve">Drag chains, grit, and desperate freedom into Prisoners Defense. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when defending, gains 50 damage per level, and reaches 10,000 damage at level 100, adding 25% of your damage stat; it also adds 1% weapon and ring damage per level, reaching 100% at level 100; and it also adds 3% armour class per level, reaching 300% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Prisoners Swarm</t>
   </si>
   <si>
-    <t xml:space="preserve">Reduces all aspects of an enemy by 100% at level 100 and gives you 100% extra spell evasion. You will deal, only while attacking, 10,000 damage growing by 100 per level for an additional 10,000 damage. The damage will also add 30% of your damage stat. Will also increase Health and Damage Stat by 200%</t>
+    <t xml:space="preserve">Drag chains, grit, and desperate freedom into Prisoners Swarm. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when using an attack, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 25% of your damage stat; it also adds 2% health per level, reaching 200% at level 100; it also adds 2% damage stat per level, reaching 200% at level 100; it also adds 0.5% spell evasion per level, reaching 50% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Jugular Slashing</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 25,000 Damage growing by 250 per level for an additional 25,000 damage adding 35% of your damage.</t>
+    <t xml:space="preserve">Drag chains, grit, and desperate freedom into Jugular Slashing. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 25,000 specialty damage when using an attack, gains 250 damage per level, and reaches 50,000 damage at level 100, adding 30% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">Guard Rush</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 50,000 damage growing by 500 doing an additional 50,000 damage using 45% of your damage stat.</t>
+    <t xml:space="preserve">Drag chains, grit, and desperate freedom into Guard Rush. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when using an attack, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 30% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">Freedom is in reach!</t>
   </si>
   <si>
-    <t xml:space="preserve">Race for the freedom, kill for it! Deal 100,000 damage growing by 1,000 for an additional 100,000 damage using 15% of your damage stat. Increase your damage and Damage Stat by 500% at level 100.</t>
+    <t xml:space="preserve">Race for the freedom, kill for it! The lesson can still be carried into another class when equipped. As you level this specialty, it deals 100,000 specialty damage when using an attack, gains 1,000 damage per level, and reaches 200,000 damage at level 100, adding 15% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Drinking Contest</t>
   </si>
   <si>
-    <t xml:space="preserve">Lets have a drinking contest and see who gets blackout drunk first!</t>
+    <t xml:space="preserve">Lets have a drinking contest and see who gets blackout drunk first! The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 5% health per level, reaching 500% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Alcoholics Rage</t>
   </si>
   <si>
-    <t xml:space="preserve">You get black out drunk and flip tables, rage out and get extremely violent towards others!</t>
+    <t xml:space="preserve">You get black out drunk and flip tables, rage out and get extremely violent towards others! The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Passed out drunk</t>
   </si>
   <si>
-    <t xml:space="preserve">You are so drunk that you end up passing out. Nothing seems to be able to wake you. (Increases Armour and Health)</t>
+    <t xml:space="preserve">You are so drunk that you end up passing out. Nothing seems to be able to wake you. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 5% armour class per level, reaching 500% at level 100; it also adds 5% health per level, reaching 500% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Blind Rage</t>
   </si>
   <si>
-    <t xml:space="preserve">Attack your foes with all you have! Drink your drink, rage on out! (Deals 1000 Damage, using 5% of your damage stat and growing by 10 over time for an additional 1000 damage)</t>
+    <t xml:space="preserve">Attack your foes with all you have! Drink your drink, rage on out! The lesson can still be carried into another class when equipped. As you level this specialty, it deals 1,000 specialty damage, gains 10 damage per level, and reaches 2,000 damage at level 100, adding 5% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 3% health per level, reaching 300% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">The bottom of the bottle</t>
   </si>
   <si>
-    <t xml:space="preserve">Work your way to the bottom of the bottle of where your courage truly lies. Battle is upon you. (deal 10,000 Damage, using 10% of your damage stat and an additional 1000 damage for a total of an extra 10,000 damage on top.)</t>
+    <t xml:space="preserve">Work your way to the bottom of the bottle of where your courage truly lies. Battle is upon you. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when using an attack, gains 1,000 damage per level, and reaches 110,000 damage at level 100, adding 10% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 3% armour class per level, reaching 300% at level 100; it also adds 3% health per level, reaching 300% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Fists of hate</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal incredible damage with your fists as you pummel the enemy into a bloody mess. (Deal 40,000 in damage using 20% of your damage stat and growing by 4000 damage over time for an additional 40,000 damage)</t>
+    <t xml:space="preserve">Deal incredible damage with your fists as you pummel the enemy into a bloody mess. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 40,000 specialty damage when using an attack, gains 2,100 damage per level, and reaches 250,000 damage at level 100, adding 20% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">The bottle is life</t>
   </si>
   <si>
-    <t xml:space="preserve">Alcohol gives you strength, gives you life. it's all you know. (Deal 50,000 damage using 30% of your damage stat and growing by 5,000 damage over time for an additional 50,000 damage)</t>
+    <t xml:space="preserve">Alcohol gives you strength, gives you life. it's all you know. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when using an attack, gains 2,000 damage per level, and reaches 250,000 damage at level 100, adding 25% of your damage stat; it also adds 5% health per level, reaching 500% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Demons in your veins</t>
   </si>
   <si>
-    <t xml:space="preserve">You drink and drink and cannot seem to quench the thirst, you cannot seem to quiet the demons in your head. (Deal 80,000 Damage, growing by 8,000 damage for an additional 80,000 damage and use 40% of your damage stat towards the damage)</t>
+    <t xml:space="preserve">You drink and drink and cannot seem to quench the thirst, you cannot seem to quiet the demons in your head. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 80,000 specialty damage when using an attack, gains 1,700 damage per level, and reaches 250,000 damage at level 100, adding 25% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 3% health per level, reaching 300% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Merchants Coin</t>
   </si>
   <si>
-    <t xml:space="preserve">Merchants need their coin, don't let anyone get in the way of that! Grow your damage stat by 2.5% over time for a total of 250% at level 100. Your damage stat will also grow by 1% over time for a total of 100% at level 100. Finally, your AC (Defence) will grow by 2% over time for a total of 200% at level 100.</t>
+    <t xml:space="preserve">Merchants need their coin, don't let anyone get in the way of that! The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 2% armour class per level, reaching 200% at level 100; and it also adds 1% damage stat per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Merchants Sale</t>
   </si>
   <si>
-    <t xml:space="preserve">What do you have for sale? Deals 1000 Damage growing by 10 over time for an additional 1000 damage using 5% of your damage stat. We will also grow your damage stat by 1.5% over time for a total of 150% at level 100. The damage of this speciality will only trigger when you use ATTACK.</t>
+    <t xml:space="preserve">What do you have for sale?. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 1,000 specialty damage when using an attack, gains 10 damage per level, and reaches 2,000 damage at level 100, adding 5% of your damage stat; it also adds 1.5% damage stat per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Merchants Charm</t>
   </si>
   <si>
-    <t xml:space="preserve">Charm the enemy into letting their guard down. (Reduces enemy skills and resistances). Reduces enemy skills and resistances by 0.5% for a total of 50% at level 100.</t>
+    <t xml:space="preserve">Charm the enemy into letting their guard down. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.5% skill reduction per level, reaching 50% at level 100; it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Sales Pitch</t>
   </si>
   <si>
-    <t xml:space="preserve">Make a sale to your enemy. They will do less damage now - through their affixes, but they might still kill you. This will reduce the enemies affix damage by 0.25% for a total of 25% at level 100.</t>
+    <t xml:space="preserve">Make a sale to your enemy. They will do less damage now - through their affixes, but they might still kill you. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.25% affix damage reduction per level, reaching 25% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Caravans War</t>
   </si>
   <si>
-    <t xml:space="preserve">Lash out at the enemy with a caravans strength. Deal 10,000 Damage ground by 100 for an additional 10,000 damage. Use 25% of your damage stat. We will grow your damage modifier by 1.5% for a total of 150% at level 100. Your armour class (defence) will grow by 2% for a total of 200% at level 100. Finally your healing will grow by 1.5% for a total of 150% at level 100. The damage of this special will only trigger when you use ATTACK.</t>
+    <t xml:space="preserve">Lash out at the enemy with a caravans strength. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when using an attack, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 25% of your damage stat; it also adds 1.5% weapon and ring damage per level, reaching 150% at level 100; it also adds 1.5% healing per level, reaching 150% at level 100; it also adds 2% armour class per level, reaching 200% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Merchants Defence</t>
   </si>
   <si>
-    <t xml:space="preserve">Defend your self child, the enemy comes! Deals 5,000 damage growing by 50 for an additional 5,000 damage over time using 15% of your damage but only when using defend.Your Damage will grow by 1.75% over time to 175% at level 100, your armour class (defence) will grow by 2.5% over time to 250% at level 100. Finally the enemies skills and resistance will bet reduced by 0.75% over time for a total of 75% at level 100. Your spell evasion will grow by 0.15% over time for a total of 15% at level 100. The damage of this special will only trigger when you use DEFEND.</t>
+    <t xml:space="preserve">Defend your self child, the enemy comes! The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when defending, gains 50 damage per level, and reaches 10,000 damage at level 100, adding 15% of your damage stat; it also adds 1.75% weapon and ring damage per level, reaching 175% at level 100; it also adds 2.5% armour class per level, reaching 250% at level 100; it also adds 0.15% spell evasion per level, reaching 15% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Coin Flip</t>
   </si>
   <si>
-    <t xml:space="preserve">Flip a coin and see what happens. Deals 25,000 damage growing by 250 over time for an additional 25,000 damage using 30% of your damage stat. This specialty will also grow your attack by 2% over time for a total of 200% towards your damage and your damage stat will increase by 1% over time for a total of 100% at level 100. The Damage of this specialty will only trigger when you use ATTACK.</t>
+    <t xml:space="preserve">Flip a coin and see what happens. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 25,000 specialty damage when using an attack, gains 250 damage per level, and reaches 50,000 damage at level 100, adding 25% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; and it also adds 1% damage stat per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Caravans Last Stand</t>
   </si>
   <si>
-    <t xml:space="preserve">Traveling with a caravan of merchants allows you to call on them when you need them the most. Deals 50,000 damage growing by 500 over time, using 15% of your damage stat. This only works when defending. This specialy will also grow you Damage, AC (Defence) and Healing by 1.75% over time to a total of 175% at level 100. You will reduce the Skill, Affix Damage, Healing and Geneeral Resistance of the enemy by 0.75% over time for a total of 75% at level 100. And finally your Spell Evasion will increade by .30% ove time for a total of 30% at level 100. The Damage of this specialty will only trigger during DEFEND.</t>
+    <t xml:space="preserve">Traveling with a caravan of merchants allows you to call on them when you need them the most. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when defending, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 15% of your damage stat; it also adds 1.75% weapon and ring damage per level, reaching 175% at level 100; it also adds 1.75% healing per level, reaching 175% at level 100; it also adds 1.75% armour class per level, reaching 175% at level 100; it also adds 0.3% spell evasion per level, reaching 30% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Magical Trade</t>
   </si>
   <si>
-    <t xml:space="preserve">Your dealings with the mages and the magical folk on the road have trained you well. Use your cast and attack to deal 60,000 damage growing by 600 over time for an additional 60,000 damage using 10% of your damage stat. The enemies spells are useless against you. This speciality will increase your Damage and your Spell Damage by 2% over time for a total of 200% at level 100. Your Spell Evasion will increase by .75% over time for a total of 75% at level 100. This specialities Damage only triggers when you use CAST AND ATTACK.</t>
+    <t xml:space="preserve">Your dealings with the mages and the magical folk on the road have trained you well. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 60,000 specialty damage when attacking and casting, gains 600 damage per level, and reaches 120,000 damage at level 100, adding 10% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 2% spell damage per level, reaching 200% at level 100; and it also adds 0.5% spell evasion per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Dancing Queen</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain 12% towards your damage for each level - for a total of +120% damage.</t>
+    <t xml:space="preserve">Move through battle with rhythm and grace through Dancing Queen. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.2% weapon and ring damage per level, reaching 120% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Confusing Day Dream Dance</t>
   </si>
   <si>
-    <t xml:space="preserve">Over time, you will reduce the enemies abilities to heal, do damage and so on, listed under Reductions Section, by 100%. You will also gain 100%, over time, in your base damage stat.</t>
+    <t xml:space="preserve">Move through battle with rhythm and grace through Confusing Day Dream Dance. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% damage stat per level, reaching 100% at level 100; it also adds 0.5% spell evasion per level, reaching 50% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Self Loving Dance</t>
   </si>
   <si>
-    <t xml:space="preserve">Increase your healing to 200% over time. You will also gain 140% over time, towards your health and 50% towards your damage stat</t>
+    <t xml:space="preserve">Move through battle with rhythm and grace through Self Loving Dance. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% healing per level, reaching 200% at level 100; it also adds 1.4% health per level, reaching 140% at level 100; and it also adds 0.5% damage stat per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Deadly strip tease</t>
   </si>
   <si>
-    <t xml:space="preserve">You will deal 5,000 +25% of your damage stat growing by 50 points per level for a total of 10,000 Damage +25% of your base damage stat. You must use ATTACK for this to trigger.</t>
+    <t xml:space="preserve">You must use ATTACK for this to trigger. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when using an attack, gains 50 damage per level, and reaches 10,000 damage at level 100, adding 25% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">Spell Weavers Dance</t>
   </si>
   <si>
-    <t xml:space="preserve">As you weave your magic into your dance you will do 10,000 + 18% of your damage stat as damage, growing by 100 over time for an additional 10,000 damage. Your spell damage will grow by +75% over time, while the enemies spell evasion will fall by 50% over time. You must use CAST attack for this to trigger.</t>
+    <t xml:space="preserve">Move through battle with rhythm and grace through Spell Weavers Dance. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when casting, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 18% of your damage stat; it also adds 0.75% spell damage per level, reaching 75% at level 100; and it also adds 0.5% spell evasion per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Double Dipping Tips</t>
   </si>
   <si>
-    <t xml:space="preserve">As you dance to steal your enemies tips, you will do 15,000 damage + 12% of your damage stat while growing this damage by 300 over time, for a total of 30,000 extra damage. You will also raise your damage by 200%, your spell damage by 100% and your damage stat by 50%, over time, Damage is only done when you use ATTACK AND CAST</t>
+    <t xml:space="preserve">Move through battle with rhythm and grace through Double Dipping Tips. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 15,000 specialty damage when attacking and casting, gains 300 damage per level, and reaches 45,000 damage at level 100, adding 12% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 1% spell damage per level, reaching 100% at level 100; and it also adds 0.5% damage stat per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Rage Induced Dance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reduces the affix damage and the resistances and enemy has by 100% over time. Deal 30,000 Damage growing by an additional 30,000 damage with +50% of your damage stat while you grow your damage stat by 200% over time. Damage is only dealt when using ATTACK.</t>
+    <t xml:space="preserve">Move through battle with rhythm and grace through Rage Induced Dance. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 30,000 specialty damage when using an attack, gains 300 damage per level, and reaches 60,000 damage at level 100, adding 25% of your damage stat; it also adds 2% damage stat per level, reaching 200% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">The Churches Dance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reduce the enemies healing by 100% over time, While increasing your own healing and health by 200%. Deal damage of 50,000 increasing by 500 for an additional 50,000 damage while applying 25% of your damage stat towards the over all damage. Damage only procs if you use CAST AND ATTACK.</t>
+    <t xml:space="preserve">Move through battle with rhythm and grace through The Churches Dance. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when casting and attacking, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 25% of your damage stat; it also adds 2% healing per level, reaching 200% at level 100; it also adds 2% health per level, reaching 200% at level 100; and it also adds 0.5% healing reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Wedding Dance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reduce all listed reductions by 100%, while dealing 100,000 Damage growing by an additional 100,000 damage over time and applying 20% of your damage stat to the damage while using ANY attack. Grow your damage by 250% over time and your base damage stat by 250% over time.</t>
+    <t xml:space="preserve">Move through battle with rhythm and grace through Wedding Dance. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 100,000 specialty damage, gains 1,000 damage per level, and reaches 200,000 damage at level 100, adding 20% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 2% damage stat per level, reaching 200% at level 100; it also adds 0.5% spell evasion per level, reaching 50% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Perfect Aim</t>
   </si>
   <si>
-    <t xml:space="preserve">Over time increase your damage and damage stat by 100%</t>
+    <t xml:space="preserve">Let powder, aim, and nerve define Perfect Aim. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% weapon and ring damage per level, reaching 100% at level 100; it also adds 1% damage stat per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Silencing Shot</t>
   </si>
   <si>
-    <t xml:space="preserve">Over time grow your damage to +150% and prevent the enemy from using their skills by up to 100%</t>
+    <t xml:space="preserve">Let powder, aim, and nerve define Silencing Shot. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% weapon and ring damage per level, reaching 150% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Shock to the system</t>
   </si>
   <si>
-    <t xml:space="preserve">Grow your damage to +150% and reduce the enemies resistances by 100% - over time.</t>
+    <t xml:space="preserve">Let powder, aim, and nerve define Shock to the system. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% damage stat per level, reaching 150% at level 100; it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Sniper Shot</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 5,000 Damage using 20% of your damage stat as bonus - which will then grow by 50 for an additional 5,000 damage - only while using ATTACK. You will also grow your damage by +150%</t>
+    <t xml:space="preserve">Let powder, aim, and nerve define Sniper Shot. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when using an attack, gains 50 damage per level, and reaches 10,000 damage at level 100, adding 20% of your damage stat; it also adds 1.5% weapon and ring damage per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Drowning Shot</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 10,000 Damage growing by 100 for an additional 10,000 damage while applying 25% of your damage stat to the damage - only while using ATTACK. Reduce all aspects of the enemy by 100% over time.</t>
+    <t xml:space="preserve">Let powder, aim, and nerve define Drowning Shot. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when using an attack, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 25% of your damage stat; it also adds 0.5% spell evasion per level, reaching 50% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Gunslinger's Deliverance</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 20,000 Damage while growing it by 200 for an additional 20,000 and applying 27% of your damage stat as bonus damage. Damage is only dealt while using ATTACK AND CAST. You will also grow your spell damage by 125% over time and reduce the enemies spell evasion and affix damage by 100% over time.</t>
+    <t xml:space="preserve">Damage is only dealt while using ATTACK AND CAST. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 20,000 specialty damage when attacking and casting, gains 200 damage per level, and reaches 40,000 damage at level 100, adding 25% of your damage stat; it also adds 1.25% spell damage per level, reaching 125% at level 100; it also adds 0.5% spell evasion per level, reaching 50% at level 100; and it also adds 0.5% affix damage reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Devastating Blow</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 25,000 Damage growing by 250 damage for an additional 25,000 damage with 30% of your damage stat as bonus. This only procs while using ATTACK. You will also grow your own damage by +250% over time.</t>
+    <t xml:space="preserve">Let powder, aim, and nerve define Devastating Blow. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 25,000 specialty damage when using an attack, gains 250 damage per level, and reaches 50,000 damage at level 100, adding 25% of your damage stat; it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Spell Shot</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 50,000 in damage growing by 500 for an additional 50,000 damage while applying 12% of your damage stat as bonus damage. Damage only procs during Cast and Attack. Reduce ass aspects on an enemy by 100% over time and grow your own spell damage by +200%</t>
+    <t xml:space="preserve">Let powder, aim, and nerve define Spell Shot. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when casting and attacking, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 12% of your damage stat; it also adds 2% spell damage per level, reaching 200% at level 100; it also adds 0.5% spell evasion per level, reaching 50% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Shot</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 75,000 Damage growing by 750 damage while applying 40% of your damage stat to the over all damage as a bonus. Only procs when using DEFEND. Will also grow your base damage stat by +300% overtime.</t>
+    <t xml:space="preserve">Let powder, aim, and nerve define Defensive Shot. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 75,000 specialty damage when defending, gains 750 damage per level, and reaches 150,000 damage at level 100, adding 25% of your damage stat; it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Clerical Prayer</t>
   </si>
   <si>
-    <t xml:space="preserve">Over time grow your health by +50% and boost your healing - done through healing spells - by +150% over time.</t>
+    <t xml:space="preserve">Channel faith, wrath, and mercy through Clerical Prayer. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% healing per level, reaching 150% at level 100; it also adds 0.5% health per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Churches Grace</t>
   </si>
   <si>
-    <t xml:space="preserve">Increase Damage, Healing and Armour class by 150% and 170% (For AC overtime. Increase your health and damage stat by 75% over time,</t>
+    <t xml:space="preserve">Channel faith, wrath, and mercy through Churches Grace. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% weapon and ring damage per level, reaching 150% at level 100; it also adds 1.5% healing per level, reaching 150% at level 100; it also adds 1.7% armour class per level, reaching 170% at level 100; it also adds 0.75% health per level, reaching 75% at level 100; and it also adds 0.75% damage stat per level, reaching 75% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Blessed Rage</t>
   </si>
   <si>
-    <t xml:space="preserve">Reduce all aspects of the enemy (see reductions) by 100% over time. Increase your Armour class by 100%, Base Healing (through healing spells) by 170%, Spell Damage by 50%, health and damage stat by 100% - all overtime.</t>
+    <t xml:space="preserve">Channel faith, wrath, and mercy through Blessed Rage. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.5% spell damage per level, reaching 50% at level 100; it also adds 1.7% healing per level, reaching 170% at level 100; it also adds 1% armour class per level, reaching 100% at level 100; it also adds 1% health per level, reaching 100% at level 100; it also adds 1% damage stat per level, reaching 100% at level 100; it also adds 0.5% spell evasion per level, reaching 50% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Faithless War Cry</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 5,000 damage growing by 50 for an additional 5,000 damage while applying 5% of your damage stat as bonus damage. must use ATTACK for this to proc. You will grow your damage stat by 150% over time.</t>
+    <t xml:space="preserve">must use ATTACK for this to proc. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when using an attack, gains 50 damage per level, and reaches 10,000 damage at level 100, adding 5% of your damage stat; it also adds 1.5% damage stat per level, reaching 150% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Malicious Prayer</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 10,000 damage growing by 100 over time dealing an additional 10,000 damage, while applying 10% of your damage stat towards the damage. This will only proc while using ATTACK AND CAST. Grow your healing and damage stat by 200% over time and grow your health by 100%, overtime.</t>
+    <t xml:space="preserve">Channel faith, wrath, and mercy through Malicious Prayer. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when attacking and casting, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 10% of your damage stat; it also adds 2% healing per level, reaching 200% at level 100; it also adds 1% health per level, reaching 100% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">The Churches Holy Magic</t>
   </si>
   <si>
-    <t xml:space="preserve">Grow healing (Healing Spells) by 250%, Spell damage by 150% and your damage stat by 200% over time. Deal 25,000 damage, growing by 250 damage over time for an additional 25,000 damage., which will apply 20% of your damage stat as bonus damage - however this only procs if you use: CAST</t>
+    <t xml:space="preserve">Channel faith, wrath, and mercy through The Churches Holy Magic. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 25,000 specialty damage when casting, gains 250 damage per level, and reaches 50,000 damage at level 100, adding 20% of your damage stat; it also adds 1.5% spell damage per level, reaching 150% at level 100; it also adds 2.5% healing per level, reaching 250% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Churches Defence</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 40,000 damage, growing by 400 for an additional, 40,000 damage while applying 18% of your damage stat as bonus damage. Only procs if you use DEFEND. Grow your own AC by 200% over time.</t>
+    <t xml:space="preserve">Channel faith, wrath, and mercy through Churches Defence. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 40,000 specialty damage when defending, gains 400 damage per level, and reaches 80,000 damage at level 100, adding 18% of your damage stat; it also adds 2% armour class per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Wrath of the true God</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 60,000 Damage growing by 600 for an additional 60,000 damage while applying 15% of your damage stat as bonus damage. Only procs during ATTACK AND CAST. Grow your damage, ac and healing by 200% over time. Grow your damage stat by 300% over time.</t>
+    <t xml:space="preserve">Channel faith, wrath, and mercy through Wrath of the true God. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 60,000 specialty damage when attacking and casting, gains 600 damage per level, and reaches 120,000 damage at level 100, adding 15% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 2% healing per level, reaching 200% at level 100; it also adds 2% armour class per level, reaching 200% at level 100; it also adds 2% damage stat per level, reaching 200% at level 100; it also adds 0.5% spell evasion per level, reaching 50% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Churches Blessing on the Faithless</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 75,000 damage growing by 750 over time while adding 10% of your damage stat as bonus damage. Will proc during ANY attack type. Will grow all your modifiers by 200% overtime - such as Damage, Healing, Spell Damage, Health and Damage Stat.</t>
+    <t xml:space="preserve">Channel faith, wrath, and mercy through Churches Blessing on the Faithless. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 75,000 specialty damage, gains 750 damage per level, and reaches 150,000 damage at level 100, adding 10% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 2% spell damage per level, reaching 200% at level 100; it also adds 2% healing per level, reaching 200% at level 100; it also adds 2% armour class per level, reaching 200% at level 100; it also adds 2% health per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Enraged Engravings</t>
   </si>
   <si>
-    <t xml:space="preserve">Grow your damage and damage stat by +100%, grow your armor class and health by +50% over time.</t>
+    <t xml:space="preserve">Bind ink, pages, and forbidden lessons into Enraged Engravings. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% weapon and ring damage per level, reaching 100% at level 100; it also adds 0.5% armour class per level, reaching 50% at level 100; it also adds 0.5% health per level, reaching 50% at level 100; and it also adds 1% damage stat per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Study and Retention</t>
   </si>
   <si>
-    <t xml:space="preserve">Reduce aspects of the enemy, listed in the reductions section, by 100% over time.</t>
+    <t xml:space="preserve">Bind ink, pages, and forbidden lessons into Study and Retention. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.5% spell evasion per level, reaching 50% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; and it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Anger Management</t>
   </si>
   <si>
-    <t xml:space="preserve">Grow your damage and damage stat by +100% over time, while also growing your armor class by +50% and your health by +75%. Deal 1,000 Damage growing by 10 for an additional 1,000 damage with an additional 5% of your damage stat as bonus damage. This only procs if you use ATTACK.</t>
+    <t xml:space="preserve">Bind ink, pages, and forbidden lessons into Anger Management. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 1,000 specialty damage when using an attack, gains 10 damage per level, and reaches 2,000 damage at level 100, adding 5% of your damage stat; it also adds 1% weapon and ring damage per level, reaching 100% at level 100; it also adds 0.5% armour class per level, reaching 50% at level 100; it also adds 0.75% health per level, reaching 75% at level 100; and it also adds 1% damage stat per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Enchanted Books</t>
   </si>
   <si>
-    <t xml:space="preserve">Reduce your enemies spell evasion by 100% over time while you grow your own spell damage by 100%. Deal 2,000 Damage while growing it by 20 damage per level for an additional 2,000 damage. Apply 8% of your damage stat towards the damage, but this only procs if you use CAST</t>
+    <t xml:space="preserve">Bind ink, pages, and forbidden lessons into Enchanted Books. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 2,000 specialty damage when casting, gains 20 damage per level, and reaches 4,000 damage at level 100, adding 8% of your damage stat; it also adds 1% spell damage per level, reaching 100% at level 100; and it also adds 0.5% spell evasion per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Enchanted Scratch Awl</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 5,000 damage growing by 50 per level for an addition 5,000 damage. Apply 10% of your damage stat as bonus damage. This only procs if you use ATTACK AND CAST. Grow your damage and spell damage by +120% over time.</t>
+    <t xml:space="preserve">Bind ink, pages, and forbidden lessons into Enchanted Scratch Awl. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when attacking and casting, gains 50 damage per level, and reaches 10,000 damage at level 100, adding 10% of your damage stat; it also adds 1.2% weapon and ring damage per level, reaching 120% at level 100; and it also adds 1.2% spell damage per level, reaching 120% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Enraged Eye Stabber</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 10,000 damage growing by 100 for an additional 10,000 damage while applying 15% of your damage stat as bonus. Only procs during ATTACK. Grow your damage by 200% over time.</t>
+    <t xml:space="preserve">Bind ink, pages, and forbidden lessons into Enraged Eye Stabber. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when using an attack, gains 100 damage per level, and reaches 20,000 damage at level 100, adding 15% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Demonic Books</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 25,000 damage growing by 250 for an additional 25,000 damage while applying 18% of your damage stat as bonus damage. Only procs with CAST AND ATTACK. Grow your spell damage by +200% over time.</t>
+    <t xml:space="preserve">Bind ink, pages, and forbidden lessons into Demonic Books. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 25,000 specialty damage when casting and attacking, gains 250 damage per level, and reaches 50,000 damage at level 100, adding 18% of your damage stat; it also adds 2% spell damage per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Brace for Death</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 50,000 damage growing by 500 damage for an additional 50,000 damage. and applying 25% of your damage stat towards the damage as bonus. Only procs while using DEFEND. Grow your armor class by +200% over time.</t>
+    <t xml:space="preserve">Bind ink, pages, and forbidden lessons into Brace for Death. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 50,000 specialty damage when defending, gains 500 damage per level, and reaches 100,000 damage at level 100, adding 25% of your damage stat; it also adds 2% armour class per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Knowledge is key</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 75,000 damage growing by 750 for an additional 75,000 damage as well as adding 30% of your damage stat as bonus damage. Procs while using ANY attack. Grow all your attributes, see below, by +200% over time.</t>
+    <t xml:space="preserve">Procs while using ANY attack. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 75,000 specialty damage, gains 750 damage per level, and reaches 150,000 damage at level 100, adding 25% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; it also adds 2% spell damage per level, reaching 200% at level 100; it also adds 2% healing per level, reaching 200% at level 100; it also adds 2% armour class per level, reaching 200% at level 100; it also adds 2% health per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Pale Whisper</t>
   </si>
   <si>
-    <t xml:space="preserve">Increase your Damage and Healing by +50% at level 100.</t>
+    <t xml:space="preserve">Mix medicine, poison, and grave-dust into Pale Whisper. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.5% weapon and ring damage per level, reaching 50% at level 100; it also adds 0.5% healing per level, reaching 50% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Tincture of Faith</t>
   </si>
   <si>
-    <t xml:space="preserve">Grow your healing by +200% at level 100.</t>
+    <t xml:space="preserve">Mix medicine, poison, and grave-dust into Tincture of Faith. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% healing per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Hollow Existance</t>
   </si>
   <si>
-    <t xml:space="preserve">Grow your damage by +75%, your AC (defence) by +100% and your healing by +250% at level 100.</t>
+    <t xml:space="preserve">Mix medicine, poison, and grave-dust into Hollow Existance. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.75% weapon and ring damage per level, reaching 75% at level 100; it also adds 2.5% healing per level, reaching 250% at level 100; and it also adds 1% armour class per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Chalice of suffering</t>
   </si>
   <si>
-    <t xml:space="preserve">Increase damage by +100%, Healing by +250% and Health by +200% at level 100</t>
+    <t xml:space="preserve">Mix medicine, poison, and grave-dust into Chalice of suffering. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2.5% healing per level, reaching 250% at level 100; it also adds 2% health per level, reaching 200% at level 100; and it also adds 1% damage stat per level, reaching 100% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Cornered in a fight</t>
   </si>
   <si>
-    <t xml:space="preserve">Increase your damage by +300% at level 100</t>
+    <t xml:space="preserve">Mix medicine, poison, and grave-dust into Cornered in a fight. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2.5% damage stat per level, reaching 250% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Faithless Aboration</t>
   </si>
   <si>
-    <t xml:space="preserve">Increase your healing by +300% at level 100 and your spell damage by +150% at level 100.</t>
+    <t xml:space="preserve">Mix medicine, poison, and grave-dust into Faithless Aboration. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% spell damage per level, reaching 150% at level 100; it also adds 2.5% healing per level, reaching 250% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Graverobbing Shadows of Pain</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal damage equal to 2500 + 2.5% of your damage, growing by a total of +2500 at level 100</t>
+    <t xml:space="preserve">Mix medicine, poison, and grave-dust into Graverobbing Shadows of Pain. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 2,500 specialty damage when using an attack, gains 25 damage per level, and reaches 5,000 damage at level 100, adding 2.5% of your damage stat.</t>
   </si>
   <si>
     <t xml:space="preserve">Necroctic Emotional Drift</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 8,000 damage + 6% of your damage stat as damage with a bonus of +8,000 damage at level 100. You will also grow your damage modifier by +200% at level 100.</t>
+    <t xml:space="preserve">Mix medicine, poison, and grave-dust into Necroctic Emotional Drift. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 8,000 specialty damage when attacking and casting, gains 80 damage per level, and reaches 16,000 damage at level 100, adding 6% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100.</t>
   </si>
   <si>
     <t xml:space="preserve">The line between life and death</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 20,000 damage while use 20% of yuor damage stat, growing to +20,000 damage at level 100. You will also grow your damage stat by +200% at level 100.</t>
+    <t xml:space="preserve">Mix medicine, poison, and grave-dust into The line between life and death. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 20,000 specialty damage when casting and attacking, gains 200 damage per level, and reaches 40,000 damage at level 100, adding 20% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1006,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1030,20 +1030,33 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal" xfId="20"/>
   </cellStyles>
 </styleSheet>
 </file>
@@ -1231,91 +1244,91 @@
   <dimension ref="A1:T144"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="41.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="136.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="42.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="48.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="25.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="24.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="26.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="21.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="18.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="24.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="41.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="136.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="42.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="48.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="25.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="30.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="24.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="26.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="24.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
@@ -1325,20 +1338,33 @@
       <c r="C2" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
+      <c r="I2" s="0"/>
+      <c r="J2" s="0"/>
+      <c r="K2" s="0"/>
+      <c r="L2" s="0"/>
+      <c r="M2" s="0"/>
       <c r="N2" s="0" t="n">
-        <v>0.05</v>
+        <v>0.025</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P2" s="0"/>
+      <c r="Q2" s="0"/>
+      <c r="R2" s="0"/>
+      <c r="S2" s="0"/>
+      <c r="T2" s="0"/>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
@@ -1348,20 +1374,33 @@
       <c r="C3" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
       <c r="I3" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J3" s="0"/>
+      <c r="K3" s="0"/>
+      <c r="L3" s="0"/>
+      <c r="M3" s="0"/>
+      <c r="N3" s="0"/>
       <c r="O3" s="0" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P3" s="0"/>
+      <c r="Q3" s="0"/>
+      <c r="R3" s="0"/>
+      <c r="S3" s="0"/>
+      <c r="T3" s="0"/>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
@@ -1371,20 +1410,33 @@
       <c r="C4" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+      <c r="I4" s="0"/>
       <c r="J4" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="K4" s="0"/>
+      <c r="L4" s="0"/>
+      <c r="M4" s="0"/>
+      <c r="N4" s="0"/>
       <c r="O4" s="0" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P4" s="0"/>
+      <c r="Q4" s="0"/>
+      <c r="R4" s="0"/>
+      <c r="S4" s="0"/>
+      <c r="T4" s="0"/>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
@@ -1394,20 +1446,33 @@
       <c r="C5" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>36</v>
       </c>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+      <c r="I5" s="0"/>
+      <c r="J5" s="0"/>
+      <c r="K5" s="0"/>
       <c r="L5" s="0" t="n">
-        <v>0.05</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="M5" s="0"/>
+      <c r="N5" s="0"/>
       <c r="O5" s="0" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P5" s="0"/>
+      <c r="Q5" s="0"/>
+      <c r="R5" s="0"/>
+      <c r="S5" s="0"/>
+      <c r="T5" s="0"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
@@ -1417,20 +1482,33 @@
       <c r="C6" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>48</v>
       </c>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
+      <c r="I6" s="0"/>
+      <c r="J6" s="0"/>
+      <c r="K6" s="0"/>
+      <c r="L6" s="0"/>
       <c r="M6" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="N6" s="0"/>
       <c r="O6" s="0" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P6" s="0"/>
+      <c r="Q6" s="0"/>
+      <c r="R6" s="0"/>
+      <c r="S6" s="0"/>
+      <c r="T6" s="0"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
@@ -1440,20 +1518,33 @@
       <c r="C7" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>60</v>
       </c>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+      <c r="I7" s="0"/>
+      <c r="J7" s="0"/>
+      <c r="K7" s="0"/>
+      <c r="L7" s="0"/>
+      <c r="M7" s="0"/>
       <c r="N7" s="0" t="n">
         <v>0.025</v>
       </c>
       <c r="O7" s="0" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P7" s="0"/>
+      <c r="Q7" s="0"/>
+      <c r="R7" s="0"/>
+      <c r="S7" s="0"/>
+      <c r="T7" s="0"/>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
@@ -1463,7 +1554,7 @@
       <c r="C8" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="0" t="n">
@@ -1478,11 +1569,22 @@
       <c r="H8" s="0" t="n">
         <v>0.05</v>
       </c>
+      <c r="I8" s="0"/>
+      <c r="J8" s="0"/>
+      <c r="K8" s="0"/>
+      <c r="L8" s="0"/>
+      <c r="M8" s="0"/>
+      <c r="N8" s="0"/>
       <c r="O8" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P8" s="0"/>
+      <c r="Q8" s="0"/>
+      <c r="R8" s="0"/>
+      <c r="S8" s="0"/>
+      <c r="T8" s="0"/>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
@@ -1492,7 +1594,7 @@
       <c r="C9" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E9" s="0" t="n">
@@ -1505,13 +1607,24 @@
         <v>100</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.15</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="0"/>
+      <c r="J9" s="0"/>
+      <c r="K9" s="0"/>
+      <c r="L9" s="0"/>
+      <c r="M9" s="0"/>
+      <c r="N9" s="0"/>
       <c r="O9" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P9" s="0"/>
+      <c r="Q9" s="0"/>
+      <c r="R9" s="0"/>
+      <c r="S9" s="0"/>
+      <c r="T9" s="0"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
@@ -1521,7 +1634,7 @@
       <c r="C10" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E10" s="0" t="n">
@@ -1536,11 +1649,22 @@
       <c r="H10" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="I10" s="0"/>
+      <c r="J10" s="0"/>
+      <c r="K10" s="0"/>
+      <c r="L10" s="0"/>
+      <c r="M10" s="0"/>
+      <c r="N10" s="0"/>
       <c r="O10" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P10" s="0"/>
+      <c r="Q10" s="0"/>
+      <c r="R10" s="0"/>
+      <c r="S10" s="0"/>
+      <c r="T10" s="0"/>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
@@ -1550,7 +1674,7 @@
       <c r="C11" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="0" t="n">
@@ -1560,19 +1684,29 @@
         <v>1000</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="H11" s="0" t="n">
         <v>0.15</v>
       </c>
+      <c r="I11" s="0"/>
       <c r="J11" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
+      <c r="N11" s="0"/>
       <c r="O11" s="0" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P11" s="0"/>
+      <c r="Q11" s="0"/>
+      <c r="R11" s="0"/>
+      <c r="S11" s="0"/>
+      <c r="T11" s="0"/>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
@@ -1582,20 +1716,33 @@
       <c r="C12" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E12" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
       <c r="I12" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="J12" s="0"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
       <c r="N12" s="0" t="n">
         <v>0.015</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O12" s="0"/>
+      <c r="P12" s="0"/>
+      <c r="Q12" s="0"/>
+      <c r="R12" s="0"/>
+      <c r="S12" s="0"/>
+      <c r="T12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
@@ -1605,17 +1752,31 @@
       <c r="C13" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+      <c r="I13" s="0"/>
       <c r="J13" s="0" t="n">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K13" s="0"/>
+      <c r="L13" s="0"/>
+      <c r="M13" s="0"/>
+      <c r="N13" s="0"/>
+      <c r="O13" s="0"/>
+      <c r="P13" s="0"/>
+      <c r="Q13" s="0"/>
+      <c r="R13" s="0"/>
+      <c r="S13" s="0"/>
+      <c r="T13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
@@ -1625,17 +1786,31 @@
       <c r="C14" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E14" s="0" t="n">
         <v>36</v>
       </c>
+      <c r="F14" s="0"/>
+      <c r="G14" s="0"/>
+      <c r="H14" s="0"/>
+      <c r="I14" s="0"/>
+      <c r="J14" s="0"/>
       <c r="K14" s="0" t="n">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L14" s="0"/>
+      <c r="M14" s="0"/>
+      <c r="N14" s="0"/>
+      <c r="O14" s="0"/>
+      <c r="P14" s="0"/>
+      <c r="Q14" s="0"/>
+      <c r="R14" s="0"/>
+      <c r="S14" s="0"/>
+      <c r="T14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
@@ -1645,17 +1820,31 @@
       <c r="C15" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="2" t="s">
         <v>50</v>
       </c>
       <c r="E15" s="0" t="n">
         <v>48</v>
       </c>
+      <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
+      <c r="I15" s="0"/>
+      <c r="J15" s="0"/>
+      <c r="K15" s="0"/>
       <c r="L15" s="0" t="n">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M15" s="0"/>
+      <c r="N15" s="0"/>
+      <c r="O15" s="0"/>
+      <c r="P15" s="0"/>
+      <c r="Q15" s="0"/>
+      <c r="R15" s="0"/>
+      <c r="S15" s="0"/>
+      <c r="T15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
@@ -1665,17 +1854,31 @@
       <c r="C16" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E16" s="0" t="n">
         <v>60</v>
       </c>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+      <c r="I16" s="0"/>
+      <c r="J16" s="0"/>
+      <c r="K16" s="0"/>
+      <c r="L16" s="0"/>
       <c r="M16" s="0" t="n">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N16" s="0"/>
+      <c r="O16" s="0"/>
+      <c r="P16" s="0"/>
+      <c r="Q16" s="0"/>
+      <c r="R16" s="0"/>
+      <c r="S16" s="0"/>
+      <c r="T16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
@@ -1685,7 +1888,7 @@
       <c r="C17" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E17" s="0" t="n">
@@ -1700,11 +1903,22 @@
       <c r="H17" s="0" t="n">
         <v>0.15</v>
       </c>
+      <c r="I17" s="0"/>
+      <c r="J17" s="0"/>
+      <c r="K17" s="0"/>
+      <c r="L17" s="0"/>
+      <c r="M17" s="0"/>
+      <c r="N17" s="0"/>
       <c r="O17" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P17" s="0"/>
+      <c r="Q17" s="0"/>
+      <c r="R17" s="0"/>
+      <c r="S17" s="0"/>
+      <c r="T17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
@@ -1714,7 +1928,7 @@
       <c r="C18" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E18" s="0" t="n">
@@ -1729,11 +1943,22 @@
       <c r="H18" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="I18" s="0"/>
+      <c r="J18" s="0"/>
+      <c r="K18" s="0"/>
+      <c r="L18" s="0"/>
+      <c r="M18" s="0"/>
+      <c r="N18" s="0"/>
       <c r="O18" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P18" s="0"/>
+      <c r="Q18" s="0"/>
+      <c r="R18" s="0"/>
+      <c r="S18" s="0"/>
+      <c r="T18" s="0"/>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
@@ -1743,7 +1968,7 @@
       <c r="C19" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E19" s="0" t="n">
@@ -1758,14 +1983,24 @@
       <c r="H19" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="I19" s="0"/>
+      <c r="J19" s="0"/>
+      <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="M19" s="0"/>
+      <c r="N19" s="0"/>
       <c r="O19" s="0" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P19" s="0"/>
+      <c r="Q19" s="0"/>
+      <c r="R19" s="0"/>
+      <c r="S19" s="0"/>
+      <c r="T19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
@@ -1775,17 +2010,31 @@
       <c r="C20" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E20" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F20" s="0"/>
+      <c r="G20" s="0"/>
+      <c r="H20" s="0"/>
+      <c r="I20" s="0"/>
+      <c r="J20" s="0"/>
+      <c r="K20" s="0"/>
+      <c r="L20" s="0"/>
       <c r="M20" s="0" t="n">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N20" s="0"/>
+      <c r="O20" s="0"/>
+      <c r="P20" s="0"/>
+      <c r="Q20" s="0"/>
+      <c r="R20" s="0"/>
+      <c r="S20" s="0"/>
+      <c r="T20" s="0"/>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="n">
         <v>20</v>
       </c>
@@ -1795,17 +2044,31 @@
       <c r="C21" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E21" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F21" s="0"/>
+      <c r="G21" s="0"/>
+      <c r="H21" s="0"/>
+      <c r="I21" s="0"/>
+      <c r="J21" s="0"/>
+      <c r="K21" s="0"/>
+      <c r="L21" s="0"/>
+      <c r="M21" s="0"/>
       <c r="N21" s="0" t="n">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O21" s="0"/>
+      <c r="P21" s="0"/>
+      <c r="Q21" s="0"/>
+      <c r="R21" s="0"/>
+      <c r="S21" s="0"/>
+      <c r="T21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="n">
         <v>21</v>
       </c>
@@ -1815,23 +2078,35 @@
       <c r="C22" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E22" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F22" s="0"/>
+      <c r="G22" s="0"/>
+      <c r="H22" s="0"/>
       <c r="I22" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J22" s="0"/>
+      <c r="K22" s="0"/>
       <c r="L22" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="M22" s="0" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.025</v>
+      </c>
+      <c r="N22" s="0"/>
+      <c r="O22" s="0"/>
+      <c r="P22" s="0"/>
+      <c r="Q22" s="0"/>
+      <c r="R22" s="0"/>
+      <c r="S22" s="0"/>
+      <c r="T22" s="0"/>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="n">
         <v>22</v>
       </c>
@@ -1841,23 +2116,35 @@
       <c r="C23" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="2" t="s">
         <v>68</v>
       </c>
       <c r="E23" s="0" t="n">
         <v>36</v>
       </c>
+      <c r="F23" s="0"/>
+      <c r="G23" s="0"/>
+      <c r="H23" s="0"/>
+      <c r="I23" s="0"/>
+      <c r="J23" s="0"/>
       <c r="K23" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="L23" s="0"/>
       <c r="M23" s="0" t="n">
         <v>0.02</v>
       </c>
       <c r="N23" s="0" t="n">
         <v>0.015</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O23" s="0"/>
+      <c r="P23" s="0"/>
+      <c r="Q23" s="0"/>
+      <c r="R23" s="0"/>
+      <c r="S23" s="0"/>
+      <c r="T23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="n">
         <v>23</v>
       </c>
@@ -1867,20 +2154,33 @@
       <c r="C24" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="E24" s="0" t="n">
         <v>48</v>
       </c>
+      <c r="F24" s="0"/>
+      <c r="G24" s="0"/>
+      <c r="H24" s="0"/>
       <c r="I24" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J24" s="0"/>
+      <c r="K24" s="0"/>
+      <c r="L24" s="0"/>
+      <c r="M24" s="0"/>
       <c r="N24" s="0" t="n">
         <v>0.015</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O24" s="0"/>
+      <c r="P24" s="0"/>
+      <c r="Q24" s="0"/>
+      <c r="R24" s="0"/>
+      <c r="S24" s="0"/>
+      <c r="T24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="n">
         <v>24</v>
       </c>
@@ -1890,20 +2190,33 @@
       <c r="C25" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E25" s="0" t="n">
         <v>60</v>
       </c>
+      <c r="F25" s="0"/>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
+      <c r="I25" s="0"/>
       <c r="J25" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="K25" s="0"/>
+      <c r="L25" s="0"/>
       <c r="M25" s="0" t="n">
         <v>0.025</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N25" s="0"/>
+      <c r="O25" s="0"/>
+      <c r="P25" s="0"/>
+      <c r="Q25" s="0"/>
+      <c r="R25" s="0"/>
+      <c r="S25" s="0"/>
+      <c r="T25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="n">
         <v>25</v>
       </c>
@@ -1913,7 +2226,7 @@
       <c r="C26" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E26" s="0" t="n">
@@ -1926,13 +2239,24 @@
         <v>50</v>
       </c>
       <c r="H26" s="0" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="I26" s="0"/>
+      <c r="J26" s="0"/>
+      <c r="K26" s="0"/>
+      <c r="L26" s="0"/>
+      <c r="M26" s="0"/>
+      <c r="N26" s="0"/>
       <c r="O26" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P26" s="0"/>
+      <c r="Q26" s="0"/>
+      <c r="R26" s="0"/>
+      <c r="S26" s="0"/>
+      <c r="T26" s="0"/>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="n">
         <v>26</v>
       </c>
@@ -1942,7 +2266,7 @@
       <c r="C27" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E27" s="0" t="n">
@@ -1952,22 +2276,31 @@
         <v>15000</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="H27" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="I27" s="0"/>
       <c r="J27" s="0" t="n">
         <v>0.025</v>
       </c>
+      <c r="K27" s="0"/>
+      <c r="L27" s="0"/>
       <c r="M27" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="N27" s="0"/>
       <c r="O27" s="0" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P27" s="0"/>
+      <c r="Q27" s="0"/>
+      <c r="R27" s="0"/>
+      <c r="S27" s="0"/>
+      <c r="T27" s="0"/>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="n">
         <v>27</v>
       </c>
@@ -1977,7 +2310,7 @@
       <c r="C28" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="2" t="s">
         <v>78</v>
       </c>
       <c r="E28" s="0" t="n">
@@ -1990,16 +2323,26 @@
         <v>500</v>
       </c>
       <c r="H28" s="0" t="n">
-        <v>0.3</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I28" s="0"/>
       <c r="J28" s="0" t="n">
         <v>0.05</v>
       </c>
+      <c r="K28" s="0"/>
+      <c r="L28" s="0"/>
+      <c r="M28" s="0"/>
+      <c r="N28" s="0"/>
       <c r="O28" s="0" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P28" s="0"/>
+      <c r="Q28" s="0"/>
+      <c r="R28" s="0"/>
+      <c r="S28" s="0"/>
+      <c r="T28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="n">
         <v>28</v>
       </c>
@@ -2009,20 +2352,33 @@
       <c r="C29" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E29" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F29" s="0"/>
+      <c r="G29" s="0"/>
+      <c r="H29" s="0"/>
       <c r="I29" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="J29" s="0"/>
+      <c r="K29" s="0"/>
+      <c r="L29" s="0"/>
       <c r="M29" s="0" t="n">
         <v>0.015</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N29" s="0"/>
+      <c r="O29" s="0"/>
+      <c r="P29" s="0"/>
+      <c r="Q29" s="0"/>
+      <c r="R29" s="0"/>
+      <c r="S29" s="0"/>
+      <c r="T29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="n">
         <v>29</v>
       </c>
@@ -2032,7 +2388,7 @@
       <c r="C30" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E30" s="0" t="n">
@@ -2047,14 +2403,24 @@
       <c r="H30" s="0" t="n">
         <v>0.15</v>
       </c>
+      <c r="I30" s="0"/>
       <c r="J30" s="0" t="n">
         <v>0.003</v>
       </c>
+      <c r="K30" s="0"/>
+      <c r="L30" s="0"/>
+      <c r="M30" s="0"/>
+      <c r="N30" s="0"/>
       <c r="O30" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P30" s="0"/>
+      <c r="Q30" s="0"/>
+      <c r="R30" s="0"/>
+      <c r="S30" s="0"/>
+      <c r="T30" s="0"/>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="n">
         <v>30</v>
       </c>
@@ -2064,23 +2430,35 @@
       <c r="C31" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="2" t="s">
         <v>84</v>
       </c>
       <c r="E31" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F31" s="0"/>
+      <c r="G31" s="0"/>
+      <c r="H31" s="0"/>
       <c r="I31" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J31" s="0"/>
       <c r="K31" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="L31" s="0"/>
+      <c r="M31" s="0"/>
       <c r="N31" s="0" t="n">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O31" s="0"/>
+      <c r="P31" s="0"/>
+      <c r="Q31" s="0"/>
+      <c r="R31" s="0"/>
+      <c r="S31" s="0"/>
+      <c r="T31" s="0"/>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="n">
         <v>31</v>
       </c>
@@ -2090,20 +2468,33 @@
       <c r="C32" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E32" s="0" t="n">
         <v>36</v>
       </c>
+      <c r="F32" s="0"/>
+      <c r="G32" s="0"/>
+      <c r="H32" s="0"/>
+      <c r="I32" s="0"/>
+      <c r="J32" s="0"/>
       <c r="K32" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="L32" s="0"/>
       <c r="M32" s="0" t="n">
         <v>0.015</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N32" s="0"/>
+      <c r="O32" s="0"/>
+      <c r="P32" s="0"/>
+      <c r="Q32" s="0"/>
+      <c r="R32" s="0"/>
+      <c r="S32" s="0"/>
+      <c r="T32" s="0"/>
+    </row>
+    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="n">
         <v>32</v>
       </c>
@@ -2113,12 +2504,15 @@
       <c r="C33" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E33" s="0" t="n">
         <v>48</v>
       </c>
+      <c r="F33" s="0"/>
+      <c r="G33" s="0"/>
+      <c r="H33" s="0"/>
       <c r="I33" s="0" t="n">
         <v>0.01</v>
       </c>
@@ -2128,14 +2522,21 @@
       <c r="K33" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="L33" s="0"/>
       <c r="M33" s="0" t="n">
         <v>0.01</v>
       </c>
       <c r="N33" s="0" t="n">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O33" s="0"/>
+      <c r="P33" s="0"/>
+      <c r="Q33" s="0"/>
+      <c r="R33" s="0"/>
+      <c r="S33" s="0"/>
+      <c r="T33" s="0"/>
+    </row>
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="n">
         <v>33</v>
       </c>
@@ -2145,7 +2546,7 @@
       <c r="C34" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E34" s="0" t="n">
@@ -2158,19 +2559,28 @@
         <v>100</v>
       </c>
       <c r="H34" s="0" t="n">
-        <v>0.3</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I34" s="0"/>
+      <c r="J34" s="0"/>
       <c r="K34" s="0" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="L34" s="0"/>
+      <c r="M34" s="0"/>
       <c r="N34" s="0" t="n">
         <v>0.02</v>
       </c>
       <c r="O34" s="0" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P34" s="0"/>
+      <c r="Q34" s="0"/>
+      <c r="R34" s="0"/>
+      <c r="S34" s="0"/>
+      <c r="T34" s="0"/>
+    </row>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="n">
         <v>34</v>
       </c>
@@ -2180,7 +2590,7 @@
       <c r="C35" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E35" s="0" t="n">
@@ -2198,11 +2608,21 @@
       <c r="I35" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="J35" s="0"/>
+      <c r="K35" s="0"/>
+      <c r="L35" s="0"/>
+      <c r="M35" s="0"/>
+      <c r="N35" s="0"/>
       <c r="O35" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P35" s="0"/>
+      <c r="Q35" s="0"/>
+      <c r="R35" s="0"/>
+      <c r="S35" s="0"/>
+      <c r="T35" s="0"/>
+    </row>
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="n">
         <v>35</v>
       </c>
@@ -2212,7 +2632,7 @@
       <c r="C36" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="2" t="s">
         <v>95</v>
       </c>
       <c r="E36" s="0" t="n">
@@ -2227,14 +2647,24 @@
       <c r="H36" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="I36" s="0"/>
+      <c r="J36" s="0"/>
+      <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
         <v>0.005</v>
       </c>
+      <c r="M36" s="0"/>
+      <c r="N36" s="0"/>
       <c r="O36" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P36" s="0"/>
+      <c r="Q36" s="0"/>
+      <c r="R36" s="0"/>
+      <c r="S36" s="0"/>
+      <c r="T36" s="0"/>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="n">
         <v>36</v>
       </c>
@@ -2244,7 +2674,7 @@
       <c r="C37" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="2" t="s">
         <v>97</v>
       </c>
       <c r="E37" s="0" t="n">
@@ -2259,17 +2689,26 @@
       <c r="H37" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="I37" s="0"/>
       <c r="J37" s="0" t="n">
         <v>0.01</v>
       </c>
       <c r="K37" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="L37" s="0"/>
+      <c r="M37" s="0"/>
+      <c r="N37" s="0"/>
       <c r="O37" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P37" s="0"/>
+      <c r="Q37" s="0"/>
+      <c r="R37" s="0"/>
+      <c r="S37" s="0"/>
+      <c r="T37" s="0"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="n">
         <v>37</v>
       </c>
@@ -2279,17 +2718,31 @@
       <c r="C38" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="2" t="s">
         <v>99</v>
       </c>
       <c r="E38" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F38" s="0"/>
+      <c r="G38" s="0"/>
+      <c r="H38" s="0"/>
+      <c r="I38" s="0"/>
+      <c r="J38" s="0"/>
       <c r="K38" s="0" t="n">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L38" s="0"/>
+      <c r="M38" s="0"/>
+      <c r="N38" s="0"/>
+      <c r="O38" s="0"/>
+      <c r="P38" s="0"/>
+      <c r="Q38" s="0"/>
+      <c r="R38" s="0"/>
+      <c r="S38" s="0"/>
+      <c r="T38" s="0"/>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="n">
         <v>38</v>
       </c>
@@ -2299,23 +2752,35 @@
       <c r="C39" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="2" t="s">
         <v>101</v>
       </c>
       <c r="E39" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F39" s="0"/>
+      <c r="G39" s="0"/>
+      <c r="H39" s="0"/>
+      <c r="I39" s="0"/>
       <c r="J39" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="K39" s="0" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="L39" s="0" t="n">
         <v>0.005</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M39" s="0"/>
+      <c r="N39" s="0"/>
+      <c r="O39" s="0"/>
+      <c r="P39" s="0"/>
+      <c r="Q39" s="0"/>
+      <c r="R39" s="0"/>
+      <c r="S39" s="0"/>
+      <c r="T39" s="0"/>
+    </row>
+    <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="n">
         <v>39</v>
       </c>
@@ -2325,7 +2790,7 @@
       <c r="C40" s="0" t="s">
         <v>102</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="2" t="s">
         <v>103</v>
       </c>
       <c r="E40" s="0" t="n">
@@ -2340,14 +2805,24 @@
       <c r="H40" s="0" t="n">
         <v>0.15</v>
       </c>
+      <c r="I40" s="0"/>
+      <c r="J40" s="0"/>
+      <c r="K40" s="0"/>
+      <c r="L40" s="0"/>
+      <c r="M40" s="0"/>
       <c r="N40" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="O40" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P40" s="0"/>
+      <c r="Q40" s="0"/>
+      <c r="R40" s="0"/>
+      <c r="S40" s="0"/>
+      <c r="T40" s="0"/>
+    </row>
+    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="n">
         <v>40</v>
       </c>
@@ -2357,12 +2832,15 @@
       <c r="C41" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="2" t="s">
         <v>105</v>
       </c>
       <c r="E41" s="0" t="n">
         <v>36</v>
       </c>
+      <c r="F41" s="0"/>
+      <c r="G41" s="0"/>
+      <c r="H41" s="0"/>
       <c r="I41" s="0" t="n">
         <v>0.01</v>
       </c>
@@ -2370,16 +2848,23 @@
         <v>0.01</v>
       </c>
       <c r="K41" s="0" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="L41" s="0"/>
       <c r="M41" s="0" t="n">
         <v>0.025</v>
       </c>
       <c r="N41" s="0" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.02</v>
+      </c>
+      <c r="O41" s="0"/>
+      <c r="P41" s="0"/>
+      <c r="Q41" s="0"/>
+      <c r="R41" s="0"/>
+      <c r="S41" s="0"/>
+      <c r="T41" s="0"/>
+    </row>
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="n">
         <v>41</v>
       </c>
@@ -2389,7 +2874,7 @@
       <c r="C42" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="2" t="s">
         <v>107</v>
       </c>
       <c r="E42" s="0" t="n">
@@ -2404,14 +2889,24 @@
       <c r="H42" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="I42" s="0"/>
+      <c r="J42" s="0"/>
+      <c r="K42" s="0"/>
+      <c r="L42" s="0"/>
+      <c r="M42" s="0"/>
       <c r="N42" s="0" t="n">
         <v>0.02</v>
       </c>
       <c r="O42" s="0" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P42" s="0"/>
+      <c r="Q42" s="0"/>
+      <c r="R42" s="0"/>
+      <c r="S42" s="0"/>
+      <c r="T42" s="0"/>
+    </row>
+    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="n">
         <v>42</v>
       </c>
@@ -2421,7 +2916,7 @@
       <c r="C43" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="2" t="s">
         <v>109</v>
       </c>
       <c r="E43" s="0" t="n">
@@ -2439,14 +2934,23 @@
       <c r="I43" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="J43" s="0"/>
+      <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="M43" s="0"/>
+      <c r="N43" s="0"/>
       <c r="O43" s="0" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P43" s="0"/>
+      <c r="Q43" s="0"/>
+      <c r="R43" s="0"/>
+      <c r="S43" s="0"/>
+      <c r="T43" s="0"/>
+    </row>
+    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="n">
         <v>43</v>
       </c>
@@ -2456,7 +2960,7 @@
       <c r="C44" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="E44" s="0" t="n">
@@ -2471,14 +2975,24 @@
       <c r="H44" s="0" t="n">
         <v>0.22</v>
       </c>
+      <c r="I44" s="0"/>
+      <c r="J44" s="0"/>
       <c r="K44" s="0" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="L44" s="0"/>
+      <c r="M44" s="0"/>
+      <c r="N44" s="0"/>
       <c r="O44" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P44" s="0"/>
+      <c r="Q44" s="0"/>
+      <c r="R44" s="0"/>
+      <c r="S44" s="0"/>
+      <c r="T44" s="0"/>
+    </row>
+    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="n">
         <v>44</v>
       </c>
@@ -2488,7 +3002,7 @@
       <c r="C45" s="0" t="s">
         <v>112</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="2" t="s">
         <v>113</v>
       </c>
       <c r="E45" s="0" t="n">
@@ -2501,19 +3015,28 @@
         <v>500</v>
       </c>
       <c r="H45" s="0" t="n">
-        <v>0.3</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I45" s="0"/>
+      <c r="J45" s="0"/>
       <c r="K45" s="0" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="L45" s="0"/>
+      <c r="M45" s="0"/>
       <c r="N45" s="0" t="n">
         <v>0.02</v>
       </c>
       <c r="O45" s="0" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P45" s="0"/>
+      <c r="Q45" s="0"/>
+      <c r="R45" s="0"/>
+      <c r="S45" s="0"/>
+      <c r="T45" s="0"/>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="n">
         <v>45</v>
       </c>
@@ -2523,7 +3046,7 @@
       <c r="C46" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="2" t="s">
         <v>115</v>
       </c>
       <c r="E46" s="0" t="n">
@@ -2538,11 +3061,22 @@
       <c r="H46" s="0" t="n">
         <v>0.3</v>
       </c>
+      <c r="I46" s="0"/>
+      <c r="J46" s="0"/>
+      <c r="K46" s="0"/>
+      <c r="L46" s="0"/>
+      <c r="M46" s="0"/>
+      <c r="N46" s="0"/>
       <c r="O46" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P46" s="0"/>
+      <c r="Q46" s="0"/>
+      <c r="R46" s="0"/>
+      <c r="S46" s="0"/>
+      <c r="T46" s="0"/>
+    </row>
+    <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="n">
         <v>46</v>
       </c>
@@ -2552,7 +3086,7 @@
       <c r="C47" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="2" t="s">
         <v>117</v>
       </c>
       <c r="E47" s="0" t="n">
@@ -2570,14 +3104,23 @@
       <c r="I47" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="J47" s="0"/>
+      <c r="K47" s="0"/>
+      <c r="L47" s="0"/>
+      <c r="M47" s="0"/>
       <c r="N47" s="0" t="n">
         <v>0.01</v>
       </c>
       <c r="O47" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P47" s="0"/>
+      <c r="Q47" s="0"/>
+      <c r="R47" s="0"/>
+      <c r="S47" s="0"/>
+      <c r="T47" s="0"/>
+    </row>
+    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="n">
         <v>47</v>
       </c>
@@ -2587,7 +3130,7 @@
       <c r="C48" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="2" t="s">
         <v>119</v>
       </c>
       <c r="E48" s="0" t="n">
@@ -2602,17 +3145,26 @@
       <c r="H48" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="I48" s="0"/>
+      <c r="J48" s="0"/>
+      <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
         <v>0.005</v>
       </c>
+      <c r="M48" s="0"/>
       <c r="N48" s="0" t="n">
         <v>0.01</v>
       </c>
       <c r="O48" s="0" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P48" s="0"/>
+      <c r="Q48" s="0"/>
+      <c r="R48" s="0"/>
+      <c r="S48" s="0"/>
+      <c r="T48" s="0"/>
+    </row>
+    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="n">
         <v>48</v>
       </c>
@@ -2622,23 +3174,35 @@
       <c r="C49" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" s="2" t="s">
         <v>121</v>
       </c>
       <c r="E49" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F49" s="0"/>
+      <c r="G49" s="0"/>
+      <c r="H49" s="0"/>
       <c r="I49" s="0" t="n">
-        <v>0.025</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="J49" s="0"/>
+      <c r="K49" s="0"/>
+      <c r="L49" s="0"/>
       <c r="M49" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="N49" s="0" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.02</v>
+      </c>
+      <c r="O49" s="0"/>
+      <c r="P49" s="0"/>
+      <c r="Q49" s="0"/>
+      <c r="R49" s="0"/>
+      <c r="S49" s="0"/>
+      <c r="T49" s="0"/>
+    </row>
+    <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="n">
         <v>49</v>
       </c>
@@ -2648,7 +3212,7 @@
       <c r="C50" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="D50" s="2" t="s">
         <v>123</v>
       </c>
       <c r="E50" s="0" t="n">
@@ -2666,11 +3230,21 @@
       <c r="I50" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J50" s="0"/>
+      <c r="K50" s="0"/>
+      <c r="L50" s="0"/>
+      <c r="M50" s="0"/>
+      <c r="N50" s="0"/>
       <c r="O50" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P50" s="0"/>
+      <c r="Q50" s="0"/>
+      <c r="R50" s="0"/>
+      <c r="S50" s="0"/>
+      <c r="T50" s="0"/>
+    </row>
+    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="n">
         <v>50</v>
       </c>
@@ -2680,26 +3254,37 @@
       <c r="C51" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="D51" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E51" s="0" t="n">
         <v>48</v>
       </c>
+      <c r="F51" s="0"/>
+      <c r="G51" s="0"/>
+      <c r="H51" s="0"/>
       <c r="I51" s="0" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="J51" s="0" t="n">
         <v>0.005</v>
       </c>
+      <c r="K51" s="0"/>
+      <c r="L51" s="0"/>
       <c r="M51" s="0" t="n">
         <v>0.01</v>
       </c>
       <c r="N51" s="0" t="n">
         <v>0.012</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O51" s="0"/>
+      <c r="P51" s="0"/>
+      <c r="Q51" s="0"/>
+      <c r="R51" s="0"/>
+      <c r="S51" s="0"/>
+      <c r="T51" s="0"/>
+    </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="n">
         <v>51</v>
       </c>
@@ -2709,7 +3294,7 @@
       <c r="C52" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="D52" s="0" t="s">
+      <c r="D52" s="2" t="s">
         <v>127</v>
       </c>
       <c r="E52" s="0" t="n">
@@ -2724,11 +3309,22 @@
       <c r="H52" s="0" t="n">
         <v>0.18</v>
       </c>
+      <c r="I52" s="0"/>
+      <c r="J52" s="0"/>
+      <c r="K52" s="0"/>
+      <c r="L52" s="0"/>
+      <c r="M52" s="0"/>
+      <c r="N52" s="0"/>
       <c r="O52" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P52" s="0"/>
+      <c r="Q52" s="0"/>
+      <c r="R52" s="0"/>
+      <c r="S52" s="0"/>
+      <c r="T52" s="0"/>
+    </row>
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="n">
         <v>52</v>
       </c>
@@ -2738,7 +3334,7 @@
       <c r="C53" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="D53" s="0" t="s">
+      <c r="D53" s="2" t="s">
         <v>129</v>
       </c>
       <c r="E53" s="0" t="n">
@@ -2753,14 +3349,24 @@
       <c r="H53" s="0" t="n">
         <v>0.22</v>
       </c>
+      <c r="I53" s="0"/>
+      <c r="J53" s="0"/>
+      <c r="K53" s="0"/>
+      <c r="L53" s="0"/>
+      <c r="M53" s="0"/>
       <c r="N53" s="0" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="O53" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P53" s="0"/>
+      <c r="Q53" s="0"/>
+      <c r="R53" s="0"/>
+      <c r="S53" s="0"/>
+      <c r="T53" s="0"/>
+    </row>
+    <row r="54" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="n">
         <v>53</v>
       </c>
@@ -2770,7 +3376,7 @@
       <c r="C54" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="D54" s="0" t="s">
+      <c r="D54" s="2" t="s">
         <v>131</v>
       </c>
       <c r="E54" s="0" t="n">
@@ -2788,6 +3394,9 @@
       <c r="I54" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="J54" s="0"/>
+      <c r="K54" s="0"/>
+      <c r="L54" s="0"/>
       <c r="M54" s="0" t="n">
         <v>0.01</v>
       </c>
@@ -2797,8 +3406,13 @@
       <c r="O54" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P54" s="0"/>
+      <c r="Q54" s="0"/>
+      <c r="R54" s="0"/>
+      <c r="S54" s="0"/>
+      <c r="T54" s="0"/>
+    </row>
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="n">
         <v>54</v>
       </c>
@@ -2808,7 +3422,7 @@
       <c r="C55" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="D55" s="2" t="s">
         <v>133</v>
       </c>
       <c r="E55" s="0" t="n">
@@ -2821,16 +3435,26 @@
         <v>500</v>
       </c>
       <c r="H55" s="0" t="n">
-        <v>0.26</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I55" s="0"/>
+      <c r="J55" s="0"/>
+      <c r="K55" s="0"/>
+      <c r="L55" s="0"/>
+      <c r="M55" s="0"/>
       <c r="N55" s="0" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="O55" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P55" s="0"/>
+      <c r="Q55" s="0"/>
+      <c r="R55" s="0"/>
+      <c r="S55" s="0"/>
+      <c r="T55" s="0"/>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="n">
         <v>55</v>
       </c>
@@ -2840,17 +3464,31 @@
       <c r="C56" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="D56" s="0" t="s">
+      <c r="D56" s="2" t="s">
         <v>135</v>
       </c>
       <c r="E56" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F56" s="0"/>
+      <c r="G56" s="0"/>
+      <c r="H56" s="0"/>
       <c r="I56" s="0" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.025</v>
+      </c>
+      <c r="J56" s="0"/>
+      <c r="K56" s="0"/>
+      <c r="L56" s="0"/>
+      <c r="M56" s="0"/>
+      <c r="N56" s="0"/>
+      <c r="O56" s="0"/>
+      <c r="P56" s="0"/>
+      <c r="Q56" s="0"/>
+      <c r="R56" s="0"/>
+      <c r="S56" s="0"/>
+      <c r="T56" s="0"/>
+    </row>
+    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="n">
         <v>56</v>
       </c>
@@ -2860,23 +3498,35 @@
       <c r="C57" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="D57" s="0" t="s">
+      <c r="D57" s="2" t="s">
         <v>137</v>
       </c>
       <c r="E57" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F57" s="0"/>
+      <c r="G57" s="0"/>
+      <c r="H57" s="0"/>
+      <c r="I57" s="0"/>
       <c r="J57" s="0" t="n">
         <v>0.025</v>
       </c>
+      <c r="K57" s="0"/>
+      <c r="L57" s="0"/>
       <c r="M57" s="0" t="n">
         <v>0.025</v>
       </c>
       <c r="N57" s="0" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.025</v>
+      </c>
+      <c r="O57" s="0"/>
+      <c r="P57" s="0"/>
+      <c r="Q57" s="0"/>
+      <c r="R57" s="0"/>
+      <c r="S57" s="0"/>
+      <c r="T57" s="0"/>
+    </row>
+    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="n">
         <v>57</v>
       </c>
@@ -2886,7 +3536,7 @@
       <c r="C58" s="0" t="s">
         <v>138</v>
       </c>
-      <c r="D58" s="0" t="s">
+      <c r="D58" s="2" t="s">
         <v>139</v>
       </c>
       <c r="E58" s="0" t="n">
@@ -2902,13 +3552,23 @@
         <v>0.25</v>
       </c>
       <c r="I58" s="0" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="J58" s="0"/>
+      <c r="K58" s="0"/>
+      <c r="L58" s="0"/>
+      <c r="M58" s="0"/>
+      <c r="N58" s="0"/>
       <c r="O58" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P58" s="0"/>
+      <c r="Q58" s="0"/>
+      <c r="R58" s="0"/>
+      <c r="S58" s="0"/>
+      <c r="T58" s="0"/>
+    </row>
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="n">
         <v>58</v>
       </c>
@@ -2918,17 +3578,31 @@
       <c r="C59" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E59" s="0" t="n">
         <v>36</v>
       </c>
+      <c r="F59" s="0"/>
+      <c r="G59" s="0"/>
+      <c r="H59" s="0"/>
+      <c r="I59" s="0"/>
       <c r="J59" s="0" t="n">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K59" s="0"/>
+      <c r="L59" s="0"/>
+      <c r="M59" s="0"/>
+      <c r="N59" s="0"/>
+      <c r="O59" s="0"/>
+      <c r="P59" s="0"/>
+      <c r="Q59" s="0"/>
+      <c r="R59" s="0"/>
+      <c r="S59" s="0"/>
+      <c r="T59" s="0"/>
+    </row>
+    <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="n">
         <v>59</v>
       </c>
@@ -2938,7 +3612,7 @@
       <c r="C60" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="D60" s="0" t="s">
+      <c r="D60" s="2" t="s">
         <v>143</v>
       </c>
       <c r="E60" s="0" t="n">
@@ -2956,17 +3630,25 @@
       <c r="I60" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J60" s="0"/>
+      <c r="K60" s="0"/>
       <c r="L60" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="M60" s="0"/>
       <c r="N60" s="0" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="O60" s="0" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P60" s="0"/>
+      <c r="Q60" s="0"/>
+      <c r="R60" s="0"/>
+      <c r="S60" s="0"/>
+      <c r="T60" s="0"/>
+    </row>
+    <row r="61" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="n">
         <v>60</v>
       </c>
@@ -2976,7 +3658,7 @@
       <c r="C61" s="0" t="s">
         <v>144</v>
       </c>
-      <c r="D61" s="0" t="s">
+      <c r="D61" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E61" s="0" t="n">
@@ -2991,9 +3673,12 @@
       <c r="H61" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="I61" s="0"/>
+      <c r="J61" s="0"/>
       <c r="K61" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="L61" s="0"/>
       <c r="M61" s="0" t="n">
         <v>0.02</v>
       </c>
@@ -3003,8 +3688,13 @@
       <c r="O61" s="0" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P61" s="0"/>
+      <c r="Q61" s="0"/>
+      <c r="R61" s="0"/>
+      <c r="S61" s="0"/>
+      <c r="T61" s="0"/>
+    </row>
+    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="n">
         <v>61</v>
       </c>
@@ -3014,7 +3704,7 @@
       <c r="C62" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="D62" s="0" t="s">
+      <c r="D62" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E62" s="0" t="n">
@@ -3029,14 +3719,24 @@
       <c r="H62" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="I62" s="0"/>
       <c r="J62" s="0" t="n">
         <v>0.04</v>
       </c>
+      <c r="K62" s="0"/>
+      <c r="L62" s="0"/>
+      <c r="M62" s="0"/>
+      <c r="N62" s="0"/>
       <c r="O62" s="0" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P62" s="0"/>
+      <c r="Q62" s="0"/>
+      <c r="R62" s="0"/>
+      <c r="S62" s="0"/>
+      <c r="T62" s="0"/>
+    </row>
+    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="n">
         <v>62</v>
       </c>
@@ -3046,7 +3746,7 @@
       <c r="C63" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="D63" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E63" s="0" t="n">
@@ -3059,16 +3759,26 @@
         <v>600</v>
       </c>
       <c r="H63" s="0" t="n">
-        <v>0.28</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I63" s="0"/>
+      <c r="J63" s="0"/>
+      <c r="K63" s="0"/>
+      <c r="L63" s="0"/>
+      <c r="M63" s="0"/>
       <c r="N63" s="0" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="O63" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P63" s="0"/>
+      <c r="Q63" s="0"/>
+      <c r="R63" s="0"/>
+      <c r="S63" s="0"/>
+      <c r="T63" s="0"/>
+    </row>
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="n">
         <v>63</v>
       </c>
@@ -3078,7 +3788,7 @@
       <c r="C64" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="D64" s="0" t="s">
+      <c r="D64" s="2" t="s">
         <v>151</v>
       </c>
       <c r="E64" s="0" t="n">
@@ -3094,16 +3804,25 @@
         <v>0.1</v>
       </c>
       <c r="I64" s="0" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="J64" s="0"/>
+      <c r="K64" s="0"/>
+      <c r="L64" s="0"/>
+      <c r="M64" s="0"/>
       <c r="N64" s="0" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="O64" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P64" s="0"/>
+      <c r="Q64" s="0"/>
+      <c r="R64" s="0"/>
+      <c r="S64" s="0"/>
+      <c r="T64" s="0"/>
+    </row>
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="n">
         <v>64</v>
       </c>
@@ -3113,23 +3832,35 @@
       <c r="C65" s="0" t="s">
         <v>152</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="D65" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E65" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F65" s="0"/>
+      <c r="G65" s="0"/>
+      <c r="H65" s="0"/>
       <c r="I65" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J65" s="0"/>
+      <c r="K65" s="0"/>
       <c r="L65" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="M65" s="0"/>
       <c r="N65" s="0" t="n">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O65" s="0"/>
+      <c r="P65" s="0"/>
+      <c r="Q65" s="0"/>
+      <c r="R65" s="0"/>
+      <c r="S65" s="0"/>
+      <c r="T65" s="0"/>
+    </row>
+    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="n">
         <v>65</v>
       </c>
@@ -3139,7 +3870,7 @@
       <c r="C66" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="D66" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E66" s="0" t="n">
@@ -3154,17 +3885,26 @@
       <c r="H66" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="I66" s="0"/>
+      <c r="J66" s="0"/>
+      <c r="K66" s="0"/>
       <c r="L66" s="0" t="n">
-        <v>0.025</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="M66" s="0"/>
       <c r="N66" s="0" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="O66" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P66" s="0"/>
+      <c r="Q66" s="0"/>
+      <c r="R66" s="0"/>
+      <c r="S66" s="0"/>
+      <c r="T66" s="0"/>
+    </row>
+    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="n">
         <v>66</v>
       </c>
@@ -3174,12 +3914,16 @@
       <c r="C67" s="0" t="s">
         <v>156</v>
       </c>
-      <c r="D67" s="0" t="s">
+      <c r="D67" s="2" t="s">
         <v>157</v>
       </c>
       <c r="E67" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F67" s="0"/>
+      <c r="G67" s="0"/>
+      <c r="H67" s="0"/>
+      <c r="I67" s="0"/>
       <c r="J67" s="0" t="n">
         <v>0.015</v>
       </c>
@@ -3192,8 +3936,15 @@
       <c r="M67" s="0" t="n">
         <v>0.025</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N67" s="0"/>
+      <c r="O67" s="0"/>
+      <c r="P67" s="0"/>
+      <c r="Q67" s="0"/>
+      <c r="R67" s="0"/>
+      <c r="S67" s="0"/>
+      <c r="T67" s="0"/>
+    </row>
+    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="n">
         <v>67</v>
       </c>
@@ -3203,7 +3954,7 @@
       <c r="C68" s="0" t="s">
         <v>158</v>
       </c>
-      <c r="D68" s="0" t="s">
+      <c r="D68" s="2" t="s">
         <v>159</v>
       </c>
       <c r="E68" s="0" t="n">
@@ -3216,19 +3967,28 @@
         <v>250</v>
       </c>
       <c r="H68" s="0" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I68" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J68" s="0"/>
+      <c r="K68" s="0"/>
       <c r="L68" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="M68" s="0"/>
+      <c r="N68" s="0"/>
       <c r="O68" s="0" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P68" s="0"/>
+      <c r="Q68" s="0"/>
+      <c r="R68" s="0"/>
+      <c r="S68" s="0"/>
+      <c r="T68" s="0"/>
+    </row>
+    <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="n">
         <v>68</v>
       </c>
@@ -3238,7 +3998,7 @@
       <c r="C69" s="0" t="s">
         <v>160</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="D69" s="2" t="s">
         <v>161</v>
       </c>
       <c r="E69" s="0" t="n">
@@ -3251,19 +4011,28 @@
         <v>500</v>
       </c>
       <c r="H69" s="0" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I69" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J69" s="0"/>
+      <c r="K69" s="0"/>
+      <c r="L69" s="0"/>
+      <c r="M69" s="0"/>
       <c r="N69" s="0" t="n">
         <v>0.02</v>
       </c>
       <c r="O69" s="0" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P69" s="0"/>
+      <c r="Q69" s="0"/>
+      <c r="R69" s="0"/>
+      <c r="S69" s="0"/>
+      <c r="T69" s="0"/>
+    </row>
+    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="n">
         <v>69</v>
       </c>
@@ -3273,7 +4042,7 @@
       <c r="C70" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="D70" s="2" t="s">
         <v>163</v>
       </c>
       <c r="E70" s="0" t="n">
@@ -3294,8 +4063,18 @@
       <c r="J70" s="0" t="n">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K70" s="0"/>
+      <c r="L70" s="0"/>
+      <c r="M70" s="0"/>
+      <c r="N70" s="0"/>
+      <c r="O70" s="0"/>
+      <c r="P70" s="0"/>
+      <c r="Q70" s="0"/>
+      <c r="R70" s="0"/>
+      <c r="S70" s="0"/>
+      <c r="T70" s="0"/>
+    </row>
+    <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="n">
         <v>70</v>
       </c>
@@ -3305,7 +4084,7 @@
       <c r="C71" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="D71" s="2" t="s">
         <v>165</v>
       </c>
       <c r="E71" s="0" t="n">
@@ -3320,14 +4099,24 @@
       <c r="H71" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="I71" s="0"/>
+      <c r="J71" s="0"/>
+      <c r="K71" s="0"/>
       <c r="L71" s="0" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="M71" s="0"/>
+      <c r="N71" s="0"/>
       <c r="O71" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P71" s="0"/>
+      <c r="Q71" s="0"/>
+      <c r="R71" s="0"/>
+      <c r="S71" s="0"/>
+      <c r="T71" s="0"/>
+    </row>
+    <row r="72" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="n">
         <v>71</v>
       </c>
@@ -3337,7 +4126,7 @@
       <c r="C72" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="D72" s="0" t="s">
+      <c r="D72" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E72" s="0" t="n">
@@ -3352,20 +4141,28 @@
       <c r="H72" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="I72" s="0"/>
+      <c r="J72" s="0"/>
       <c r="K72" s="0" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="L72" s="0"/>
       <c r="M72" s="0" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="N72" s="0" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="O72" s="0" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P72" s="0"/>
+      <c r="Q72" s="0"/>
+      <c r="R72" s="0"/>
+      <c r="S72" s="0"/>
+      <c r="T72" s="0"/>
+    </row>
+    <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="n">
         <v>72</v>
       </c>
@@ -3375,7 +4172,7 @@
       <c r="C73" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="D73" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E73" s="0" t="n">
@@ -3388,19 +4185,28 @@
         <v>600</v>
       </c>
       <c r="H73" s="0" t="n">
-        <v>0.3</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I73" s="0"/>
+      <c r="J73" s="0"/>
+      <c r="K73" s="0"/>
       <c r="L73" s="0" t="n">
-        <v>0.05</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="M73" s="0"/>
       <c r="N73" s="0" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="O73" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P73" s="0"/>
+      <c r="Q73" s="0"/>
+      <c r="R73" s="0"/>
+      <c r="S73" s="0"/>
+      <c r="T73" s="0"/>
+    </row>
+    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="n">
         <v>73</v>
       </c>
@@ -3410,20 +4216,33 @@
       <c r="C74" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="D74" s="0" t="s">
+      <c r="D74" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E74" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F74" s="0"/>
+      <c r="G74" s="0"/>
+      <c r="H74" s="0"/>
+      <c r="I74" s="0"/>
       <c r="J74" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="K74" s="0"/>
+      <c r="L74" s="0"/>
+      <c r="M74" s="0"/>
+      <c r="N74" s="0"/>
+      <c r="O74" s="0"/>
+      <c r="P74" s="0"/>
+      <c r="Q74" s="0"/>
       <c r="R74" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+      <c r="S74" s="0"/>
+      <c r="T74" s="0"/>
+    </row>
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="n">
         <v>74</v>
       </c>
@@ -3433,20 +4252,33 @@
       <c r="C75" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="D75" s="0" t="s">
+      <c r="D75" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E75" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F75" s="0"/>
+      <c r="G75" s="0"/>
+      <c r="H75" s="0"/>
       <c r="I75" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J75" s="0"/>
+      <c r="K75" s="0"/>
+      <c r="L75" s="0"/>
+      <c r="M75" s="0"/>
+      <c r="N75" s="0"/>
+      <c r="O75" s="0"/>
       <c r="P75" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+      <c r="Q75" s="0"/>
+      <c r="R75" s="0"/>
+      <c r="S75" s="0"/>
+      <c r="T75" s="0"/>
+    </row>
+    <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="n">
         <v>75</v>
       </c>
@@ -3456,23 +4288,35 @@
       <c r="C76" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="D76" s="0" t="s">
+      <c r="D76" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E76" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F76" s="0"/>
+      <c r="G76" s="0"/>
+      <c r="H76" s="0"/>
+      <c r="I76" s="0"/>
+      <c r="J76" s="0"/>
+      <c r="K76" s="0"/>
       <c r="L76" s="0" t="n">
         <v>0.0075</v>
       </c>
       <c r="M76" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="N76" s="0"/>
+      <c r="O76" s="0"/>
+      <c r="P76" s="0"/>
       <c r="Q76" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+      <c r="R76" s="0"/>
+      <c r="S76" s="0"/>
+      <c r="T76" s="0"/>
+    </row>
+    <row r="77" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="n">
         <v>76</v>
       </c>
@@ -3482,7 +4326,7 @@
       <c r="C77" s="0" t="s">
         <v>176</v>
       </c>
-      <c r="D77" s="0" t="s">
+      <c r="D77" s="2" t="s">
         <v>177</v>
       </c>
       <c r="E77" s="0" t="n">
@@ -3503,6 +4347,8 @@
       <c r="J77" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="K77" s="0"/>
+      <c r="L77" s="0"/>
       <c r="M77" s="0" t="n">
         <v>0.02</v>
       </c>
@@ -3512,11 +4358,15 @@
       <c r="O77" s="0" t="s">
         <v>55</v>
       </c>
+      <c r="P77" s="0"/>
+      <c r="Q77" s="0"/>
+      <c r="R77" s="0"/>
       <c r="S77" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+      <c r="T77" s="0"/>
+    </row>
+    <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="n">
         <v>77</v>
       </c>
@@ -3526,7 +4376,7 @@
       <c r="C78" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="D78" s="0" t="s">
+      <c r="D78" s="2" t="s">
         <v>179</v>
       </c>
       <c r="E78" s="0" t="n">
@@ -3547,11 +4397,20 @@
       <c r="J78" s="0" t="n">
         <v>0.03</v>
       </c>
+      <c r="K78" s="0"/>
+      <c r="L78" s="0"/>
+      <c r="M78" s="0"/>
+      <c r="N78" s="0"/>
       <c r="O78" s="0" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P78" s="0"/>
+      <c r="Q78" s="0"/>
+      <c r="R78" s="0"/>
+      <c r="S78" s="0"/>
+      <c r="T78" s="0"/>
+    </row>
+    <row r="79" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="n">
         <v>78</v>
       </c>
@@ -3561,7 +4420,7 @@
       <c r="C79" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="D79" s="0" t="s">
+      <c r="D79" s="2" t="s">
         <v>181</v>
       </c>
       <c r="E79" s="0" t="n">
@@ -3574,8 +4433,12 @@
         <v>100</v>
       </c>
       <c r="H79" s="0" t="n">
-        <v>0.3</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I79" s="0"/>
+      <c r="J79" s="0"/>
+      <c r="K79" s="0"/>
+      <c r="L79" s="0"/>
       <c r="M79" s="0" t="n">
         <v>0.02</v>
       </c>
@@ -3586,22 +4449,22 @@
         <v>55</v>
       </c>
       <c r="P79" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="Q79" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R79" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="S79" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="T79" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="n">
         <v>79</v>
       </c>
@@ -3611,7 +4474,7 @@
       <c r="C80" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="D80" s="0" t="s">
+      <c r="D80" s="2" t="s">
         <v>183</v>
       </c>
       <c r="E80" s="0" t="n">
@@ -3624,13 +4487,24 @@
         <v>250</v>
       </c>
       <c r="H80" s="0" t="n">
-        <v>0.35</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="I80" s="0"/>
+      <c r="J80" s="0"/>
+      <c r="K80" s="0"/>
+      <c r="L80" s="0"/>
+      <c r="M80" s="0"/>
+      <c r="N80" s="0"/>
       <c r="O80" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P80" s="0"/>
+      <c r="Q80" s="0"/>
+      <c r="R80" s="0"/>
+      <c r="S80" s="0"/>
+      <c r="T80" s="0"/>
+    </row>
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="n">
         <v>80</v>
       </c>
@@ -3640,7 +4514,7 @@
       <c r="C81" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="D81" s="0" t="s">
+      <c r="D81" s="2" t="s">
         <v>185</v>
       </c>
       <c r="E81" s="0" t="n">
@@ -3653,13 +4527,24 @@
         <v>500</v>
       </c>
       <c r="H81" s="0" t="n">
-        <v>0.45</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="I81" s="0"/>
+      <c r="J81" s="0"/>
+      <c r="K81" s="0"/>
+      <c r="L81" s="0"/>
+      <c r="M81" s="0"/>
+      <c r="N81" s="0"/>
       <c r="O81" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P81" s="0"/>
+      <c r="Q81" s="0"/>
+      <c r="R81" s="0"/>
+      <c r="S81" s="0"/>
+      <c r="T81" s="0"/>
+    </row>
+    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="n">
         <v>81</v>
       </c>
@@ -3669,7 +4554,7 @@
       <c r="C82" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="D82" s="0" t="s">
+      <c r="D82" s="2" t="s">
         <v>187</v>
       </c>
       <c r="E82" s="0" t="n">
@@ -3685,16 +4570,25 @@
         <v>0.15</v>
       </c>
       <c r="I82" s="0" t="n">
-        <v>0.05</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="J82" s="0"/>
+      <c r="K82" s="0"/>
+      <c r="L82" s="0"/>
+      <c r="M82" s="0"/>
       <c r="N82" s="0" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="O82" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P82" s="0"/>
+      <c r="Q82" s="0"/>
+      <c r="R82" s="0"/>
+      <c r="S82" s="0"/>
+      <c r="T82" s="0"/>
+    </row>
+    <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="n">
         <v>82</v>
       </c>
@@ -3704,23 +4598,35 @@
       <c r="C83" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="D83" s="0" t="s">
+      <c r="D83" s="2" t="s">
         <v>189</v>
       </c>
       <c r="E83" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F83" s="0"/>
+      <c r="G83" s="0"/>
+      <c r="H83" s="0"/>
       <c r="I83" s="0" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J83" s="0"/>
+      <c r="K83" s="0"/>
+      <c r="L83" s="0"/>
+      <c r="M83" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M83" s="0" t="n">
-        <v>0.1</v>
-      </c>
       <c r="N83" s="0" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.02</v>
+      </c>
+      <c r="O83" s="0"/>
+      <c r="P83" s="0"/>
+      <c r="Q83" s="0"/>
+      <c r="R83" s="0"/>
+      <c r="S83" s="0"/>
+      <c r="T83" s="0"/>
+    </row>
+    <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="n">
         <v>83</v>
       </c>
@@ -3730,20 +4636,33 @@
       <c r="C84" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="D84" s="0" t="s">
+      <c r="D84" s="2" t="s">
         <v>191</v>
       </c>
       <c r="E84" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F84" s="0"/>
+      <c r="G84" s="0"/>
+      <c r="H84" s="0"/>
       <c r="I84" s="0" t="n">
-        <v>0.08</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="J84" s="0"/>
+      <c r="K84" s="0"/>
+      <c r="L84" s="0"/>
+      <c r="M84" s="0"/>
       <c r="N84" s="0" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.02</v>
+      </c>
+      <c r="O84" s="0"/>
+      <c r="P84" s="0"/>
+      <c r="Q84" s="0"/>
+      <c r="R84" s="0"/>
+      <c r="S84" s="0"/>
+      <c r="T84" s="0"/>
+    </row>
+    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="n">
         <v>84</v>
       </c>
@@ -3753,20 +4672,33 @@
       <c r="C85" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="D85" s="0" t="s">
+      <c r="D85" s="2" t="s">
         <v>193</v>
       </c>
       <c r="E85" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F85" s="0"/>
+      <c r="G85" s="0"/>
+      <c r="H85" s="0"/>
+      <c r="I85" s="0"/>
       <c r="J85" s="0" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="K85" s="0"/>
+      <c r="L85" s="0"/>
       <c r="M85" s="0" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.05</v>
+      </c>
+      <c r="N85" s="0"/>
+      <c r="O85" s="0"/>
+      <c r="P85" s="0"/>
+      <c r="Q85" s="0"/>
+      <c r="R85" s="0"/>
+      <c r="S85" s="0"/>
+      <c r="T85" s="0"/>
+    </row>
+    <row r="86" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="n">
         <v>85</v>
       </c>
@@ -3776,7 +4708,7 @@
       <c r="C86" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="D86" s="0" t="s">
+      <c r="D86" s="2" t="s">
         <v>195</v>
       </c>
       <c r="E86" s="0" t="n">
@@ -3792,16 +4724,25 @@
         <v>0.05</v>
       </c>
       <c r="I86" s="0" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="J86" s="0"/>
+      <c r="K86" s="0"/>
+      <c r="L86" s="0"/>
       <c r="M86" s="0" t="n">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="N86" s="0" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.02</v>
+      </c>
+      <c r="O86" s="0"/>
+      <c r="P86" s="0"/>
+      <c r="Q86" s="0"/>
+      <c r="R86" s="0"/>
+      <c r="S86" s="0"/>
+      <c r="T86" s="0"/>
+    </row>
+    <row r="87" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="n">
         <v>86</v>
       </c>
@@ -3811,7 +4752,7 @@
       <c r="C87" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="D87" s="0" t="s">
+      <c r="D87" s="2" t="s">
         <v>197</v>
       </c>
       <c r="E87" s="0" t="n">
@@ -3827,22 +4768,29 @@
         <v>0.1</v>
       </c>
       <c r="I87" s="0" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="J87" s="0" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K87" s="0"/>
+      <c r="L87" s="0"/>
       <c r="M87" s="0" t="n">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
       <c r="N87" s="0" t="n">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
       <c r="O87" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P87" s="0"/>
+      <c r="Q87" s="0"/>
+      <c r="R87" s="0"/>
+      <c r="S87" s="0"/>
+      <c r="T87" s="0"/>
+    </row>
+    <row r="88" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="n">
         <v>87</v>
       </c>
@@ -3852,7 +4800,7 @@
       <c r="C88" s="0" t="s">
         <v>198</v>
       </c>
-      <c r="D88" s="0" t="s">
+      <c r="D88" s="2" t="s">
         <v>199</v>
       </c>
       <c r="E88" s="0" t="n">
@@ -3862,22 +4810,31 @@
         <v>40000</v>
       </c>
       <c r="G88" s="0" t="n">
-        <v>4000</v>
+        <v>2100</v>
       </c>
       <c r="H88" s="0" t="n">
         <v>0.2</v>
       </c>
       <c r="I88" s="0" t="n">
-        <v>0.4</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="J88" s="0"/>
+      <c r="K88" s="0"/>
+      <c r="L88" s="0"/>
+      <c r="M88" s="0"/>
       <c r="N88" s="0" t="n">
-        <v>0.6</v>
+        <v>0.02</v>
       </c>
       <c r="O88" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P88" s="0"/>
+      <c r="Q88" s="0"/>
+      <c r="R88" s="0"/>
+      <c r="S88" s="0"/>
+      <c r="T88" s="0"/>
+    </row>
+    <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="n">
         <v>88</v>
       </c>
@@ -3887,7 +4844,7 @@
       <c r="C89" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="D89" s="0" t="s">
+      <c r="D89" s="2" t="s">
         <v>201</v>
       </c>
       <c r="E89" s="0" t="n">
@@ -3897,19 +4854,29 @@
         <v>50000</v>
       </c>
       <c r="G89" s="0" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H89" s="0" t="n">
-        <v>0.3</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I89" s="0"/>
+      <c r="J89" s="0"/>
+      <c r="K89" s="0"/>
+      <c r="L89" s="0"/>
       <c r="M89" s="0" t="n">
-        <v>0.7</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="N89" s="0"/>
       <c r="O89" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P89" s="0"/>
+      <c r="Q89" s="0"/>
+      <c r="R89" s="0"/>
+      <c r="S89" s="0"/>
+      <c r="T89" s="0"/>
+    </row>
+    <row r="90" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="n">
         <v>89</v>
       </c>
@@ -3919,7 +4886,7 @@
       <c r="C90" s="0" t="s">
         <v>202</v>
       </c>
-      <c r="D90" s="0" t="s">
+      <c r="D90" s="2" t="s">
         <v>203</v>
       </c>
       <c r="E90" s="0" t="n">
@@ -3929,25 +4896,33 @@
         <v>80000</v>
       </c>
       <c r="G90" s="0" t="n">
-        <v>8000</v>
+        <v>1700</v>
       </c>
       <c r="H90" s="0" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="I90" s="0" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="J90" s="0"/>
+      <c r="K90" s="0"/>
+      <c r="L90" s="0"/>
       <c r="M90" s="0" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="N90" s="0" t="n">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="O90" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P90" s="0"/>
+      <c r="Q90" s="0"/>
+      <c r="R90" s="0"/>
+      <c r="S90" s="0"/>
+      <c r="T90" s="0"/>
+    </row>
+    <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="n">
         <v>90</v>
       </c>
@@ -3957,23 +4932,35 @@
       <c r="C91" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="D91" s="0" t="s">
+      <c r="D91" s="2" t="s">
         <v>205</v>
       </c>
       <c r="E91" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F91" s="0"/>
+      <c r="G91" s="0"/>
+      <c r="H91" s="0"/>
       <c r="I91" s="0" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="J91" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="K91" s="0"/>
+      <c r="L91" s="0"/>
+      <c r="M91" s="0"/>
       <c r="N91" s="0" t="n">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O91" s="0"/>
+      <c r="P91" s="0"/>
+      <c r="Q91" s="0"/>
+      <c r="R91" s="0"/>
+      <c r="S91" s="0"/>
+      <c r="T91" s="0"/>
+    </row>
+    <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="n">
         <v>91</v>
       </c>
@@ -3983,7 +4970,7 @@
       <c r="C92" s="0" t="s">
         <v>206</v>
       </c>
-      <c r="D92" s="0" t="s">
+      <c r="D92" s="2" t="s">
         <v>207</v>
       </c>
       <c r="E92" s="0" t="n">
@@ -3998,14 +4985,24 @@
       <c r="H92" s="0" t="n">
         <v>0.05</v>
       </c>
+      <c r="I92" s="0"/>
+      <c r="J92" s="0"/>
+      <c r="K92" s="0"/>
+      <c r="L92" s="0"/>
+      <c r="M92" s="0"/>
       <c r="N92" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="O92" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P92" s="0"/>
+      <c r="Q92" s="0"/>
+      <c r="R92" s="0"/>
+      <c r="S92" s="0"/>
+      <c r="T92" s="0"/>
+    </row>
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="n">
         <v>92</v>
       </c>
@@ -4015,12 +5012,25 @@
       <c r="C93" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="D93" s="0" t="s">
+      <c r="D93" s="2" t="s">
         <v>209</v>
       </c>
       <c r="E93" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F93" s="0"/>
+      <c r="G93" s="0"/>
+      <c r="H93" s="0"/>
+      <c r="I93" s="0"/>
+      <c r="J93" s="0"/>
+      <c r="K93" s="0"/>
+      <c r="L93" s="0"/>
+      <c r="M93" s="0"/>
+      <c r="N93" s="0"/>
+      <c r="O93" s="0"/>
+      <c r="P93" s="0"/>
+      <c r="Q93" s="0"/>
+      <c r="R93" s="0"/>
       <c r="S93" s="0" t="n">
         <v>0.005</v>
       </c>
@@ -4028,7 +5038,7 @@
         <v>0.005</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="n">
         <v>93</v>
       </c>
@@ -4038,17 +5048,31 @@
       <c r="C94" s="0" t="s">
         <v>210</v>
       </c>
-      <c r="D94" s="0" t="s">
+      <c r="D94" s="2" t="s">
         <v>211</v>
       </c>
       <c r="E94" s="0" t="n">
         <v>36</v>
       </c>
+      <c r="F94" s="0"/>
+      <c r="G94" s="0"/>
+      <c r="H94" s="0"/>
+      <c r="I94" s="0"/>
+      <c r="J94" s="0"/>
+      <c r="K94" s="0"/>
+      <c r="L94" s="0"/>
+      <c r="M94" s="0"/>
+      <c r="N94" s="0"/>
+      <c r="O94" s="0"/>
+      <c r="P94" s="0"/>
       <c r="Q94" s="0" t="n">
         <v>0.0025</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R94" s="0"/>
+      <c r="S94" s="0"/>
+      <c r="T94" s="0"/>
+    </row>
+    <row r="95" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="n">
         <v>94</v>
       </c>
@@ -4058,7 +5082,7 @@
       <c r="C95" s="0" t="s">
         <v>212</v>
       </c>
-      <c r="D95" s="0" t="s">
+      <c r="D95" s="2" t="s">
         <v>213</v>
       </c>
       <c r="E95" s="0" t="n">
@@ -4082,23 +5106,27 @@
       <c r="K95" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="L95" s="0"/>
+      <c r="M95" s="0"/>
+      <c r="N95" s="0"/>
       <c r="O95" s="0" t="s">
         <v>55</v>
       </c>
+      <c r="P95" s="0"/>
       <c r="Q95" s="0" t="n">
-        <v>0.1</v>
+        <v>0.005</v>
       </c>
       <c r="R95" s="0" t="n">
-        <v>0.05</v>
+        <v>0.005</v>
       </c>
       <c r="S95" s="0" t="n">
-        <v>0.15</v>
+        <v>0.005</v>
       </c>
       <c r="T95" s="0" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="n">
         <v>95</v>
       </c>
@@ -4108,7 +5136,7 @@
       <c r="C96" s="0" t="s">
         <v>214</v>
       </c>
-      <c r="D96" s="0" t="s">
+      <c r="D96" s="2" t="s">
         <v>215</v>
       </c>
       <c r="E96" s="0" t="n">
@@ -4121,7 +5149,7 @@
         <v>50</v>
       </c>
       <c r="H96" s="0" t="n">
-        <v>0.0015</v>
+        <v>0.15</v>
       </c>
       <c r="I96" s="0" t="n">
         <v>0.0175</v>
@@ -4129,20 +5157,26 @@
       <c r="J96" s="0" t="n">
         <v>0.025</v>
       </c>
+      <c r="K96" s="0"/>
+      <c r="L96" s="0"/>
+      <c r="M96" s="0"/>
+      <c r="N96" s="0"/>
       <c r="O96" s="0" t="s">
         <v>42</v>
       </c>
       <c r="P96" s="0" t="n">
         <v>0.0015</v>
       </c>
+      <c r="Q96" s="0"/>
+      <c r="R96" s="0"/>
       <c r="S96" s="0" t="n">
-        <v>0.0075</v>
+        <v>0.005</v>
       </c>
       <c r="T96" s="0" t="n">
-        <v>0.0075</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="n">
         <v>96</v>
       </c>
@@ -4152,7 +5186,7 @@
       <c r="C97" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="D97" s="0" t="s">
+      <c r="D97" s="2" t="s">
         <v>217</v>
       </c>
       <c r="E97" s="0" t="n">
@@ -4165,19 +5199,28 @@
         <v>250</v>
       </c>
       <c r="H97" s="0" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I97" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J97" s="0"/>
+      <c r="K97" s="0"/>
+      <c r="L97" s="0"/>
+      <c r="M97" s="0"/>
       <c r="N97" s="0" t="n">
         <v>0.01</v>
       </c>
       <c r="O97" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P97" s="0"/>
+      <c r="Q97" s="0"/>
+      <c r="R97" s="0"/>
+      <c r="S97" s="0"/>
+      <c r="T97" s="0"/>
+    </row>
+    <row r="98" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="n">
         <v>97</v>
       </c>
@@ -4187,7 +5230,7 @@
       <c r="C98" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="D98" s="0" t="s">
+      <c r="D98" s="2" t="s">
         <v>219</v>
       </c>
       <c r="E98" s="0" t="n">
@@ -4211,6 +5254,9 @@
       <c r="K98" s="0" t="n">
         <v>0.0175</v>
       </c>
+      <c r="L98" s="0"/>
+      <c r="M98" s="0"/>
+      <c r="N98" s="0"/>
       <c r="O98" s="0" t="s">
         <v>42</v>
       </c>
@@ -4218,19 +5264,19 @@
         <v>0.003</v>
       </c>
       <c r="Q98" s="0" t="n">
-        <v>0.0075</v>
+        <v>0.005</v>
       </c>
       <c r="R98" s="0" t="n">
-        <v>0.0075</v>
+        <v>0.005</v>
       </c>
       <c r="S98" s="0" t="n">
-        <v>0.0075</v>
+        <v>0.005</v>
       </c>
       <c r="T98" s="0" t="n">
-        <v>0.0075</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="n">
         <v>98</v>
       </c>
@@ -4240,7 +5286,7 @@
       <c r="C99" s="0" t="s">
         <v>220</v>
       </c>
-      <c r="D99" s="0" t="s">
+      <c r="D99" s="2" t="s">
         <v>221</v>
       </c>
       <c r="E99" s="0" t="n">
@@ -4258,17 +5304,25 @@
       <c r="I99" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J99" s="0"/>
+      <c r="K99" s="0"/>
       <c r="L99" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="M99" s="0"/>
+      <c r="N99" s="0"/>
       <c r="O99" s="0" t="s">
         <v>60</v>
       </c>
       <c r="P99" s="0" t="n">
-        <v>0.0075</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+      <c r="Q99" s="0"/>
+      <c r="R99" s="0"/>
+      <c r="S99" s="0"/>
+      <c r="T99" s="0"/>
+    </row>
+    <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="n">
         <v>99</v>
       </c>
@@ -4278,17 +5332,31 @@
       <c r="C100" s="0" t="s">
         <v>222</v>
       </c>
-      <c r="D100" s="0" t="s">
+      <c r="D100" s="2" t="s">
         <v>223</v>
       </c>
       <c r="E100" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F100" s="0"/>
+      <c r="G100" s="0"/>
+      <c r="H100" s="0"/>
       <c r="I100" s="0" t="n">
         <v>0.012</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J100" s="0"/>
+      <c r="K100" s="0"/>
+      <c r="L100" s="0"/>
+      <c r="M100" s="0"/>
+      <c r="N100" s="0"/>
+      <c r="O100" s="0"/>
+      <c r="P100" s="0"/>
+      <c r="Q100" s="0"/>
+      <c r="R100" s="0"/>
+      <c r="S100" s="0"/>
+      <c r="T100" s="0"/>
+    </row>
+    <row r="101" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="n">
         <v>100</v>
       </c>
@@ -4298,32 +5366,41 @@
       <c r="C101" s="0" t="s">
         <v>224</v>
       </c>
-      <c r="D101" s="0" t="s">
+      <c r="D101" s="2" t="s">
         <v>225</v>
       </c>
       <c r="E101" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F101" s="0"/>
+      <c r="G101" s="0"/>
+      <c r="H101" s="0"/>
+      <c r="I101" s="0"/>
+      <c r="J101" s="0"/>
+      <c r="K101" s="0"/>
+      <c r="L101" s="0"/>
+      <c r="M101" s="0"/>
       <c r="N101" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="O101" s="0"/>
       <c r="P101" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="Q101" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R101" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="S101" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="T101" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="n">
         <v>101</v>
       </c>
@@ -4333,23 +5410,35 @@
       <c r="C102" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="D102" s="0" t="s">
+      <c r="D102" s="2" t="s">
         <v>227</v>
       </c>
       <c r="E102" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F102" s="0"/>
+      <c r="G102" s="0"/>
+      <c r="H102" s="0"/>
+      <c r="I102" s="0"/>
+      <c r="J102" s="0"/>
       <c r="K102" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="L102" s="0"/>
       <c r="M102" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="N102" s="0" t="n">
         <v>0.005</v>
       </c>
-    </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O102" s="0"/>
+      <c r="P102" s="0"/>
+      <c r="Q102" s="0"/>
+      <c r="R102" s="0"/>
+      <c r="S102" s="0"/>
+      <c r="T102" s="0"/>
+    </row>
+    <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="n">
         <v>102</v>
       </c>
@@ -4359,7 +5448,7 @@
       <c r="C103" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="D103" s="0" t="s">
+      <c r="D103" s="2" t="s">
         <v>229</v>
       </c>
       <c r="E103" s="0" t="n">
@@ -4374,11 +5463,22 @@
       <c r="H103" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="I103" s="0"/>
+      <c r="J103" s="0"/>
+      <c r="K103" s="0"/>
+      <c r="L103" s="0"/>
+      <c r="M103" s="0"/>
+      <c r="N103" s="0"/>
       <c r="O103" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P103" s="0"/>
+      <c r="Q103" s="0"/>
+      <c r="R103" s="0"/>
+      <c r="S103" s="0"/>
+      <c r="T103" s="0"/>
+    </row>
+    <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="n">
         <v>103</v>
       </c>
@@ -4388,7 +5488,7 @@
       <c r="C104" s="0" t="s">
         <v>230</v>
       </c>
-      <c r="D104" s="0" t="s">
+      <c r="D104" s="2" t="s">
         <v>231</v>
       </c>
       <c r="E104" s="0" t="n">
@@ -4403,17 +5503,26 @@
       <c r="H104" s="0" t="n">
         <v>0.18</v>
       </c>
+      <c r="I104" s="0"/>
+      <c r="J104" s="0"/>
+      <c r="K104" s="0"/>
       <c r="L104" s="0" t="n">
         <v>0.0075</v>
       </c>
+      <c r="M104" s="0"/>
+      <c r="N104" s="0"/>
       <c r="O104" s="0" t="s">
         <v>35</v>
       </c>
       <c r="P104" s="0" t="n">
         <v>0.005</v>
       </c>
-    </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q104" s="0"/>
+      <c r="R104" s="0"/>
+      <c r="S104" s="0"/>
+      <c r="T104" s="0"/>
+    </row>
+    <row r="105" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="n">
         <v>104</v>
       </c>
@@ -4423,7 +5532,7 @@
       <c r="C105" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="D105" s="0" t="s">
+      <c r="D105" s="2" t="s">
         <v>233</v>
       </c>
       <c r="E105" s="0" t="n">
@@ -4441,17 +5550,25 @@
       <c r="I105" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J105" s="0"/>
+      <c r="K105" s="0"/>
       <c r="L105" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="M105" s="0"/>
       <c r="N105" s="0" t="n">
         <v>0.005</v>
       </c>
       <c r="O105" s="0" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P105" s="0"/>
+      <c r="Q105" s="0"/>
+      <c r="R105" s="0"/>
+      <c r="S105" s="0"/>
+      <c r="T105" s="0"/>
+    </row>
+    <row r="106" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="n">
         <v>105</v>
       </c>
@@ -4461,7 +5578,7 @@
       <c r="C106" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="D106" s="0" t="s">
+      <c r="D106" s="2" t="s">
         <v>235</v>
       </c>
       <c r="E106" s="0" t="n">
@@ -4474,22 +5591,30 @@
         <v>300</v>
       </c>
       <c r="H106" s="0" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I106" s="0"/>
+      <c r="J106" s="0"/>
+      <c r="K106" s="0"/>
+      <c r="L106" s="0"/>
+      <c r="M106" s="0"/>
       <c r="N106" s="0" t="n">
         <v>0.02</v>
       </c>
       <c r="O106" s="0" t="s">
         <v>55</v>
       </c>
+      <c r="P106" s="0"/>
       <c r="Q106" s="0" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="R106" s="0"/>
+      <c r="S106" s="0"/>
       <c r="T106" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="n">
         <v>106</v>
       </c>
@@ -4499,7 +5624,7 @@
       <c r="C107" s="0" t="s">
         <v>236</v>
       </c>
-      <c r="D107" s="0" t="s">
+      <c r="D107" s="2" t="s">
         <v>237</v>
       </c>
       <c r="E107" s="0" t="n">
@@ -4514,20 +5639,28 @@
       <c r="H107" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="I107" s="0"/>
+      <c r="J107" s="0"/>
       <c r="K107" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="L107" s="0"/>
       <c r="M107" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="N107" s="0"/>
       <c r="O107" s="0" t="s">
         <v>91</v>
       </c>
+      <c r="P107" s="0"/>
+      <c r="Q107" s="0"/>
       <c r="R107" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+      <c r="S107" s="0"/>
+      <c r="T107" s="0"/>
+    </row>
+    <row r="108" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="n">
         <v>107</v>
       </c>
@@ -4537,7 +5670,7 @@
       <c r="C108" s="0" t="s">
         <v>238</v>
       </c>
-      <c r="D108" s="0" t="s">
+      <c r="D108" s="2" t="s">
         <v>239</v>
       </c>
       <c r="E108" s="0" t="n">
@@ -4553,31 +5686,35 @@
         <v>0.2</v>
       </c>
       <c r="I108" s="0" t="n">
-        <v>0.025</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="J108" s="0"/>
+      <c r="K108" s="0"/>
+      <c r="L108" s="0"/>
+      <c r="M108" s="0"/>
       <c r="N108" s="0" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="O108" s="0" t="s">
         <v>22</v>
       </c>
       <c r="P108" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="Q108" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R108" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="S108" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="T108" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="n">
         <v>108</v>
       </c>
@@ -4587,20 +5724,33 @@
       <c r="C109" s="0" t="s">
         <v>240</v>
       </c>
-      <c r="D109" s="0" t="s">
+      <c r="D109" s="2" t="s">
         <v>241</v>
       </c>
       <c r="E109" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F109" s="0"/>
+      <c r="G109" s="0"/>
+      <c r="H109" s="0"/>
       <c r="I109" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="J109" s="0"/>
+      <c r="K109" s="0"/>
+      <c r="L109" s="0"/>
+      <c r="M109" s="0"/>
       <c r="N109" s="0" t="n">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O109" s="0"/>
+      <c r="P109" s="0"/>
+      <c r="Q109" s="0"/>
+      <c r="R109" s="0"/>
+      <c r="S109" s="0"/>
+      <c r="T109" s="0"/>
+    </row>
+    <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="n">
         <v>109</v>
       </c>
@@ -4610,20 +5760,33 @@
       <c r="C110" s="0" t="s">
         <v>242</v>
       </c>
-      <c r="D110" s="0" t="s">
+      <c r="D110" s="2" t="s">
         <v>243</v>
       </c>
       <c r="E110" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F110" s="0"/>
+      <c r="G110" s="0"/>
+      <c r="H110" s="0"/>
       <c r="I110" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="J110" s="0"/>
+      <c r="K110" s="0"/>
+      <c r="L110" s="0"/>
+      <c r="M110" s="0"/>
+      <c r="N110" s="0"/>
+      <c r="O110" s="0"/>
+      <c r="P110" s="0"/>
+      <c r="Q110" s="0"/>
+      <c r="R110" s="0"/>
       <c r="S110" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+      <c r="T110" s="0"/>
+    </row>
+    <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="n">
         <v>110</v>
       </c>
@@ -4633,20 +5796,33 @@
       <c r="C111" s="0" t="s">
         <v>244</v>
       </c>
-      <c r="D111" s="0" t="s">
+      <c r="D111" s="2" t="s">
         <v>245</v>
       </c>
       <c r="E111" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F111" s="0"/>
+      <c r="G111" s="0"/>
+      <c r="H111" s="0"/>
+      <c r="I111" s="0"/>
+      <c r="J111" s="0"/>
+      <c r="K111" s="0"/>
+      <c r="L111" s="0"/>
+      <c r="M111" s="0"/>
       <c r="N111" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="O111" s="0"/>
+      <c r="P111" s="0"/>
+      <c r="Q111" s="0"/>
+      <c r="R111" s="0"/>
+      <c r="S111" s="0"/>
       <c r="T111" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="n">
         <v>111</v>
       </c>
@@ -4656,7 +5832,7 @@
       <c r="C112" s="0" t="s">
         <v>246</v>
       </c>
-      <c r="D112" s="0" t="s">
+      <c r="D112" s="2" t="s">
         <v>247</v>
       </c>
       <c r="E112" s="0" t="n">
@@ -4672,13 +5848,23 @@
         <v>0.2</v>
       </c>
       <c r="I112" s="0" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.015</v>
+      </c>
+      <c r="J112" s="0"/>
+      <c r="K112" s="0"/>
+      <c r="L112" s="0"/>
+      <c r="M112" s="0"/>
+      <c r="N112" s="0"/>
       <c r="O112" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P112" s="0"/>
+      <c r="Q112" s="0"/>
+      <c r="R112" s="0"/>
+      <c r="S112" s="0"/>
+      <c r="T112" s="0"/>
+    </row>
+    <row r="113" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="n">
         <v>112</v>
       </c>
@@ -4688,7 +5874,7 @@
       <c r="C113" s="0" t="s">
         <v>248</v>
       </c>
-      <c r="D113" s="0" t="s">
+      <c r="D113" s="2" t="s">
         <v>249</v>
       </c>
       <c r="E113" s="0" t="n">
@@ -4703,26 +5889,32 @@
       <c r="H113" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="I113" s="0"/>
+      <c r="J113" s="0"/>
+      <c r="K113" s="0"/>
+      <c r="L113" s="0"/>
+      <c r="M113" s="0"/>
+      <c r="N113" s="0"/>
       <c r="O113" s="0" t="s">
         <v>55</v>
       </c>
       <c r="P113" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="Q113" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R113" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="S113" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="T113" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="n">
         <v>113</v>
       </c>
@@ -4732,7 +5924,7 @@
       <c r="C114" s="0" t="s">
         <v>250</v>
       </c>
-      <c r="D114" s="0" t="s">
+      <c r="D114" s="2" t="s">
         <v>251</v>
       </c>
       <c r="E114" s="0" t="n">
@@ -4745,22 +5937,30 @@
         <v>200</v>
       </c>
       <c r="H114" s="0" t="n">
-        <v>0.27</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I114" s="0"/>
+      <c r="J114" s="0"/>
+      <c r="K114" s="0"/>
       <c r="L114" s="0" t="n">
-        <v>0.012</v>
-      </c>
+        <v>0.0125</v>
+      </c>
+      <c r="M114" s="0"/>
+      <c r="N114" s="0"/>
       <c r="O114" s="0" t="s">
         <v>60</v>
       </c>
       <c r="P114" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="Q114" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+      <c r="R114" s="0"/>
+      <c r="S114" s="0"/>
+      <c r="T114" s="0"/>
+    </row>
+    <row r="115" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="n">
         <v>114</v>
       </c>
@@ -4770,7 +5970,7 @@
       <c r="C115" s="0" t="s">
         <v>252</v>
       </c>
-      <c r="D115" s="0" t="s">
+      <c r="D115" s="2" t="s">
         <v>253</v>
       </c>
       <c r="E115" s="0" t="n">
@@ -4783,16 +5983,26 @@
         <v>250</v>
       </c>
       <c r="H115" s="0" t="n">
-        <v>0.3</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I115" s="0"/>
+      <c r="J115" s="0"/>
+      <c r="K115" s="0"/>
+      <c r="L115" s="0"/>
+      <c r="M115" s="0"/>
       <c r="N115" s="0" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="O115" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P115" s="0"/>
+      <c r="Q115" s="0"/>
+      <c r="R115" s="0"/>
+      <c r="S115" s="0"/>
+      <c r="T115" s="0"/>
+    </row>
+    <row r="116" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="n">
         <v>115</v>
       </c>
@@ -4802,7 +6012,7 @@
       <c r="C116" s="0" t="s">
         <v>254</v>
       </c>
-      <c r="D116" s="0" t="s">
+      <c r="D116" s="2" t="s">
         <v>255</v>
       </c>
       <c r="E116" s="0" t="n">
@@ -4817,29 +6027,34 @@
       <c r="H116" s="0" t="n">
         <v>0.12</v>
       </c>
+      <c r="I116" s="0"/>
+      <c r="J116" s="0"/>
+      <c r="K116" s="0"/>
       <c r="L116" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="M116" s="0"/>
+      <c r="N116" s="0"/>
       <c r="O116" s="0" t="s">
         <v>91</v>
       </c>
       <c r="P116" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="Q116" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R116" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="S116" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="T116" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="n">
         <v>116</v>
       </c>
@@ -4849,7 +6064,7 @@
       <c r="C117" s="0" t="s">
         <v>256</v>
       </c>
-      <c r="D117" s="0" t="s">
+      <c r="D117" s="2" t="s">
         <v>257</v>
       </c>
       <c r="E117" s="0" t="n">
@@ -4862,16 +6077,26 @@
         <v>750</v>
       </c>
       <c r="H117" s="0" t="n">
-        <v>0.4</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I117" s="0"/>
+      <c r="J117" s="0"/>
+      <c r="K117" s="0"/>
+      <c r="L117" s="0"/>
+      <c r="M117" s="0"/>
       <c r="N117" s="0" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="O117" s="0" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P117" s="0"/>
+      <c r="Q117" s="0"/>
+      <c r="R117" s="0"/>
+      <c r="S117" s="0"/>
+      <c r="T117" s="0"/>
+    </row>
+    <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="n">
         <v>117</v>
       </c>
@@ -4881,20 +6106,33 @@
       <c r="C118" s="0" t="s">
         <v>258</v>
       </c>
-      <c r="D118" s="0" t="s">
+      <c r="D118" s="2" t="s">
         <v>259</v>
       </c>
       <c r="E118" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F118" s="0"/>
+      <c r="G118" s="0"/>
+      <c r="H118" s="0"/>
+      <c r="I118" s="0"/>
+      <c r="J118" s="0"/>
       <c r="K118" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="L118" s="0"/>
       <c r="M118" s="0" t="n">
         <v>0.005</v>
       </c>
-    </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N118" s="0"/>
+      <c r="O118" s="0"/>
+      <c r="P118" s="0"/>
+      <c r="Q118" s="0"/>
+      <c r="R118" s="0"/>
+      <c r="S118" s="0"/>
+      <c r="T118" s="0"/>
+    </row>
+    <row r="119" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="n">
         <v>118</v>
       </c>
@@ -4904,12 +6142,15 @@
       <c r="C119" s="0" t="s">
         <v>260</v>
       </c>
-      <c r="D119" s="0" t="s">
+      <c r="D119" s="2" t="s">
         <v>261</v>
       </c>
       <c r="E119" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F119" s="0"/>
+      <c r="G119" s="0"/>
+      <c r="H119" s="0"/>
       <c r="I119" s="0" t="n">
         <v>0.015</v>
       </c>
@@ -4919,14 +6160,21 @@
       <c r="K119" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="L119" s="0"/>
       <c r="M119" s="0" t="n">
         <v>0.0075</v>
       </c>
       <c r="N119" s="0" t="n">
         <v>0.0075</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O119" s="0"/>
+      <c r="P119" s="0"/>
+      <c r="Q119" s="0"/>
+      <c r="R119" s="0"/>
+      <c r="S119" s="0"/>
+      <c r="T119" s="0"/>
+    </row>
+    <row r="120" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="n">
         <v>119</v>
       </c>
@@ -4936,12 +6184,16 @@
       <c r="C120" s="0" t="s">
         <v>262</v>
       </c>
-      <c r="D120" s="0" t="s">
+      <c r="D120" s="2" t="s">
         <v>263</v>
       </c>
       <c r="E120" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F120" s="0"/>
+      <c r="G120" s="0"/>
+      <c r="H120" s="0"/>
+      <c r="I120" s="0"/>
       <c r="J120" s="0" t="n">
         <v>0.01</v>
       </c>
@@ -4957,23 +6209,24 @@
       <c r="N120" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="O120" s="0"/>
       <c r="P120" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="Q120" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R120" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="S120" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="T120" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="n">
         <v>120</v>
       </c>
@@ -4983,7 +6236,7 @@
       <c r="C121" s="0" t="s">
         <v>264</v>
       </c>
-      <c r="D121" s="0" t="s">
+      <c r="D121" s="2" t="s">
         <v>265</v>
       </c>
       <c r="E121" s="0" t="n">
@@ -4998,14 +6251,24 @@
       <c r="H121" s="0" t="n">
         <v>0.05</v>
       </c>
+      <c r="I121" s="0"/>
+      <c r="J121" s="0"/>
+      <c r="K121" s="0"/>
+      <c r="L121" s="0"/>
+      <c r="M121" s="0"/>
       <c r="N121" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="O121" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P121" s="0"/>
+      <c r="Q121" s="0"/>
+      <c r="R121" s="0"/>
+      <c r="S121" s="0"/>
+      <c r="T121" s="0"/>
+    </row>
+    <row r="122" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="n">
         <v>121</v>
       </c>
@@ -5015,7 +6278,7 @@
       <c r="C122" s="0" t="s">
         <v>266</v>
       </c>
-      <c r="D122" s="0" t="s">
+      <c r="D122" s="2" t="s">
         <v>267</v>
       </c>
       <c r="E122" s="0" t="n">
@@ -5030,9 +6293,12 @@
       <c r="H122" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="I122" s="0"/>
+      <c r="J122" s="0"/>
       <c r="K122" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="L122" s="0"/>
       <c r="M122" s="0" t="n">
         <v>0.01</v>
       </c>
@@ -5042,8 +6308,13 @@
       <c r="O122" s="0" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P122" s="0"/>
+      <c r="Q122" s="0"/>
+      <c r="R122" s="0"/>
+      <c r="S122" s="0"/>
+      <c r="T122" s="0"/>
+    </row>
+    <row r="123" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="n">
         <v>122</v>
       </c>
@@ -5053,7 +6324,7 @@
       <c r="C123" s="0" t="s">
         <v>268</v>
       </c>
-      <c r="D123" s="0" t="s">
+      <c r="D123" s="2" t="s">
         <v>269</v>
       </c>
       <c r="E123" s="0" t="n">
@@ -5068,20 +6339,28 @@
       <c r="H123" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="I123" s="0"/>
+      <c r="J123" s="0"/>
       <c r="K123" s="0" t="n">
         <v>0.025</v>
       </c>
       <c r="L123" s="0" t="n">
         <v>0.015</v>
       </c>
+      <c r="M123" s="0"/>
       <c r="N123" s="0" t="n">
         <v>0.02</v>
       </c>
       <c r="O123" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P123" s="0"/>
+      <c r="Q123" s="0"/>
+      <c r="R123" s="0"/>
+      <c r="S123" s="0"/>
+      <c r="T123" s="0"/>
+    </row>
+    <row r="124" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="n">
         <v>123</v>
       </c>
@@ -5091,7 +6370,7 @@
       <c r="C124" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="D124" s="0" t="s">
+      <c r="D124" s="2" t="s">
         <v>271</v>
       </c>
       <c r="E124" s="0" t="n">
@@ -5106,14 +6385,24 @@
       <c r="H124" s="0" t="n">
         <v>0.18</v>
       </c>
+      <c r="I124" s="0"/>
       <c r="J124" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="K124" s="0"/>
+      <c r="L124" s="0"/>
+      <c r="M124" s="0"/>
+      <c r="N124" s="0"/>
       <c r="O124" s="0" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P124" s="0"/>
+      <c r="Q124" s="0"/>
+      <c r="R124" s="0"/>
+      <c r="S124" s="0"/>
+      <c r="T124" s="0"/>
+    </row>
+    <row r="125" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="n">
         <v>124</v>
       </c>
@@ -5123,7 +6412,7 @@
       <c r="C125" s="0" t="s">
         <v>272</v>
       </c>
-      <c r="D125" s="0" t="s">
+      <c r="D125" s="2" t="s">
         <v>273</v>
       </c>
       <c r="E125" s="0" t="n">
@@ -5147,29 +6436,31 @@
       <c r="K125" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="L125" s="0"/>
+      <c r="M125" s="0"/>
       <c r="N125" s="0" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="O125" s="0" t="s">
         <v>60</v>
       </c>
       <c r="P125" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="Q125" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R125" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="S125" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="T125" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="n">
         <v>125</v>
       </c>
@@ -5179,7 +6470,7 @@
       <c r="C126" s="0" t="s">
         <v>274</v>
       </c>
-      <c r="D126" s="0" t="s">
+      <c r="D126" s="2" t="s">
         <v>275</v>
       </c>
       <c r="E126" s="0" t="n">
@@ -5215,8 +6506,13 @@
       <c r="O126" s="0" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P126" s="0"/>
+      <c r="Q126" s="0"/>
+      <c r="R126" s="0"/>
+      <c r="S126" s="0"/>
+      <c r="T126" s="0"/>
+    </row>
+    <row r="127" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="n">
         <v>126</v>
       </c>
@@ -5226,26 +6522,37 @@
       <c r="C127" s="0" t="s">
         <v>276</v>
       </c>
-      <c r="D127" s="0" t="s">
+      <c r="D127" s="2" t="s">
         <v>277</v>
       </c>
       <c r="E127" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F127" s="0"/>
+      <c r="G127" s="0"/>
+      <c r="H127" s="0"/>
       <c r="I127" s="0" t="n">
         <v>0.01</v>
       </c>
       <c r="J127" s="0" t="n">
         <v>0.005</v>
       </c>
+      <c r="K127" s="0"/>
+      <c r="L127" s="0"/>
       <c r="M127" s="0" t="n">
         <v>0.005</v>
       </c>
       <c r="N127" s="0" t="n">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O127" s="0"/>
+      <c r="P127" s="0"/>
+      <c r="Q127" s="0"/>
+      <c r="R127" s="0"/>
+      <c r="S127" s="0"/>
+      <c r="T127" s="0"/>
+    </row>
+    <row r="128" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="n">
         <v>127</v>
       </c>
@@ -5255,29 +6562,39 @@
       <c r="C128" s="0" t="s">
         <v>278</v>
       </c>
-      <c r="D128" s="0" t="s">
+      <c r="D128" s="2" t="s">
         <v>279</v>
       </c>
       <c r="E128" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F128" s="0"/>
+      <c r="G128" s="0"/>
+      <c r="H128" s="0"/>
+      <c r="I128" s="0"/>
+      <c r="J128" s="0"/>
+      <c r="K128" s="0"/>
+      <c r="L128" s="0"/>
+      <c r="M128" s="0"/>
+      <c r="N128" s="0"/>
+      <c r="O128" s="0"/>
       <c r="P128" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="Q128" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R128" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="S128" s="0" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="T128" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="n">
         <v>128</v>
       </c>
@@ -5287,7 +6604,7 @@
       <c r="C129" s="0" t="s">
         <v>280</v>
       </c>
-      <c r="D129" s="0" t="s">
+      <c r="D129" s="2" t="s">
         <v>281</v>
       </c>
       <c r="E129" s="0" t="n">
@@ -5308,6 +6625,8 @@
       <c r="J129" s="0" t="n">
         <v>0.005</v>
       </c>
+      <c r="K129" s="0"/>
+      <c r="L129" s="0"/>
       <c r="M129" s="0" t="n">
         <v>0.0075</v>
       </c>
@@ -5317,8 +6636,13 @@
       <c r="O129" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P129" s="0"/>
+      <c r="Q129" s="0"/>
+      <c r="R129" s="0"/>
+      <c r="S129" s="0"/>
+      <c r="T129" s="0"/>
+    </row>
+    <row r="130" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="n">
         <v>129</v>
       </c>
@@ -5328,7 +6652,7 @@
       <c r="C130" s="0" t="s">
         <v>282</v>
       </c>
-      <c r="D130" s="0" t="s">
+      <c r="D130" s="2" t="s">
         <v>283</v>
       </c>
       <c r="E130" s="0" t="n">
@@ -5343,17 +6667,26 @@
       <c r="H130" s="0" t="n">
         <v>0.08</v>
       </c>
+      <c r="I130" s="0"/>
+      <c r="J130" s="0"/>
+      <c r="K130" s="0"/>
       <c r="L130" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="M130" s="0"/>
+      <c r="N130" s="0"/>
       <c r="O130" s="0" t="s">
         <v>35</v>
       </c>
       <c r="P130" s="0" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+      <c r="Q130" s="0"/>
+      <c r="R130" s="0"/>
+      <c r="S130" s="0"/>
+      <c r="T130" s="0"/>
+    </row>
+    <row r="131" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="n">
         <v>130</v>
       </c>
@@ -5363,7 +6696,7 @@
       <c r="C131" s="0" t="s">
         <v>284</v>
       </c>
-      <c r="D131" s="0" t="s">
+      <c r="D131" s="2" t="s">
         <v>285</v>
       </c>
       <c r="E131" s="0" t="n">
@@ -5381,14 +6714,23 @@
       <c r="I131" s="0" t="n">
         <v>0.012</v>
       </c>
+      <c r="J131" s="0"/>
+      <c r="K131" s="0"/>
       <c r="L131" s="0" t="n">
         <v>0.012</v>
       </c>
+      <c r="M131" s="0"/>
+      <c r="N131" s="0"/>
       <c r="O131" s="0" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P131" s="0"/>
+      <c r="Q131" s="0"/>
+      <c r="R131" s="0"/>
+      <c r="S131" s="0"/>
+      <c r="T131" s="0"/>
+    </row>
+    <row r="132" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="n">
         <v>131</v>
       </c>
@@ -5398,7 +6740,7 @@
       <c r="C132" s="0" t="s">
         <v>286</v>
       </c>
-      <c r="D132" s="0" t="s">
+      <c r="D132" s="2" t="s">
         <v>287</v>
       </c>
       <c r="E132" s="0" t="n">
@@ -5414,13 +6756,23 @@
         <v>0.15</v>
       </c>
       <c r="I132" s="0" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="J132" s="0"/>
+      <c r="K132" s="0"/>
+      <c r="L132" s="0"/>
+      <c r="M132" s="0"/>
+      <c r="N132" s="0"/>
       <c r="O132" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P132" s="0"/>
+      <c r="Q132" s="0"/>
+      <c r="R132" s="0"/>
+      <c r="S132" s="0"/>
+      <c r="T132" s="0"/>
+    </row>
+    <row r="133" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="n">
         <v>132</v>
       </c>
@@ -5430,7 +6782,7 @@
       <c r="C133" s="0" t="s">
         <v>288</v>
       </c>
-      <c r="D133" s="0" t="s">
+      <c r="D133" s="2" t="s">
         <v>289</v>
       </c>
       <c r="E133" s="0" t="n">
@@ -5445,14 +6797,24 @@
       <c r="H133" s="0" t="n">
         <v>0.18</v>
       </c>
+      <c r="I133" s="0"/>
+      <c r="J133" s="0"/>
+      <c r="K133" s="0"/>
       <c r="L133" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="M133" s="0"/>
+      <c r="N133" s="0"/>
       <c r="O133" s="0" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P133" s="0"/>
+      <c r="Q133" s="0"/>
+      <c r="R133" s="0"/>
+      <c r="S133" s="0"/>
+      <c r="T133" s="0"/>
+    </row>
+    <row r="134" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="n">
         <v>133</v>
       </c>
@@ -5462,7 +6824,7 @@
       <c r="C134" s="0" t="s">
         <v>290</v>
       </c>
-      <c r="D134" s="0" t="s">
+      <c r="D134" s="2" t="s">
         <v>291</v>
       </c>
       <c r="E134" s="0" t="n">
@@ -5477,14 +6839,24 @@
       <c r="H134" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="I134" s="0"/>
       <c r="J134" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="K134" s="0"/>
+      <c r="L134" s="0"/>
+      <c r="M134" s="0"/>
+      <c r="N134" s="0"/>
       <c r="O134" s="0" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P134" s="0"/>
+      <c r="Q134" s="0"/>
+      <c r="R134" s="0"/>
+      <c r="S134" s="0"/>
+      <c r="T134" s="0"/>
+    </row>
+    <row r="135" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="n">
         <v>134</v>
       </c>
@@ -5494,7 +6866,7 @@
       <c r="C135" s="0" t="s">
         <v>292</v>
       </c>
-      <c r="D135" s="0" t="s">
+      <c r="D135" s="2" t="s">
         <v>293</v>
       </c>
       <c r="E135" s="0" t="n">
@@ -5507,7 +6879,7 @@
         <v>750</v>
       </c>
       <c r="H135" s="0" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I135" s="0" t="n">
         <v>0.02</v>
@@ -5530,8 +6902,13 @@
       <c r="O135" s="0" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P135" s="0"/>
+      <c r="Q135" s="0"/>
+      <c r="R135" s="0"/>
+      <c r="S135" s="0"/>
+      <c r="T135" s="0"/>
+    </row>
+    <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="n">
         <v>135</v>
       </c>
@@ -5541,20 +6918,33 @@
       <c r="C136" s="0" t="s">
         <v>294</v>
       </c>
-      <c r="D136" s="0" t="s">
+      <c r="D136" s="2" t="s">
         <v>295</v>
       </c>
       <c r="E136" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F136" s="0"/>
+      <c r="G136" s="0"/>
+      <c r="H136" s="0"/>
       <c r="I136" s="0" t="n">
-        <v>0.05</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="J136" s="0"/>
       <c r="K136" s="0" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.005</v>
+      </c>
+      <c r="L136" s="0"/>
+      <c r="M136" s="0"/>
+      <c r="N136" s="0"/>
+      <c r="O136" s="0"/>
+      <c r="P136" s="0"/>
+      <c r="Q136" s="0"/>
+      <c r="R136" s="0"/>
+      <c r="S136" s="0"/>
+      <c r="T136" s="0"/>
+    </row>
+    <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="n">
         <v>136</v>
       </c>
@@ -5564,17 +6954,31 @@
       <c r="C137" s="0" t="s">
         <v>296</v>
       </c>
-      <c r="D137" s="0" t="s">
+      <c r="D137" s="2" t="s">
         <v>297</v>
       </c>
       <c r="E137" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="F137" s="0"/>
+      <c r="G137" s="0"/>
+      <c r="H137" s="0"/>
+      <c r="I137" s="0"/>
+      <c r="J137" s="0"/>
       <c r="K137" s="0" t="n">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L137" s="0"/>
+      <c r="M137" s="0"/>
+      <c r="N137" s="0"/>
+      <c r="O137" s="0"/>
+      <c r="P137" s="0"/>
+      <c r="Q137" s="0"/>
+      <c r="R137" s="0"/>
+      <c r="S137" s="0"/>
+      <c r="T137" s="0"/>
+    </row>
+    <row r="138" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="n">
         <v>137</v>
       </c>
@@ -5584,12 +6988,15 @@
       <c r="C138" s="0" t="s">
         <v>298</v>
       </c>
-      <c r="D138" s="0" t="s">
+      <c r="D138" s="2" t="s">
         <v>299</v>
       </c>
       <c r="E138" s="0" t="n">
         <v>24</v>
       </c>
+      <c r="F138" s="0"/>
+      <c r="G138" s="0"/>
+      <c r="H138" s="0"/>
       <c r="I138" s="0" t="n">
         <v>0.0075</v>
       </c>
@@ -5599,8 +7006,17 @@
       <c r="K138" s="0" t="n">
         <v>0.025</v>
       </c>
-    </row>
-    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L138" s="0"/>
+      <c r="M138" s="0"/>
+      <c r="N138" s="0"/>
+      <c r="O138" s="0"/>
+      <c r="P138" s="0"/>
+      <c r="Q138" s="0"/>
+      <c r="R138" s="0"/>
+      <c r="S138" s="0"/>
+      <c r="T138" s="0"/>
+    </row>
+    <row r="139" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="n">
         <v>138</v>
       </c>
@@ -5610,23 +7026,35 @@
       <c r="C139" s="0" t="s">
         <v>300</v>
       </c>
-      <c r="D139" s="0" t="s">
+      <c r="D139" s="2" t="s">
         <v>301</v>
       </c>
       <c r="E139" s="0" t="n">
         <v>36</v>
       </c>
+      <c r="F139" s="0"/>
+      <c r="G139" s="0"/>
+      <c r="H139" s="0"/>
+      <c r="I139" s="0"/>
+      <c r="J139" s="0"/>
       <c r="K139" s="0" t="n">
         <v>0.025</v>
       </c>
+      <c r="L139" s="0"/>
       <c r="M139" s="0" t="n">
         <v>0.02</v>
       </c>
       <c r="N139" s="0" t="n">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O139" s="0"/>
+      <c r="P139" s="0"/>
+      <c r="Q139" s="0"/>
+      <c r="R139" s="0"/>
+      <c r="S139" s="0"/>
+      <c r="T139" s="0"/>
+    </row>
+    <row r="140" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="n">
         <v>139</v>
       </c>
@@ -5636,17 +7064,31 @@
       <c r="C140" s="0" t="s">
         <v>302</v>
       </c>
-      <c r="D140" s="0" t="s">
+      <c r="D140" s="2" t="s">
         <v>303</v>
       </c>
       <c r="E140" s="0" t="n">
         <v>48</v>
       </c>
+      <c r="F140" s="0"/>
+      <c r="G140" s="0"/>
+      <c r="H140" s="0"/>
+      <c r="I140" s="0"/>
+      <c r="J140" s="0"/>
+      <c r="K140" s="0"/>
+      <c r="L140" s="0"/>
+      <c r="M140" s="0"/>
       <c r="N140" s="0" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.025</v>
+      </c>
+      <c r="O140" s="0"/>
+      <c r="P140" s="0"/>
+      <c r="Q140" s="0"/>
+      <c r="R140" s="0"/>
+      <c r="S140" s="0"/>
+      <c r="T140" s="0"/>
+    </row>
+    <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="n">
         <v>140</v>
       </c>
@@ -5656,20 +7098,33 @@
       <c r="C141" s="0" t="s">
         <v>304</v>
       </c>
-      <c r="D141" s="0" t="s">
+      <c r="D141" s="2" t="s">
         <v>305</v>
       </c>
       <c r="E141" s="0" t="n">
         <v>60</v>
       </c>
+      <c r="F141" s="0"/>
+      <c r="G141" s="0"/>
+      <c r="H141" s="0"/>
+      <c r="I141" s="0"/>
+      <c r="J141" s="0"/>
       <c r="K141" s="0" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="L141" s="0" t="n">
         <v>0.015</v>
       </c>
-    </row>
-    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M141" s="0"/>
+      <c r="N141" s="0"/>
+      <c r="O141" s="0"/>
+      <c r="P141" s="0"/>
+      <c r="Q141" s="0"/>
+      <c r="R141" s="0"/>
+      <c r="S141" s="0"/>
+      <c r="T141" s="0"/>
+    </row>
+    <row r="142" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="n">
         <v>141</v>
       </c>
@@ -5679,7 +7134,7 @@
       <c r="C142" s="0" t="s">
         <v>306</v>
       </c>
-      <c r="D142" s="0" t="s">
+      <c r="D142" s="2" t="s">
         <v>307</v>
       </c>
       <c r="E142" s="0" t="n">
@@ -5694,11 +7149,22 @@
       <c r="H142" s="0" t="n">
         <v>0.025</v>
       </c>
+      <c r="I142" s="0"/>
+      <c r="J142" s="0"/>
+      <c r="K142" s="0"/>
+      <c r="L142" s="0"/>
+      <c r="M142" s="0"/>
+      <c r="N142" s="0"/>
       <c r="O142" s="0" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P142" s="0"/>
+      <c r="Q142" s="0"/>
+      <c r="R142" s="0"/>
+      <c r="S142" s="0"/>
+      <c r="T142" s="0"/>
+    </row>
+    <row r="143" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="n">
         <v>142</v>
       </c>
@@ -5708,7 +7174,7 @@
       <c r="C143" s="0" t="s">
         <v>308</v>
       </c>
-      <c r="D143" s="0" t="s">
+      <c r="D143" s="2" t="s">
         <v>309</v>
       </c>
       <c r="E143" s="0" t="n">
@@ -5726,11 +7192,21 @@
       <c r="I143" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J143" s="0"/>
+      <c r="K143" s="0"/>
+      <c r="L143" s="0"/>
+      <c r="M143" s="0"/>
+      <c r="N143" s="0"/>
       <c r="O143" s="0" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P143" s="0"/>
+      <c r="Q143" s="0"/>
+      <c r="R143" s="0"/>
+      <c r="S143" s="0"/>
+      <c r="T143" s="0"/>
+    </row>
+    <row r="144" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="n">
         <v>143</v>
       </c>
@@ -5740,7 +7216,7 @@
       <c r="C144" s="0" t="s">
         <v>310</v>
       </c>
-      <c r="D144" s="0" t="s">
+      <c r="D144" s="2" t="s">
         <v>311</v>
       </c>
       <c r="E144" s="0" t="n">
@@ -5753,17 +7229,26 @@
         <v>200</v>
       </c>
       <c r="H144" s="0" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="I144" s="0" t="n">
         <v>0.02</v>
       </c>
+      <c r="J144" s="0"/>
+      <c r="K144" s="0"/>
+      <c r="L144" s="0"/>
+      <c r="M144" s="0"/>
       <c r="N144" s="0" t="n">
         <v>0.02</v>
       </c>
       <c r="O144" s="0" t="s">
         <v>91</v>
       </c>
+      <c r="P144" s="0"/>
+      <c r="Q144" s="0"/>
+      <c r="R144" s="0"/>
+      <c r="S144" s="0"/>
+      <c r="T144" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/resources/data-imports/Core Imports/class-specials.xlsx
+++ b/resources/data-imports/Core Imports/class-specials.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="360">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -956,16 +956,162 @@
   </si>
   <si>
     <t xml:space="preserve">Mix medicine, poison, and grave-dust into The line between life and death. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 20,000 specialty damage when casting and attacking, gains 200 damage per level, and reaches 40,000 damage at level 100, adding 20% of your damage stat; it also adds 2% weapon and ring damage per level, reaching 200% at level 100; and it also adds 2% damage stat per level, reaching 200% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flintlock Discipline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime the old flintlock and keep every shot steady under pressure through Flintlock Discipline. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% base damage modifier per level, reaching 100% at level 100; it also adds 0.5% damage stat per level, reaching 50% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salt-Iron Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set your shield and let sea-worn steel carry the worst of the blow through Salt-Iron Guard. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% armour class per level, reaching 150% at level 100; it also adds 1% health per level, reaching 100% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powder Saint Reprisal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Answer betrayal with shield-braced gunfire through Powder Saint Reprisal. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 1,000 specialty damage when attacking, gains 10 damage per level, reaches 2,000 damage at level 100, and adds 5% of your damage stat to the hit; it also adds 0.75% base damage modifier per level, reaching 75% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blackwake Broadside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break the black wake open and make every gunshot count through Blackwake Broadside. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when attacking, gains 50 damage per level, reaches 10,000 damage at level 100, and adds 8% of your damage stat to the hit; it also adds 1% damage stat per level, reaching 100% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corsairs Remedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep bitter medicine under the coat and refuse to fall when the deck turns against you through Corsairs Remedy. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% healing per level, reaching 150% at level 100; it also adds 0.75% health per level, reaching 75% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke Over the Deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cast choking smoke and vanish between gunfire and shieldwork through Smoke Over the Deck. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.5% spell evasion per level, reaching 50% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grave-Tide Volley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let the grave-tide answer and bury doubt under disciplined fire through Grave-Tide Volley. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when attacking, gains 100 damage per level, reaches 20,000 damage at level 100, and adds 10% of your damage stat to the hit; it also adds 1.25% base damage modifier per level, reaching 125% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powder Keg Oath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swear the oath and turn old sea-curses into disciplined violence through Powder Keg Oath. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% damage stat per level, reaching 150% at level 100; it also adds 1% spell damage per level, reaching 100% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iron Keel Stance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant yourself hard and let the enemy break against your footing through Iron Keel Stance. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% armour class per level, reaching 200% at level 100; it also adds 1.5% health per level, reaching 150% at level 100; it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead Mans Parley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Force the enemy into bad odds before the first shot lands through Dead Mans Parley. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drowned Admirals Command</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give the command and make every volley obey the old flag through Drowned Admirals Command. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 25,000 specialty damage when attacking, gains 250 damage per level, reaches 50,000 damage at level 100, and adds 15% of your damage stat to the hit; it also adds 1.5% base damage modifier per level, reaching 150% at level 100; it also adds 1.5% damage stat per level, reaching 150% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Flag Benediction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise the black flag and let the crew fight beneath a terrible promise through Black Flag Benediction. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 75,000 specialty damage when attacking, gains 750 damage per level, reaches 150,000 damage at level 100, and adds 25% of your damage stat to the hit; it also adds 2% base damage modifier per level, reaching 200% at level 100; it also adds 2% armour class per level, reaching 200% at level 100; it also adds 2% health per level, reaching 200% at level 100; it also adds 2% damage stat per level, reaching 200% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wildmark Discipline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark the trail and steady the killing hand through Wildmark Discipline. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1% base damage modifier per level, reaching 100% at level 100; it also adds 0.5% damage stat per level, reaching 50% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oakhide Pact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bind your flesh to old forest bark through Oakhide Pact and endure the hunt longer than the prey. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% armour class per level, reaching 150% at level 100; it also adds 1% health per level, reaching 100% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devils Piercing Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set the bowstring against the devil's mark through Devils Piercing Focus. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 1,000 specialty damage when attacking, gains 10 damage per level, reaches 2,000 damage at level 100, and adds 5% of your damage stat to the hit; it also adds 0.75% base damage modifier per level, reaching 75% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beast Stomp Initiate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive the hammer down and teach the ground to answer through Beast Stomp Initiate. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 5,000 specialty damage when attacking, gains 50 damage per level, reaches 10,000 damage at level 100, and adds 8% of your damage stat to the hit; it also adds 1% base damage modifier per level, reaching 100% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood Trail Instinct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read the enemy's weakness in every footprint through Blood Trail Instinct. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.5% healing reduction per level, reaching 50% at level 100; it also adds 0.5% skill reduction per level, reaching 50% at level 100; it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thornhide Recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let pain close over like thorns around wounded flesh through Thornhide Recovery. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.5% healing per level, reaching 150% at level 100; it also adds 0.75% health per level, reaching 75% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savage Draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw with the patience of the wild and release with killing certainty through Savage Draw. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 1.25% base damage modifier per level, reaching 125% at level 100; it also adds 1% damage stat per level, reaching 100% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earthshaker Posture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant both feet and let the mountain lend its spine through Earthshaker Posture. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 2% armour class per level, reaching 200% at level 100; it also adds 0.5% affix damage reduction per level, reaching 50% at level 100; it also adds 0.5% resistance reduction per level, reaching 50% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hellhorn Volley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loose a brutal volley under the sign of the horned beast through Hellhorn Volley. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 10,000 specialty damage when attacking, gains 100 damage per level, reaches 20,000 damage at level 100, and adds 10% of your damage stat to the hit; it also adds 1.25% base damage modifier per level, reaching 125% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predators Silence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still the enemy's answer before the strike lands through Predators Silence. The lesson can still be carried into another class when equipped. As you level this specialty, it adds 0.75% spell evasion per level, reaching 75% at level 100; it also adds 0.75% skill reduction per level, reaching 75% at level 100; it also adds 0.5% healing reduction per level, reaching 50% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apex Hunt Command</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Command the hunt at its cruelest height through Apex Hunt Command. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 25,000 specialty damage when attacking, gains 250 damage per level, reaches 50,000 damage at level 100, and adds 15% of your damage stat to the hit; it also adds 1.5% base damage modifier per level, reaching 150% at level 100; it also adds 1.5% damage stat per level, reaching 150% at level 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worldbreaker Roar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let the beast inside split the field with one final command through Worldbreaker Roar. The lesson can still be carried into another class when equipped. As you level this specialty, it deals 75,000 specialty damage when attacking, gains 750 damage per level, reaches 150,000 damage at level 100, and adds 25% of your damage stat to the hit; it also adds 2% base damage modifier per level, reaching 200% at level 100; it also adds 2% armour class per level, reaching 200% at level 100; it also adds 2% health per level, reaching 200% at level 100; it also adds 2% damage stat per level, reaching 200% at level 100.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.####"/>
+    <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -987,6 +1133,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1035,7 +1187,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1044,8 +1196,36 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1241,7 +1421,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T144"/>
+  <dimension ref="A1:T168"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.57"/>
@@ -1329,5926 +1509,5334 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="0"/>
-      <c r="G2" s="0"/>
-      <c r="H2" s="0"/>
-      <c r="I2" s="0"/>
-      <c r="J2" s="0"/>
-      <c r="K2" s="0"/>
-      <c r="L2" s="0"/>
-      <c r="M2" s="0"/>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="O2" s="0" t="s">
+      <c r="O2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="0"/>
-      <c r="Q2" s="0"/>
-      <c r="R2" s="0"/>
-      <c r="S2" s="0"/>
-      <c r="T2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="0"/>
-      <c r="G3" s="0"/>
-      <c r="H3" s="0"/>
-      <c r="I3" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J3" s="0"/>
-      <c r="K3" s="0"/>
-      <c r="L3" s="0"/>
-      <c r="M3" s="0"/>
-      <c r="N3" s="0"/>
-      <c r="O3" s="0" t="s">
+      <c r="I3" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P3" s="0"/>
-      <c r="Q3" s="0"/>
-      <c r="R3" s="0"/>
-      <c r="S3" s="0"/>
-      <c r="T3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F4" s="0"/>
-      <c r="G4" s="0"/>
-      <c r="H4" s="0"/>
-      <c r="I4" s="0"/>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="K4" s="0"/>
-      <c r="L4" s="0"/>
-      <c r="M4" s="0"/>
-      <c r="N4" s="0"/>
-      <c r="O4" s="0" t="s">
+      <c r="O4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="0"/>
-      <c r="Q4" s="0"/>
-      <c r="R4" s="0"/>
-      <c r="S4" s="0"/>
-      <c r="T4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F5" s="0"/>
-      <c r="G5" s="0"/>
-      <c r="H5" s="0"/>
-      <c r="I5" s="0"/>
-      <c r="J5" s="0"/>
-      <c r="K5" s="0"/>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="M5" s="0"/>
-      <c r="N5" s="0"/>
-      <c r="O5" s="0" t="s">
+      <c r="O5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="0"/>
-      <c r="Q5" s="0"/>
-      <c r="R5" s="0"/>
-      <c r="S5" s="0"/>
-      <c r="T5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F6" s="0"/>
-      <c r="G6" s="0"/>
-      <c r="H6" s="0"/>
-      <c r="I6" s="0"/>
-      <c r="J6" s="0"/>
-      <c r="K6" s="0"/>
-      <c r="L6" s="0"/>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="N6" s="0"/>
-      <c r="O6" s="0" t="s">
+      <c r="O6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P6" s="0"/>
-      <c r="Q6" s="0"/>
-      <c r="R6" s="0"/>
-      <c r="S6" s="0"/>
-      <c r="T6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F7" s="0"/>
-      <c r="G7" s="0"/>
-      <c r="H7" s="0"/>
-      <c r="I7" s="0"/>
-      <c r="J7" s="0"/>
-      <c r="K7" s="0"/>
-      <c r="L7" s="0"/>
-      <c r="M7" s="0"/>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="O7" s="0" t="s">
+      <c r="O7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P7" s="0"/>
-      <c r="Q7" s="0"/>
-      <c r="R7" s="0"/>
-      <c r="S7" s="0"/>
-      <c r="T7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="I8" s="0"/>
-      <c r="J8" s="0"/>
-      <c r="K8" s="0"/>
-      <c r="L8" s="0"/>
-      <c r="M8" s="0"/>
-      <c r="N8" s="0"/>
-      <c r="O8" s="0" t="s">
+      <c r="O8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P8" s="0"/>
-      <c r="Q8" s="0"/>
-      <c r="R8" s="0"/>
-      <c r="S8" s="0"/>
-      <c r="T8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="I9" s="0"/>
-      <c r="J9" s="0"/>
-      <c r="K9" s="0"/>
-      <c r="L9" s="0"/>
-      <c r="M9" s="0"/>
-      <c r="N9" s="0"/>
-      <c r="O9" s="0" t="s">
+      <c r="O9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P9" s="0"/>
-      <c r="Q9" s="0"/>
-      <c r="R9" s="0"/>
-      <c r="S9" s="0"/>
-      <c r="T9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I10" s="0"/>
-      <c r="J10" s="0"/>
-      <c r="K10" s="0"/>
-      <c r="L10" s="0"/>
-      <c r="M10" s="0"/>
-      <c r="N10" s="0"/>
-      <c r="O10" s="0" t="s">
+      <c r="O10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P10" s="0"/>
-      <c r="Q10" s="0"/>
-      <c r="R10" s="0"/>
-      <c r="S10" s="0"/>
-      <c r="T10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="I11" s="0"/>
-      <c r="J11" s="0" t="n">
+      <c r="J11" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="K11" s="0"/>
-      <c r="L11" s="0"/>
-      <c r="M11" s="0"/>
-      <c r="N11" s="0"/>
-      <c r="O11" s="0" t="s">
+      <c r="O11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="0"/>
-      <c r="R11" s="0"/>
-      <c r="S11" s="0"/>
-      <c r="T11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="J12" s="0"/>
-      <c r="K12" s="0"/>
-      <c r="L12" s="0"/>
-      <c r="M12" s="0"/>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="O12" s="0"/>
-      <c r="P12" s="0"/>
-      <c r="Q12" s="0"/>
-      <c r="R12" s="0"/>
-      <c r="S12" s="0"/>
-      <c r="T12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F13" s="0"/>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0" t="n">
+      <c r="J13" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="K13" s="0"/>
-      <c r="L13" s="0"/>
-      <c r="M13" s="0"/>
-      <c r="N13" s="0"/>
-      <c r="O13" s="0"/>
-      <c r="P13" s="0"/>
-      <c r="Q13" s="0"/>
-      <c r="R13" s="0"/>
-      <c r="S13" s="0"/>
-      <c r="T13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
-      <c r="I14" s="0"/>
-      <c r="J14" s="0"/>
-      <c r="K14" s="0" t="n">
+      <c r="K14" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="L14" s="0"/>
-      <c r="M14" s="0"/>
-      <c r="N14" s="0"/>
-      <c r="O14" s="0"/>
-      <c r="P14" s="0"/>
-      <c r="Q14" s="0"/>
-      <c r="R14" s="0"/>
-      <c r="S14" s="0"/>
-      <c r="T14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
-      <c r="I15" s="0"/>
-      <c r="J15" s="0"/>
-      <c r="K15" s="0"/>
-      <c r="L15" s="0" t="n">
+      <c r="L15" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="M15" s="0"/>
-      <c r="N15" s="0"/>
-      <c r="O15" s="0"/>
-      <c r="P15" s="0"/>
-      <c r="Q15" s="0"/>
-      <c r="R15" s="0"/>
-      <c r="S15" s="0"/>
-      <c r="T15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F16" s="0"/>
-      <c r="G16" s="0"/>
-      <c r="H16" s="0"/>
-      <c r="I16" s="0"/>
-      <c r="J16" s="0"/>
-      <c r="K16" s="0"/>
-      <c r="L16" s="0"/>
-      <c r="M16" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N16" s="0"/>
-      <c r="O16" s="0"/>
-      <c r="P16" s="0"/>
-      <c r="Q16" s="0"/>
-      <c r="R16" s="0"/>
-      <c r="S16" s="0"/>
-      <c r="T16" s="0"/>
+      <c r="M16" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="I17" s="0"/>
-      <c r="J17" s="0"/>
-      <c r="K17" s="0"/>
-      <c r="L17" s="0"/>
-      <c r="M17" s="0"/>
-      <c r="N17" s="0"/>
-      <c r="O17" s="0" t="s">
+      <c r="O17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P17" s="0"/>
-      <c r="Q17" s="0"/>
-      <c r="R17" s="0"/>
-      <c r="S17" s="0"/>
-      <c r="T17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="H18" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I18" s="0"/>
-      <c r="J18" s="0"/>
-      <c r="K18" s="0"/>
-      <c r="L18" s="0"/>
-      <c r="M18" s="0"/>
-      <c r="N18" s="0"/>
-      <c r="O18" s="0" t="s">
+      <c r="O18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P18" s="0"/>
-      <c r="Q18" s="0"/>
-      <c r="R18" s="0"/>
-      <c r="S18" s="0"/>
-      <c r="T18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I19" s="0"/>
-      <c r="J19" s="0"/>
-      <c r="K19" s="0"/>
-      <c r="L19" s="0" t="n">
+      <c r="L19" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="M19" s="0"/>
-      <c r="N19" s="0"/>
-      <c r="O19" s="0" t="s">
+      <c r="O19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P19" s="0"/>
-      <c r="Q19" s="0"/>
-      <c r="R19" s="0"/>
-      <c r="S19" s="0"/>
-      <c r="T19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="0"/>
-      <c r="G20" s="0"/>
-      <c r="H20" s="0"/>
-      <c r="I20" s="0"/>
-      <c r="J20" s="0"/>
-      <c r="K20" s="0"/>
-      <c r="L20" s="0"/>
-      <c r="M20" s="0" t="n">
+      <c r="M20" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="N20" s="0"/>
-      <c r="O20" s="0"/>
-      <c r="P20" s="0"/>
-      <c r="Q20" s="0"/>
-      <c r="R20" s="0"/>
-      <c r="S20" s="0"/>
-      <c r="T20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F21" s="0"/>
-      <c r="G21" s="0"/>
-      <c r="H21" s="0"/>
-      <c r="I21" s="0"/>
-      <c r="J21" s="0"/>
-      <c r="K21" s="0"/>
-      <c r="L21" s="0"/>
-      <c r="M21" s="0"/>
-      <c r="N21" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O21" s="0"/>
-      <c r="P21" s="0"/>
-      <c r="Q21" s="0"/>
-      <c r="R21" s="0"/>
-      <c r="S21" s="0"/>
-      <c r="T21" s="0"/>
+      <c r="N21" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F22" s="0"/>
-      <c r="G22" s="0"/>
-      <c r="H22" s="0"/>
-      <c r="I22" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J22" s="0"/>
-      <c r="K22" s="0"/>
-      <c r="L22" s="0" t="n">
+      <c r="I22" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L22" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="M22" s="0" t="n">
+      <c r="M22" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="N22" s="0"/>
-      <c r="O22" s="0"/>
-      <c r="P22" s="0"/>
-      <c r="Q22" s="0"/>
-      <c r="R22" s="0"/>
-      <c r="S22" s="0"/>
-      <c r="T22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F23" s="0"/>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
-      <c r="I23" s="0"/>
-      <c r="J23" s="0"/>
-      <c r="K23" s="0" t="n">
+      <c r="K23" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="L23" s="0"/>
-      <c r="M23" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N23" s="0" t="n">
+      <c r="M23" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N23" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="O23" s="0"/>
-      <c r="P23" s="0"/>
-      <c r="Q23" s="0"/>
-      <c r="R23" s="0"/>
-      <c r="S23" s="0"/>
-      <c r="T23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>69</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F24" s="0"/>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
-      <c r="I24" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J24" s="0"/>
-      <c r="K24" s="0"/>
-      <c r="L24" s="0"/>
-      <c r="M24" s="0"/>
-      <c r="N24" s="0" t="n">
+      <c r="I24" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N24" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="O24" s="0"/>
-      <c r="P24" s="0"/>
-      <c r="Q24" s="0"/>
-      <c r="R24" s="0"/>
-      <c r="S24" s="0"/>
-      <c r="T24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F25" s="0"/>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-      <c r="I25" s="0"/>
-      <c r="J25" s="0" t="n">
+      <c r="J25" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="K25" s="0"/>
-      <c r="L25" s="0"/>
-      <c r="M25" s="0" t="n">
+      <c r="M25" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="N25" s="0"/>
-      <c r="O25" s="0"/>
-      <c r="P25" s="0"/>
-      <c r="Q25" s="0"/>
-      <c r="R25" s="0"/>
-      <c r="S25" s="0"/>
-      <c r="T25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="F26" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="G26" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="H26" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I26" s="0"/>
-      <c r="J26" s="0"/>
-      <c r="K26" s="0"/>
-      <c r="L26" s="0"/>
-      <c r="M26" s="0"/>
-      <c r="N26" s="0"/>
-      <c r="O26" s="0" t="s">
+      <c r="O26" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P26" s="0"/>
-      <c r="Q26" s="0"/>
-      <c r="R26" s="0"/>
-      <c r="S26" s="0"/>
-      <c r="T26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="1" t="n">
         <v>15000</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="G27" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I27" s="0"/>
-      <c r="J27" s="0" t="n">
+      <c r="J27" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="K27" s="0"/>
-      <c r="L27" s="0"/>
-      <c r="M27" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N27" s="0"/>
-      <c r="O27" s="0" t="s">
+      <c r="M27" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P27" s="0"/>
-      <c r="Q27" s="0"/>
-      <c r="R27" s="0"/>
-      <c r="S27" s="0"/>
-      <c r="T27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="F28" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="G28" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I28" s="0"/>
-      <c r="J28" s="0" t="n">
+      <c r="J28" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="K28" s="0"/>
-      <c r="L28" s="0"/>
-      <c r="M28" s="0"/>
-      <c r="N28" s="0"/>
-      <c r="O28" s="0" t="s">
+      <c r="O28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P28" s="0"/>
-      <c r="Q28" s="0"/>
-      <c r="R28" s="0"/>
-      <c r="S28" s="0"/>
-      <c r="T28" s="0"/>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="0"/>
-      <c r="G29" s="0"/>
-      <c r="H29" s="0"/>
-      <c r="I29" s="0" t="n">
+      <c r="I29" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="J29" s="0"/>
-      <c r="K29" s="0"/>
-      <c r="L29" s="0"/>
-      <c r="M29" s="0" t="n">
+      <c r="M29" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="N29" s="0"/>
-      <c r="O29" s="0"/>
-      <c r="P29" s="0"/>
-      <c r="Q29" s="0"/>
-      <c r="R29" s="0"/>
-      <c r="S29" s="0"/>
-      <c r="T29" s="0"/>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F30" s="0" t="n">
+      <c r="F30" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G30" s="0" t="n">
+      <c r="G30" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="H30" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="I30" s="0"/>
-      <c r="J30" s="0" t="n">
+      <c r="J30" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="K30" s="0"/>
-      <c r="L30" s="0"/>
-      <c r="M30" s="0"/>
-      <c r="N30" s="0"/>
-      <c r="O30" s="0" t="s">
+      <c r="O30" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P30" s="0"/>
-      <c r="Q30" s="0"/>
-      <c r="R30" s="0"/>
-      <c r="S30" s="0"/>
-      <c r="T30" s="0"/>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E31" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F31" s="0"/>
-      <c r="G31" s="0"/>
-      <c r="H31" s="0"/>
-      <c r="I31" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J31" s="0"/>
-      <c r="K31" s="0" t="n">
+      <c r="I31" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K31" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="L31" s="0"/>
-      <c r="M31" s="0"/>
-      <c r="N31" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O31" s="0"/>
-      <c r="P31" s="0"/>
-      <c r="Q31" s="0"/>
-      <c r="R31" s="0"/>
-      <c r="S31" s="0"/>
-      <c r="T31" s="0"/>
+      <c r="N31" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="A32" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F32" s="0"/>
-      <c r="G32" s="0"/>
-      <c r="H32" s="0"/>
-      <c r="I32" s="0"/>
-      <c r="J32" s="0"/>
-      <c r="K32" s="0" t="n">
+      <c r="K32" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="L32" s="0"/>
-      <c r="M32" s="0" t="n">
+      <c r="M32" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="N32" s="0"/>
-      <c r="O32" s="0"/>
-      <c r="P32" s="0"/>
-      <c r="Q32" s="0"/>
-      <c r="R32" s="0"/>
-      <c r="S32" s="0"/>
-      <c r="T32" s="0"/>
     </row>
     <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="A33" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F33" s="0"/>
-      <c r="G33" s="0"/>
-      <c r="H33" s="0"/>
-      <c r="I33" s="0" t="n">
+      <c r="I33" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="J33" s="0" t="n">
+      <c r="J33" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="K33" s="0" t="n">
+      <c r="K33" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="L33" s="0"/>
-      <c r="M33" s="0" t="n">
+      <c r="M33" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="N33" s="0" t="n">
+      <c r="N33" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O33" s="0"/>
-      <c r="P33" s="0"/>
-      <c r="Q33" s="0"/>
-      <c r="R33" s="0"/>
-      <c r="S33" s="0"/>
-      <c r="T33" s="0"/>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F34" s="0" t="n">
+      <c r="F34" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G34" s="0" t="n">
+      <c r="G34" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H34" s="0" t="n">
+      <c r="H34" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I34" s="0"/>
-      <c r="J34" s="0"/>
-      <c r="K34" s="0" t="n">
+      <c r="K34" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="L34" s="0"/>
-      <c r="M34" s="0"/>
-      <c r="N34" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O34" s="0" t="s">
+      <c r="N34" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="P34" s="0"/>
-      <c r="Q34" s="0"/>
-      <c r="R34" s="0"/>
-      <c r="S34" s="0"/>
-      <c r="T34" s="0"/>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+      <c r="A35" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>92</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F35" s="0" t="n">
+      <c r="F35" s="1" t="n">
         <v>15000</v>
       </c>
-      <c r="G35" s="0" t="n">
+      <c r="G35" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="H35" s="0" t="n">
+      <c r="H35" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="I35" s="0" t="n">
+      <c r="I35" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="J35" s="0"/>
-      <c r="K35" s="0"/>
-      <c r="L35" s="0"/>
-      <c r="M35" s="0"/>
-      <c r="N35" s="0"/>
-      <c r="O35" s="0" t="s">
+      <c r="O35" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P35" s="0"/>
-      <c r="Q35" s="0"/>
-      <c r="R35" s="0"/>
-      <c r="S35" s="0"/>
-      <c r="T35" s="0"/>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F36" s="0" t="n">
+      <c r="F36" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="G36" s="0" t="n">
+      <c r="G36" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="H36" s="0" t="n">
+      <c r="H36" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I36" s="0"/>
-      <c r="J36" s="0"/>
-      <c r="K36" s="0"/>
-      <c r="L36" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M36" s="0"/>
-      <c r="N36" s="0"/>
-      <c r="O36" s="0" t="s">
+      <c r="L36" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P36" s="0"/>
-      <c r="Q36" s="0"/>
-      <c r="R36" s="0"/>
-      <c r="S36" s="0"/>
-      <c r="T36" s="0"/>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+      <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F37" s="0" t="n">
+      <c r="F37" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="G37" s="0" t="n">
+      <c r="G37" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="H37" s="0" t="n">
+      <c r="H37" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I37" s="0"/>
-      <c r="J37" s="0" t="n">
+      <c r="J37" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="K37" s="0" t="n">
+      <c r="K37" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="L37" s="0"/>
-      <c r="M37" s="0"/>
-      <c r="N37" s="0"/>
-      <c r="O37" s="0" t="s">
+      <c r="O37" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P37" s="0"/>
-      <c r="Q37" s="0"/>
-      <c r="R37" s="0"/>
-      <c r="S37" s="0"/>
-      <c r="T37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="0"/>
-      <c r="G38" s="0"/>
-      <c r="H38" s="0"/>
-      <c r="I38" s="0"/>
-      <c r="J38" s="0"/>
-      <c r="K38" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L38" s="0"/>
-      <c r="M38" s="0"/>
-      <c r="N38" s="0"/>
-      <c r="O38" s="0"/>
-      <c r="P38" s="0"/>
-      <c r="Q38" s="0"/>
-      <c r="R38" s="0"/>
-      <c r="S38" s="0"/>
-      <c r="T38" s="0"/>
+      <c r="K38" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>100</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F39" s="0"/>
-      <c r="G39" s="0"/>
-      <c r="H39" s="0"/>
-      <c r="I39" s="0"/>
-      <c r="J39" s="0" t="n">
+      <c r="J39" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="K39" s="0" t="n">
+      <c r="K39" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="L39" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M39" s="0"/>
-      <c r="N39" s="0"/>
-      <c r="O39" s="0"/>
-      <c r="P39" s="0"/>
-      <c r="Q39" s="0"/>
-      <c r="R39" s="0"/>
-      <c r="S39" s="0"/>
-      <c r="T39" s="0"/>
+      <c r="L39" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+      <c r="A40" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F40" s="0" t="n">
+      <c r="F40" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G40" s="0" t="n">
+      <c r="G40" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H40" s="0" t="n">
+      <c r="H40" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="I40" s="0"/>
-      <c r="J40" s="0"/>
-      <c r="K40" s="0"/>
-      <c r="L40" s="0"/>
-      <c r="M40" s="0"/>
-      <c r="N40" s="0" t="n">
+      <c r="N40" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="O40" s="0" t="s">
+      <c r="O40" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P40" s="0"/>
-      <c r="Q40" s="0"/>
-      <c r="R40" s="0"/>
-      <c r="S40" s="0"/>
-      <c r="T40" s="0"/>
     </row>
     <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+      <c r="A41" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>104</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F41" s="0"/>
-      <c r="G41" s="0"/>
-      <c r="H41" s="0"/>
-      <c r="I41" s="0" t="n">
+      <c r="I41" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="J41" s="0" t="n">
+      <c r="J41" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="K41" s="0" t="n">
+      <c r="K41" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="L41" s="0"/>
-      <c r="M41" s="0" t="n">
+      <c r="M41" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="N41" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O41" s="0"/>
-      <c r="P41" s="0"/>
-      <c r="Q41" s="0"/>
-      <c r="R41" s="0"/>
-      <c r="S41" s="0"/>
-      <c r="T41" s="0"/>
+      <c r="N41" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+      <c r="A42" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>106</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F42" s="0" t="n">
+      <c r="F42" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G42" s="0" t="n">
+      <c r="G42" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H42" s="0" t="n">
+      <c r="H42" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I42" s="0"/>
-      <c r="J42" s="0"/>
-      <c r="K42" s="0"/>
-      <c r="L42" s="0"/>
-      <c r="M42" s="0"/>
-      <c r="N42" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O42" s="0" t="s">
+      <c r="N42" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="P42" s="0"/>
-      <c r="Q42" s="0"/>
-      <c r="R42" s="0"/>
-      <c r="S42" s="0"/>
-      <c r="T42" s="0"/>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+      <c r="A43" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F43" s="0" t="n">
+      <c r="F43" s="1" t="n">
         <v>15000</v>
       </c>
-      <c r="G43" s="0" t="n">
+      <c r="G43" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="H43" s="0" t="n">
+      <c r="H43" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I43" s="0" t="n">
+      <c r="I43" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="J43" s="0"/>
-      <c r="K43" s="0"/>
-      <c r="L43" s="0" t="n">
+      <c r="L43" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="M43" s="0"/>
-      <c r="N43" s="0"/>
-      <c r="O43" s="0" t="s">
+      <c r="O43" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P43" s="0"/>
-      <c r="Q43" s="0"/>
-      <c r="R43" s="0"/>
-      <c r="S43" s="0"/>
-      <c r="T43" s="0"/>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+      <c r="A44" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="C44" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F44" s="0" t="n">
+      <c r="F44" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="G44" s="0" t="n">
+      <c r="G44" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="H44" s="0" t="n">
+      <c r="H44" s="1" t="n">
         <v>0.22</v>
       </c>
-      <c r="I44" s="0"/>
-      <c r="J44" s="0"/>
-      <c r="K44" s="0" t="n">
+      <c r="K44" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="L44" s="0"/>
-      <c r="M44" s="0"/>
-      <c r="N44" s="0"/>
-      <c r="O44" s="0" t="s">
+      <c r="O44" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P44" s="0"/>
-      <c r="Q44" s="0"/>
-      <c r="R44" s="0"/>
-      <c r="S44" s="0"/>
-      <c r="T44" s="0"/>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+      <c r="A45" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="C45" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E45" s="0" t="n">
+      <c r="E45" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F45" s="0" t="n">
+      <c r="F45" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G45" s="0" t="n">
+      <c r="G45" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H45" s="0" t="n">
+      <c r="H45" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I45" s="0"/>
-      <c r="J45" s="0"/>
-      <c r="K45" s="0" t="n">
+      <c r="K45" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="L45" s="0"/>
-      <c r="M45" s="0"/>
-      <c r="N45" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O45" s="0" t="s">
+      <c r="N45" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O45" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="P45" s="0"/>
-      <c r="Q45" s="0"/>
-      <c r="R45" s="0"/>
-      <c r="S45" s="0"/>
-      <c r="T45" s="0"/>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+      <c r="A46" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E46" s="0" t="n">
+      <c r="E46" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F46" s="0" t="n">
+      <c r="F46" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="G46" s="0" t="n">
+      <c r="G46" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="H46" s="0" t="n">
+      <c r="H46" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="I46" s="0"/>
-      <c r="J46" s="0"/>
-      <c r="K46" s="0"/>
-      <c r="L46" s="0"/>
-      <c r="M46" s="0"/>
-      <c r="N46" s="0"/>
-      <c r="O46" s="0" t="s">
+      <c r="O46" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P46" s="0"/>
-      <c r="Q46" s="0"/>
-      <c r="R46" s="0"/>
-      <c r="S46" s="0"/>
-      <c r="T46" s="0"/>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+      <c r="A47" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" s="1" t="s">
         <v>116</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E47" s="0" t="n">
+      <c r="E47" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="0" t="n">
+      <c r="F47" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="G47" s="0" t="n">
+      <c r="G47" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H47" s="0" t="n">
+      <c r="H47" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="I47" s="0" t="n">
+      <c r="I47" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="J47" s="0"/>
-      <c r="K47" s="0"/>
-      <c r="L47" s="0"/>
-      <c r="M47" s="0"/>
-      <c r="N47" s="0" t="n">
+      <c r="N47" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O47" s="0" t="s">
+      <c r="O47" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P47" s="0"/>
-      <c r="Q47" s="0"/>
-      <c r="R47" s="0"/>
-      <c r="S47" s="0"/>
-      <c r="T47" s="0"/>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+      <c r="A48" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" s="1" t="s">
         <v>118</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E48" s="0" t="n">
+      <c r="E48" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F48" s="0" t="n">
+      <c r="F48" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="G48" s="0" t="n">
+      <c r="G48" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="H48" s="0" t="n">
+      <c r="H48" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="I48" s="0"/>
-      <c r="J48" s="0"/>
-      <c r="K48" s="0"/>
-      <c r="L48" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M48" s="0"/>
-      <c r="N48" s="0" t="n">
+      <c r="L48" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N48" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O48" s="0" t="s">
+      <c r="O48" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="P48" s="0"/>
-      <c r="Q48" s="0"/>
-      <c r="R48" s="0"/>
-      <c r="S48" s="0"/>
-      <c r="T48" s="0"/>
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+      <c r="A49" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C49" s="0" t="s">
+      <c r="C49" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E49" s="0" t="n">
+      <c r="E49" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F49" s="0"/>
-      <c r="G49" s="0"/>
-      <c r="H49" s="0"/>
-      <c r="I49" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J49" s="0"/>
-      <c r="K49" s="0"/>
-      <c r="L49" s="0"/>
-      <c r="M49" s="0" t="n">
+      <c r="I49" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M49" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="N49" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O49" s="0"/>
-      <c r="P49" s="0"/>
-      <c r="Q49" s="0"/>
-      <c r="R49" s="0"/>
-      <c r="S49" s="0"/>
-      <c r="T49" s="0"/>
+      <c r="N49" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
+      <c r="A50" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C50" s="0" t="s">
+      <c r="C50" s="1" t="s">
         <v>122</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E50" s="0" t="n">
+      <c r="E50" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F50" s="0" t="n">
+      <c r="F50" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G50" s="0" t="n">
+      <c r="G50" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H50" s="0" t="n">
+      <c r="H50" s="1" t="n">
         <v>0.14</v>
       </c>
-      <c r="I50" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J50" s="0"/>
-      <c r="K50" s="0"/>
-      <c r="L50" s="0"/>
-      <c r="M50" s="0"/>
-      <c r="N50" s="0"/>
-      <c r="O50" s="0" t="s">
+      <c r="I50" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O50" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P50" s="0"/>
-      <c r="Q50" s="0"/>
-      <c r="R50" s="0"/>
-      <c r="S50" s="0"/>
-      <c r="T50" s="0"/>
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+      <c r="A51" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C51" s="0" t="s">
+      <c r="C51" s="1" t="s">
         <v>124</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E51" s="0" t="n">
+      <c r="E51" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F51" s="0"/>
-      <c r="G51" s="0"/>
-      <c r="H51" s="0"/>
-      <c r="I51" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J51" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="K51" s="0"/>
-      <c r="L51" s="0"/>
-      <c r="M51" s="0" t="n">
+      <c r="I51" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M51" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="N51" s="0" t="n">
+      <c r="N51" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="O51" s="0"/>
-      <c r="P51" s="0"/>
-      <c r="Q51" s="0"/>
-      <c r="R51" s="0"/>
-      <c r="S51" s="0"/>
-      <c r="T51" s="0"/>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
+      <c r="A52" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C52" s="0" t="s">
+      <c r="C52" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E52" s="0" t="n">
+      <c r="E52" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F52" s="0" t="n">
+      <c r="F52" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G52" s="0" t="n">
+      <c r="G52" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H52" s="0" t="n">
+      <c r="H52" s="1" t="n">
         <v>0.18</v>
       </c>
-      <c r="I52" s="0"/>
-      <c r="J52" s="0"/>
-      <c r="K52" s="0"/>
-      <c r="L52" s="0"/>
-      <c r="M52" s="0"/>
-      <c r="N52" s="0"/>
-      <c r="O52" s="0" t="s">
+      <c r="O52" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P52" s="0"/>
-      <c r="Q52" s="0"/>
-      <c r="R52" s="0"/>
-      <c r="S52" s="0"/>
-      <c r="T52" s="0"/>
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="n">
+      <c r="A53" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C53" s="0" t="s">
+      <c r="C53" s="1" t="s">
         <v>128</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E53" s="0" t="n">
+      <c r="E53" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F53" s="0" t="n">
+      <c r="F53" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="G53" s="0" t="n">
+      <c r="G53" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="H53" s="0" t="n">
+      <c r="H53" s="1" t="n">
         <v>0.22</v>
       </c>
-      <c r="I53" s="0"/>
-      <c r="J53" s="0"/>
-      <c r="K53" s="0"/>
-      <c r="L53" s="0"/>
-      <c r="M53" s="0"/>
-      <c r="N53" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O53" s="0" t="s">
+      <c r="N53" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O53" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P53" s="0"/>
-      <c r="Q53" s="0"/>
-      <c r="R53" s="0"/>
-      <c r="S53" s="0"/>
-      <c r="T53" s="0"/>
     </row>
     <row r="54" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="n">
+      <c r="A54" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C54" s="0" t="s">
+      <c r="C54" s="1" t="s">
         <v>130</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E54" s="0" t="n">
+      <c r="E54" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F54" s="0" t="n">
+      <c r="F54" s="1" t="n">
         <v>45000</v>
       </c>
-      <c r="G54" s="0" t="n">
+      <c r="G54" s="1" t="n">
         <v>450</v>
       </c>
-      <c r="H54" s="0" t="n">
+      <c r="H54" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I54" s="0" t="n">
+      <c r="I54" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="J54" s="0"/>
-      <c r="K54" s="0"/>
-      <c r="L54" s="0"/>
-      <c r="M54" s="0" t="n">
+      <c r="M54" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="N54" s="0" t="n">
+      <c r="N54" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O54" s="0" t="s">
+      <c r="O54" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P54" s="0"/>
-      <c r="Q54" s="0"/>
-      <c r="R54" s="0"/>
-      <c r="S54" s="0"/>
-      <c r="T54" s="0"/>
     </row>
     <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="n">
+      <c r="A55" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C55" s="0" t="s">
+      <c r="C55" s="1" t="s">
         <v>132</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E55" s="0" t="n">
+      <c r="E55" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F55" s="0" t="n">
+      <c r="F55" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G55" s="0" t="n">
+      <c r="G55" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H55" s="0" t="n">
+      <c r="H55" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I55" s="0"/>
-      <c r="J55" s="0"/>
-      <c r="K55" s="0"/>
-      <c r="L55" s="0"/>
-      <c r="M55" s="0"/>
-      <c r="N55" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O55" s="0" t="s">
+      <c r="N55" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O55" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P55" s="0"/>
-      <c r="Q55" s="0"/>
-      <c r="R55" s="0"/>
-      <c r="S55" s="0"/>
-      <c r="T55" s="0"/>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="n">
+      <c r="A56" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C56" s="0" t="s">
+      <c r="C56" s="1" t="s">
         <v>134</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E56" s="0" t="n">
+      <c r="E56" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="0"/>
-      <c r="G56" s="0"/>
-      <c r="H56" s="0"/>
-      <c r="I56" s="0" t="n">
+      <c r="I56" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="J56" s="0"/>
-      <c r="K56" s="0"/>
-      <c r="L56" s="0"/>
-      <c r="M56" s="0"/>
-      <c r="N56" s="0"/>
-      <c r="O56" s="0"/>
-      <c r="P56" s="0"/>
-      <c r="Q56" s="0"/>
-      <c r="R56" s="0"/>
-      <c r="S56" s="0"/>
-      <c r="T56" s="0"/>
     </row>
     <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="n">
+      <c r="A57" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C57" s="0" t="s">
+      <c r="C57" s="1" t="s">
         <v>136</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E57" s="0" t="n">
+      <c r="E57" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F57" s="0"/>
-      <c r="G57" s="0"/>
-      <c r="H57" s="0"/>
-      <c r="I57" s="0"/>
-      <c r="J57" s="0" t="n">
+      <c r="J57" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="K57" s="0"/>
-      <c r="L57" s="0"/>
-      <c r="M57" s="0" t="n">
+      <c r="M57" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="N57" s="0" t="n">
+      <c r="N57" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="O57" s="0"/>
-      <c r="P57" s="0"/>
-      <c r="Q57" s="0"/>
-      <c r="R57" s="0"/>
-      <c r="S57" s="0"/>
-      <c r="T57" s="0"/>
     </row>
     <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="n">
+      <c r="A58" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C58" s="0" t="s">
+      <c r="C58" s="1" t="s">
         <v>138</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E58" s="0" t="n">
+      <c r="E58" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F58" s="0" t="n">
+      <c r="F58" s="1" t="n">
         <v>15000</v>
       </c>
-      <c r="G58" s="0" t="n">
+      <c r="G58" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="H58" s="0" t="n">
+      <c r="H58" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I58" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J58" s="0"/>
-      <c r="K58" s="0"/>
-      <c r="L58" s="0"/>
-      <c r="M58" s="0"/>
-      <c r="N58" s="0"/>
-      <c r="O58" s="0" t="s">
+      <c r="I58" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O58" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P58" s="0"/>
-      <c r="Q58" s="0"/>
-      <c r="R58" s="0"/>
-      <c r="S58" s="0"/>
-      <c r="T58" s="0"/>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="n">
+      <c r="A59" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C59" s="0" t="s">
+      <c r="C59" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E59" s="0" t="n">
+      <c r="E59" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F59" s="0"/>
-      <c r="G59" s="0"/>
-      <c r="H59" s="0"/>
-      <c r="I59" s="0"/>
-      <c r="J59" s="0" t="n">
+      <c r="J59" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="K59" s="0"/>
-      <c r="L59" s="0"/>
-      <c r="M59" s="0"/>
-      <c r="N59" s="0"/>
-      <c r="O59" s="0"/>
-      <c r="P59" s="0"/>
-      <c r="Q59" s="0"/>
-      <c r="R59" s="0"/>
-      <c r="S59" s="0"/>
-      <c r="T59" s="0"/>
     </row>
     <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="n">
+      <c r="A60" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C60" s="0" t="s">
+      <c r="C60" s="1" t="s">
         <v>142</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E60" s="0" t="n">
+      <c r="E60" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F60" s="0" t="n">
+      <c r="F60" s="1" t="n">
         <v>18000</v>
       </c>
-      <c r="G60" s="0" t="n">
+      <c r="G60" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="H60" s="0" t="n">
+      <c r="H60" s="1" t="n">
         <v>0.16</v>
       </c>
-      <c r="I60" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J60" s="0"/>
-      <c r="K60" s="0"/>
-      <c r="L60" s="0" t="n">
+      <c r="I60" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L60" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="M60" s="0"/>
-      <c r="N60" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O60" s="0" t="s">
+      <c r="N60" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O60" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P60" s="0"/>
-      <c r="Q60" s="0"/>
-      <c r="R60" s="0"/>
-      <c r="S60" s="0"/>
-      <c r="T60" s="0"/>
     </row>
     <row r="61" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="n">
+      <c r="A61" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C61" s="0" t="s">
+      <c r="C61" s="1" t="s">
         <v>144</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E61" s="0" t="n">
+      <c r="E61" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F61" s="0" t="n">
+      <c r="F61" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="G61" s="0" t="n">
+      <c r="G61" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="H61" s="0" t="n">
+      <c r="H61" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I61" s="0"/>
-      <c r="J61" s="0"/>
-      <c r="K61" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L61" s="0"/>
-      <c r="M61" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N61" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O61" s="0" t="s">
+      <c r="K61" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M61" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N61" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O61" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P61" s="0"/>
-      <c r="Q61" s="0"/>
-      <c r="R61" s="0"/>
-      <c r="S61" s="0"/>
-      <c r="T61" s="0"/>
     </row>
     <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="n">
+      <c r="A62" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C62" s="0" t="s">
+      <c r="C62" s="1" t="s">
         <v>146</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E62" s="0" t="n">
+      <c r="E62" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F62" s="0" t="n">
+      <c r="F62" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G62" s="0" t="n">
+      <c r="G62" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H62" s="0" t="n">
+      <c r="H62" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I62" s="0"/>
-      <c r="J62" s="0" t="n">
+      <c r="J62" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="K62" s="0"/>
-      <c r="L62" s="0"/>
-      <c r="M62" s="0"/>
-      <c r="N62" s="0"/>
-      <c r="O62" s="0" t="s">
+      <c r="O62" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P62" s="0"/>
-      <c r="Q62" s="0"/>
-      <c r="R62" s="0"/>
-      <c r="S62" s="0"/>
-      <c r="T62" s="0"/>
     </row>
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="n">
+      <c r="A63" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C63" s="0" t="s">
+      <c r="C63" s="1" t="s">
         <v>148</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E63" s="0" t="n">
+      <c r="E63" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F63" s="0" t="n">
+      <c r="F63" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="G63" s="0" t="n">
+      <c r="G63" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="H63" s="0" t="n">
+      <c r="H63" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I63" s="0"/>
-      <c r="J63" s="0"/>
-      <c r="K63" s="0"/>
-      <c r="L63" s="0"/>
-      <c r="M63" s="0"/>
-      <c r="N63" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O63" s="0" t="s">
+      <c r="N63" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O63" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P63" s="0"/>
-      <c r="Q63" s="0"/>
-      <c r="R63" s="0"/>
-      <c r="S63" s="0"/>
-      <c r="T63" s="0"/>
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="n">
+      <c r="A64" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C64" s="0" t="s">
+      <c r="C64" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E64" s="0" t="n">
+      <c r="E64" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F64" s="0" t="n">
+      <c r="F64" s="1" t="n">
         <v>70000</v>
       </c>
-      <c r="G64" s="0" t="n">
+      <c r="G64" s="1" t="n">
         <v>700</v>
       </c>
-      <c r="H64" s="0" t="n">
+      <c r="H64" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="I64" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J64" s="0"/>
-      <c r="K64" s="0"/>
-      <c r="L64" s="0"/>
-      <c r="M64" s="0"/>
-      <c r="N64" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O64" s="0" t="s">
+      <c r="I64" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N64" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O64" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P64" s="0"/>
-      <c r="Q64" s="0"/>
-      <c r="R64" s="0"/>
-      <c r="S64" s="0"/>
-      <c r="T64" s="0"/>
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="n">
+      <c r="A65" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C65" s="0" t="s">
+      <c r="C65" s="1" t="s">
         <v>152</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E65" s="0" t="n">
+      <c r="E65" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="0"/>
-      <c r="G65" s="0"/>
-      <c r="H65" s="0"/>
-      <c r="I65" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J65" s="0"/>
-      <c r="K65" s="0"/>
-      <c r="L65" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M65" s="0"/>
-      <c r="N65" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O65" s="0"/>
-      <c r="P65" s="0"/>
-      <c r="Q65" s="0"/>
-      <c r="R65" s="0"/>
-      <c r="S65" s="0"/>
-      <c r="T65" s="0"/>
+      <c r="I65" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L65" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N65" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="n">
+      <c r="A66" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C66" s="0" t="s">
+      <c r="C66" s="1" t="s">
         <v>154</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E66" s="0" t="n">
+      <c r="E66" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F66" s="0" t="n">
+      <c r="F66" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="G66" s="0" t="n">
+      <c r="G66" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H66" s="0" t="n">
+      <c r="H66" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I66" s="0"/>
-      <c r="J66" s="0"/>
-      <c r="K66" s="0"/>
-      <c r="L66" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M66" s="0"/>
-      <c r="N66" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O66" s="0" t="s">
+      <c r="L66" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N66" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O66" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P66" s="0"/>
-      <c r="Q66" s="0"/>
-      <c r="R66" s="0"/>
-      <c r="S66" s="0"/>
-      <c r="T66" s="0"/>
     </row>
     <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="n">
+      <c r="A67" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="0" t="n">
+      <c r="B67" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C67" s="0" t="s">
+      <c r="C67" s="1" t="s">
         <v>156</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E67" s="0" t="n">
+      <c r="E67" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F67" s="0"/>
-      <c r="G67" s="0"/>
-      <c r="H67" s="0"/>
-      <c r="I67" s="0"/>
-      <c r="J67" s="0" t="n">
+      <c r="J67" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="K67" s="0" t="n">
+      <c r="K67" s="1" t="n">
         <v>0.009</v>
       </c>
-      <c r="L67" s="0" t="n">
+      <c r="L67" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="M67" s="0" t="n">
+      <c r="M67" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="N67" s="0"/>
-      <c r="O67" s="0"/>
-      <c r="P67" s="0"/>
-      <c r="Q67" s="0"/>
-      <c r="R67" s="0"/>
-      <c r="S67" s="0"/>
-      <c r="T67" s="0"/>
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="n">
+      <c r="A68" s="1" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="0" t="n">
+      <c r="B68" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C68" s="0" t="s">
+      <c r="C68" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E68" s="0" t="n">
+      <c r="E68" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F68" s="0" t="n">
+      <c r="F68" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G68" s="0" t="n">
+      <c r="G68" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="H68" s="0" t="n">
+      <c r="H68" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I68" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J68" s="0"/>
-      <c r="K68" s="0"/>
-      <c r="L68" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M68" s="0"/>
-      <c r="N68" s="0"/>
-      <c r="O68" s="0" t="s">
+      <c r="I68" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L68" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O68" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="P68" s="0"/>
-      <c r="Q68" s="0"/>
-      <c r="R68" s="0"/>
-      <c r="S68" s="0"/>
-      <c r="T68" s="0"/>
     </row>
     <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="n">
+      <c r="A69" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="0" t="n">
+      <c r="B69" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C69" s="0" t="s">
+      <c r="C69" s="1" t="s">
         <v>160</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="E69" s="0" t="n">
+      <c r="E69" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F69" s="0" t="n">
+      <c r="F69" s="1" t="n">
         <v>8000</v>
       </c>
-      <c r="G69" s="0" t="n">
+      <c r="G69" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H69" s="0" t="n">
+      <c r="H69" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I69" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J69" s="0"/>
-      <c r="K69" s="0"/>
-      <c r="L69" s="0"/>
-      <c r="M69" s="0"/>
-      <c r="N69" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O69" s="0" t="s">
+      <c r="I69" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N69" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O69" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P69" s="0"/>
-      <c r="Q69" s="0"/>
-      <c r="R69" s="0"/>
-      <c r="S69" s="0"/>
-      <c r="T69" s="0"/>
     </row>
     <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="n">
+      <c r="A70" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="0" t="n">
+      <c r="B70" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C70" s="0" t="s">
+      <c r="C70" s="1" t="s">
         <v>162</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E70" s="0" t="n">
+      <c r="E70" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F70" s="0" t="n">
+      <c r="F70" s="1" t="n">
         <v>15000</v>
       </c>
-      <c r="G70" s="0" t="n">
+      <c r="G70" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H70" s="0" t="n">
+      <c r="H70" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I70" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J70" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K70" s="0"/>
-      <c r="L70" s="0"/>
-      <c r="M70" s="0"/>
-      <c r="N70" s="0"/>
-      <c r="O70" s="0"/>
-      <c r="P70" s="0"/>
-      <c r="Q70" s="0"/>
-      <c r="R70" s="0"/>
-      <c r="S70" s="0"/>
-      <c r="T70" s="0"/>
+      <c r="I70" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J70" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="n">
+      <c r="A71" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="0" t="n">
+      <c r="B71" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C71" s="0" t="s">
+      <c r="C71" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E71" s="0" t="n">
+      <c r="E71" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F71" s="0" t="n">
+      <c r="F71" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="G71" s="0" t="n">
+      <c r="G71" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H71" s="0" t="n">
+      <c r="H71" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I71" s="0"/>
-      <c r="J71" s="0"/>
-      <c r="K71" s="0"/>
-      <c r="L71" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M71" s="0"/>
-      <c r="N71" s="0"/>
-      <c r="O71" s="0" t="s">
+      <c r="L71" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O71" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P71" s="0"/>
-      <c r="Q71" s="0"/>
-      <c r="R71" s="0"/>
-      <c r="S71" s="0"/>
-      <c r="T71" s="0"/>
     </row>
     <row r="72" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="n">
+      <c r="A72" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="0" t="n">
+      <c r="B72" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C72" s="0" t="s">
+      <c r="C72" s="1" t="s">
         <v>166</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E72" s="0" t="n">
+      <c r="E72" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F72" s="0" t="n">
+      <c r="F72" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G72" s="0" t="n">
+      <c r="G72" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H72" s="0" t="n">
+      <c r="H72" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I72" s="0"/>
-      <c r="J72" s="0"/>
-      <c r="K72" s="0" t="n">
+      <c r="K72" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="L72" s="0"/>
-      <c r="M72" s="0" t="n">
+      <c r="M72" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="N72" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O72" s="0" t="s">
+      <c r="N72" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O72" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="P72" s="0"/>
-      <c r="Q72" s="0"/>
-      <c r="R72" s="0"/>
-      <c r="S72" s="0"/>
-      <c r="T72" s="0"/>
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="n">
+      <c r="A73" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="0" t="n">
+      <c r="B73" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C73" s="0" t="s">
+      <c r="C73" s="1" t="s">
         <v>168</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E73" s="0" t="n">
+      <c r="E73" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F73" s="0" t="n">
+      <c r="F73" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="G73" s="0" t="n">
+      <c r="G73" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="H73" s="0" t="n">
+      <c r="H73" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I73" s="0"/>
-      <c r="J73" s="0"/>
-      <c r="K73" s="0"/>
-      <c r="L73" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M73" s="0"/>
-      <c r="N73" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O73" s="0" t="s">
+      <c r="L73" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N73" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O73" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P73" s="0"/>
-      <c r="Q73" s="0"/>
-      <c r="R73" s="0"/>
-      <c r="S73" s="0"/>
-      <c r="T73" s="0"/>
     </row>
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="n">
+      <c r="A74" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="0" t="n">
+      <c r="B74" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C74" s="0" t="s">
+      <c r="C74" s="1" t="s">
         <v>170</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E74" s="0" t="n">
+      <c r="E74" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="0"/>
-      <c r="G74" s="0"/>
-      <c r="H74" s="0"/>
-      <c r="I74" s="0"/>
-      <c r="J74" s="0" t="n">
+      <c r="J74" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="K74" s="0"/>
-      <c r="L74" s="0"/>
-      <c r="M74" s="0"/>
-      <c r="N74" s="0"/>
-      <c r="O74" s="0"/>
-      <c r="P74" s="0"/>
-      <c r="Q74" s="0"/>
-      <c r="R74" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S74" s="0"/>
-      <c r="T74" s="0"/>
+      <c r="R74" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="n">
+      <c r="A75" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="0" t="n">
+      <c r="B75" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C75" s="0" t="s">
+      <c r="C75" s="1" t="s">
         <v>172</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E75" s="0" t="n">
+      <c r="E75" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F75" s="0"/>
-      <c r="G75" s="0"/>
-      <c r="H75" s="0"/>
-      <c r="I75" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J75" s="0"/>
-      <c r="K75" s="0"/>
-      <c r="L75" s="0"/>
-      <c r="M75" s="0"/>
-      <c r="N75" s="0"/>
-      <c r="O75" s="0"/>
-      <c r="P75" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q75" s="0"/>
-      <c r="R75" s="0"/>
-      <c r="S75" s="0"/>
-      <c r="T75" s="0"/>
+      <c r="I75" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P75" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="n">
+      <c r="A76" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="0" t="n">
+      <c r="B76" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C76" s="0" t="s">
+      <c r="C76" s="1" t="s">
         <v>174</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E76" s="0" t="n">
+      <c r="E76" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F76" s="0"/>
-      <c r="G76" s="0"/>
-      <c r="H76" s="0"/>
-      <c r="I76" s="0"/>
-      <c r="J76" s="0"/>
-      <c r="K76" s="0"/>
-      <c r="L76" s="0" t="n">
+      <c r="L76" s="1" t="n">
         <v>0.0075</v>
       </c>
-      <c r="M76" s="0" t="n">
+      <c r="M76" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="N76" s="0"/>
-      <c r="O76" s="0"/>
-      <c r="P76" s="0"/>
-      <c r="Q76" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R76" s="0"/>
-      <c r="S76" s="0"/>
-      <c r="T76" s="0"/>
+      <c r="Q76" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="n">
+      <c r="A77" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="0" t="n">
+      <c r="B77" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C77" s="0" t="s">
+      <c r="C77" s="1" t="s">
         <v>176</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E77" s="0" t="n">
+      <c r="E77" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F77" s="0" t="n">
+      <c r="F77" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="G77" s="0" t="n">
+      <c r="G77" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H77" s="0" t="n">
+      <c r="H77" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I77" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J77" s="0" t="n">
+      <c r="I77" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J77" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="K77" s="0"/>
-      <c r="L77" s="0"/>
-      <c r="M77" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N77" s="0" t="n">
+      <c r="M77" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N77" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O77" s="0" t="s">
+      <c r="O77" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P77" s="0"/>
-      <c r="Q77" s="0"/>
-      <c r="R77" s="0"/>
-      <c r="S77" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T77" s="0"/>
+      <c r="S77" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="n">
+      <c r="A78" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="0" t="n">
+      <c r="B78" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C78" s="0" t="s">
+      <c r="C78" s="1" t="s">
         <v>178</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E78" s="0" t="n">
+      <c r="E78" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F78" s="0" t="n">
+      <c r="F78" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G78" s="0" t="n">
+      <c r="G78" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H78" s="0" t="n">
+      <c r="H78" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I78" s="0" t="n">
+      <c r="I78" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="J78" s="0" t="n">
+      <c r="J78" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="K78" s="0"/>
-      <c r="L78" s="0"/>
-      <c r="M78" s="0"/>
-      <c r="N78" s="0"/>
-      <c r="O78" s="0" t="s">
+      <c r="O78" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P78" s="0"/>
-      <c r="Q78" s="0"/>
-      <c r="R78" s="0"/>
-      <c r="S78" s="0"/>
-      <c r="T78" s="0"/>
     </row>
     <row r="79" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="n">
+      <c r="A79" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="0" t="n">
+      <c r="B79" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C79" s="0" t="s">
+      <c r="C79" s="1" t="s">
         <v>180</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E79" s="0" t="n">
+      <c r="E79" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F79" s="0" t="n">
+      <c r="F79" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G79" s="0" t="n">
+      <c r="G79" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H79" s="0" t="n">
+      <c r="H79" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I79" s="0"/>
-      <c r="J79" s="0"/>
-      <c r="K79" s="0"/>
-      <c r="L79" s="0"/>
-      <c r="M79" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N79" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O79" s="0" t="s">
+      <c r="M79" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N79" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O79" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P79" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q79" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R79" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S79" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T79" s="0" t="n">
+      <c r="P79" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q79" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R79" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S79" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T79" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="n">
+      <c r="A80" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="0" t="n">
+      <c r="B80" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C80" s="0" t="s">
+      <c r="C80" s="1" t="s">
         <v>182</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E80" s="0" t="n">
+      <c r="E80" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F80" s="0" t="n">
+      <c r="F80" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="G80" s="0" t="n">
+      <c r="G80" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="H80" s="0" t="n">
+      <c r="H80" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="I80" s="0"/>
-      <c r="J80" s="0"/>
-      <c r="K80" s="0"/>
-      <c r="L80" s="0"/>
-      <c r="M80" s="0"/>
-      <c r="N80" s="0"/>
-      <c r="O80" s="0" t="s">
+      <c r="O80" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P80" s="0"/>
-      <c r="Q80" s="0"/>
-      <c r="R80" s="0"/>
-      <c r="S80" s="0"/>
-      <c r="T80" s="0"/>
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="n">
+      <c r="A81" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="0" t="n">
+      <c r="B81" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C81" s="0" t="s">
+      <c r="C81" s="1" t="s">
         <v>184</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E81" s="0" t="n">
+      <c r="E81" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F81" s="0" t="n">
+      <c r="F81" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G81" s="0" t="n">
+      <c r="G81" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H81" s="0" t="n">
+      <c r="H81" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="I81" s="0"/>
-      <c r="J81" s="0"/>
-      <c r="K81" s="0"/>
-      <c r="L81" s="0"/>
-      <c r="M81" s="0"/>
-      <c r="N81" s="0"/>
-      <c r="O81" s="0" t="s">
+      <c r="O81" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P81" s="0"/>
-      <c r="Q81" s="0"/>
-      <c r="R81" s="0"/>
-      <c r="S81" s="0"/>
-      <c r="T81" s="0"/>
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="n">
+      <c r="A82" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="0" t="n">
+      <c r="B82" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C82" s="0" t="s">
+      <c r="C82" s="1" t="s">
         <v>186</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E82" s="0" t="n">
+      <c r="E82" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F82" s="0" t="n">
+      <c r="F82" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="G82" s="0" t="n">
+      <c r="G82" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="H82" s="0" t="n">
+      <c r="H82" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="I82" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J82" s="0"/>
-      <c r="K82" s="0"/>
-      <c r="L82" s="0"/>
-      <c r="M82" s="0"/>
-      <c r="N82" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O82" s="0" t="s">
+      <c r="I82" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N82" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O82" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P82" s="0"/>
-      <c r="Q82" s="0"/>
-      <c r="R82" s="0"/>
-      <c r="S82" s="0"/>
-      <c r="T82" s="0"/>
     </row>
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="n">
+      <c r="A83" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="0" t="n">
+      <c r="B83" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C83" s="0" t="s">
+      <c r="C83" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E83" s="0" t="n">
+      <c r="E83" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="0"/>
-      <c r="G83" s="0"/>
-      <c r="H83" s="0"/>
-      <c r="I83" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J83" s="0"/>
-      <c r="K83" s="0"/>
-      <c r="L83" s="0"/>
-      <c r="M83" s="0" t="n">
+      <c r="I83" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M83" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="N83" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O83" s="0"/>
-      <c r="P83" s="0"/>
-      <c r="Q83" s="0"/>
-      <c r="R83" s="0"/>
-      <c r="S83" s="0"/>
-      <c r="T83" s="0"/>
+      <c r="N83" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="n">
+      <c r="A84" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="0" t="n">
+      <c r="B84" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C84" s="0" t="s">
+      <c r="C84" s="1" t="s">
         <v>190</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E84" s="0" t="n">
+      <c r="E84" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F84" s="0"/>
-      <c r="G84" s="0"/>
-      <c r="H84" s="0"/>
-      <c r="I84" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J84" s="0"/>
-      <c r="K84" s="0"/>
-      <c r="L84" s="0"/>
-      <c r="M84" s="0"/>
-      <c r="N84" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O84" s="0"/>
-      <c r="P84" s="0"/>
-      <c r="Q84" s="0"/>
-      <c r="R84" s="0"/>
-      <c r="S84" s="0"/>
-      <c r="T84" s="0"/>
+      <c r="I84" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N84" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="n">
+      <c r="A85" s="1" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="0" t="n">
+      <c r="B85" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C85" s="0" t="s">
+      <c r="C85" s="1" t="s">
         <v>192</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E85" s="0" t="n">
+      <c r="E85" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F85" s="0"/>
-      <c r="G85" s="0"/>
-      <c r="H85" s="0"/>
-      <c r="I85" s="0"/>
-      <c r="J85" s="0" t="n">
+      <c r="J85" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="K85" s="0"/>
-      <c r="L85" s="0"/>
-      <c r="M85" s="0" t="n">
+      <c r="M85" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="N85" s="0"/>
-      <c r="O85" s="0"/>
-      <c r="P85" s="0"/>
-      <c r="Q85" s="0"/>
-      <c r="R85" s="0"/>
-      <c r="S85" s="0"/>
-      <c r="T85" s="0"/>
     </row>
     <row r="86" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="n">
+      <c r="A86" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="0" t="n">
+      <c r="B86" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C86" s="0" t="s">
+      <c r="C86" s="1" t="s">
         <v>194</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E86" s="0" t="n">
+      <c r="E86" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F86" s="0" t="n">
+      <c r="F86" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="G86" s="0" t="n">
+      <c r="G86" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H86" s="0" t="n">
+      <c r="H86" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="I86" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J86" s="0"/>
-      <c r="K86" s="0"/>
-      <c r="L86" s="0"/>
-      <c r="M86" s="0" t="n">
+      <c r="I86" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M86" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="N86" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O86" s="0"/>
-      <c r="P86" s="0"/>
-      <c r="Q86" s="0"/>
-      <c r="R86" s="0"/>
-      <c r="S86" s="0"/>
-      <c r="T86" s="0"/>
+      <c r="N86" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="n">
+      <c r="A87" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="0" t="n">
+      <c r="B87" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C87" s="0" t="s">
+      <c r="C87" s="1" t="s">
         <v>196</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E87" s="0" t="n">
+      <c r="E87" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F87" s="0" t="n">
+      <c r="F87" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G87" s="0" t="n">
+      <c r="G87" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="H87" s="0" t="n">
+      <c r="H87" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="I87" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J87" s="0" t="n">
+      <c r="I87" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J87" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="K87" s="0"/>
-      <c r="L87" s="0"/>
-      <c r="M87" s="0" t="n">
+      <c r="M87" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="N87" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O87" s="0" t="s">
+      <c r="N87" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O87" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P87" s="0"/>
-      <c r="Q87" s="0"/>
-      <c r="R87" s="0"/>
-      <c r="S87" s="0"/>
-      <c r="T87" s="0"/>
     </row>
     <row r="88" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="n">
+      <c r="A88" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="0" t="n">
+      <c r="B88" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C88" s="0" t="s">
+      <c r="C88" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E88" s="0" t="n">
+      <c r="E88" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F88" s="0" t="n">
+      <c r="F88" s="1" t="n">
         <v>40000</v>
       </c>
-      <c r="G88" s="0" t="n">
+      <c r="G88" s="1" t="n">
         <v>2100</v>
       </c>
-      <c r="H88" s="0" t="n">
+      <c r="H88" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I88" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J88" s="0"/>
-      <c r="K88" s="0"/>
-      <c r="L88" s="0"/>
-      <c r="M88" s="0"/>
-      <c r="N88" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O88" s="0" t="s">
+      <c r="I88" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N88" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O88" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P88" s="0"/>
-      <c r="Q88" s="0"/>
-      <c r="R88" s="0"/>
-      <c r="S88" s="0"/>
-      <c r="T88" s="0"/>
     </row>
     <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="n">
+      <c r="A89" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="0" t="n">
+      <c r="B89" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C89" s="0" t="s">
+      <c r="C89" s="1" t="s">
         <v>200</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E89" s="0" t="n">
+      <c r="E89" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F89" s="0" t="n">
+      <c r="F89" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G89" s="0" t="n">
+      <c r="G89" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="H89" s="0" t="n">
+      <c r="H89" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I89" s="0"/>
-      <c r="J89" s="0"/>
-      <c r="K89" s="0"/>
-      <c r="L89" s="0"/>
-      <c r="M89" s="0" t="n">
+      <c r="M89" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="N89" s="0"/>
-      <c r="O89" s="0" t="s">
+      <c r="O89" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P89" s="0"/>
-      <c r="Q89" s="0"/>
-      <c r="R89" s="0"/>
-      <c r="S89" s="0"/>
-      <c r="T89" s="0"/>
     </row>
     <row r="90" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="n">
+      <c r="A90" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="0" t="n">
+      <c r="B90" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C90" s="0" t="s">
+      <c r="C90" s="1" t="s">
         <v>202</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E90" s="0" t="n">
+      <c r="E90" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F90" s="0" t="n">
+      <c r="F90" s="1" t="n">
         <v>80000</v>
       </c>
-      <c r="G90" s="0" t="n">
+      <c r="G90" s="1" t="n">
         <v>1700</v>
       </c>
-      <c r="H90" s="0" t="n">
+      <c r="H90" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I90" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J90" s="0"/>
-      <c r="K90" s="0"/>
-      <c r="L90" s="0"/>
-      <c r="M90" s="0" t="n">
+      <c r="I90" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M90" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="N90" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O90" s="0" t="s">
+      <c r="N90" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O90" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P90" s="0"/>
-      <c r="Q90" s="0"/>
-      <c r="R90" s="0"/>
-      <c r="S90" s="0"/>
-      <c r="T90" s="0"/>
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="n">
+      <c r="A91" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="0" t="n">
+      <c r="B91" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C91" s="0" t="s">
+      <c r="C91" s="1" t="s">
         <v>204</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E91" s="0" t="n">
+      <c r="E91" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="0"/>
-      <c r="G91" s="0"/>
-      <c r="H91" s="0"/>
-      <c r="I91" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J91" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K91" s="0"/>
-      <c r="L91" s="0"/>
-      <c r="M91" s="0"/>
-      <c r="N91" s="0" t="n">
+      <c r="I91" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J91" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N91" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O91" s="0"/>
-      <c r="P91" s="0"/>
-      <c r="Q91" s="0"/>
-      <c r="R91" s="0"/>
-      <c r="S91" s="0"/>
-      <c r="T91" s="0"/>
     </row>
     <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="n">
+      <c r="A92" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="0" t="n">
+      <c r="B92" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C92" s="0" t="s">
+      <c r="C92" s="1" t="s">
         <v>206</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E92" s="0" t="n">
+      <c r="E92" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F92" s="0" t="n">
+      <c r="F92" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="G92" s="0" t="n">
+      <c r="G92" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H92" s="0" t="n">
+      <c r="H92" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="I92" s="0"/>
-      <c r="J92" s="0"/>
-      <c r="K92" s="0"/>
-      <c r="L92" s="0"/>
-      <c r="M92" s="0"/>
-      <c r="N92" s="0" t="n">
+      <c r="N92" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="O92" s="0" t="s">
+      <c r="O92" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P92" s="0"/>
-      <c r="Q92" s="0"/>
-      <c r="R92" s="0"/>
-      <c r="S92" s="0"/>
-      <c r="T92" s="0"/>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="n">
+      <c r="A93" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="0" t="n">
+      <c r="B93" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C93" s="0" t="s">
+      <c r="C93" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E93" s="0" t="n">
+      <c r="E93" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F93" s="0"/>
-      <c r="G93" s="0"/>
-      <c r="H93" s="0"/>
-      <c r="I93" s="0"/>
-      <c r="J93" s="0"/>
-      <c r="K93" s="0"/>
-      <c r="L93" s="0"/>
-      <c r="M93" s="0"/>
-      <c r="N93" s="0"/>
-      <c r="O93" s="0"/>
-      <c r="P93" s="0"/>
-      <c r="Q93" s="0"/>
-      <c r="R93" s="0"/>
-      <c r="S93" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T93" s="0" t="n">
+      <c r="S93" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T93" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="n">
+      <c r="A94" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="0" t="n">
+      <c r="B94" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C94" s="0" t="s">
+      <c r="C94" s="1" t="s">
         <v>210</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E94" s="0" t="n">
+      <c r="E94" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F94" s="0"/>
-      <c r="G94" s="0"/>
-      <c r="H94" s="0"/>
-      <c r="I94" s="0"/>
-      <c r="J94" s="0"/>
-      <c r="K94" s="0"/>
-      <c r="L94" s="0"/>
-      <c r="M94" s="0"/>
-      <c r="N94" s="0"/>
-      <c r="O94" s="0"/>
-      <c r="P94" s="0"/>
-      <c r="Q94" s="0" t="n">
+      <c r="Q94" s="1" t="n">
         <v>0.0025</v>
       </c>
-      <c r="R94" s="0"/>
-      <c r="S94" s="0"/>
-      <c r="T94" s="0"/>
     </row>
     <row r="95" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="n">
+      <c r="A95" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="0" t="n">
+      <c r="B95" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C95" s="0" t="s">
+      <c r="C95" s="1" t="s">
         <v>212</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E95" s="0" t="n">
+      <c r="E95" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F95" s="0" t="n">
+      <c r="F95" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G95" s="0" t="n">
+      <c r="G95" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H95" s="0" t="n">
+      <c r="H95" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I95" s="0" t="n">
+      <c r="I95" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="J95" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K95" s="0" t="n">
+      <c r="J95" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K95" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="L95" s="0"/>
-      <c r="M95" s="0"/>
-      <c r="N95" s="0"/>
-      <c r="O95" s="0" t="s">
+      <c r="O95" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P95" s="0"/>
-      <c r="Q95" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R95" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S95" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T95" s="0" t="n">
+      <c r="Q95" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R95" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S95" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T95" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="n">
+      <c r="A96" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="0" t="n">
+      <c r="B96" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C96" s="0" t="s">
+      <c r="C96" s="1" t="s">
         <v>214</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="E96" s="0" t="n">
+      <c r="E96" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F96" s="0" t="n">
+      <c r="F96" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G96" s="0" t="n">
+      <c r="G96" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H96" s="0" t="n">
+      <c r="H96" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="I96" s="0" t="n">
+      <c r="I96" s="1" t="n">
         <v>0.0175</v>
       </c>
-      <c r="J96" s="0" t="n">
+      <c r="J96" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="K96" s="0"/>
-      <c r="L96" s="0"/>
-      <c r="M96" s="0"/>
-      <c r="N96" s="0"/>
-      <c r="O96" s="0" t="s">
+      <c r="O96" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P96" s="0" t="n">
+      <c r="P96" s="1" t="n">
         <v>0.0015</v>
       </c>
-      <c r="Q96" s="0"/>
-      <c r="R96" s="0"/>
-      <c r="S96" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T96" s="0" t="n">
+      <c r="S96" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T96" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="n">
+      <c r="A97" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="0" t="n">
+      <c r="B97" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C97" s="0" t="s">
+      <c r="C97" s="1" t="s">
         <v>216</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E97" s="0" t="n">
+      <c r="E97" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F97" s="0" t="n">
+      <c r="F97" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="G97" s="0" t="n">
+      <c r="G97" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="H97" s="0" t="n">
+      <c r="H97" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I97" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J97" s="0"/>
-      <c r="K97" s="0"/>
-      <c r="L97" s="0"/>
-      <c r="M97" s="0"/>
-      <c r="N97" s="0" t="n">
+      <c r="I97" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N97" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O97" s="0" t="s">
+      <c r="O97" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P97" s="0"/>
-      <c r="Q97" s="0"/>
-      <c r="R97" s="0"/>
-      <c r="S97" s="0"/>
-      <c r="T97" s="0"/>
     </row>
     <row r="98" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="n">
+      <c r="A98" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="0" t="n">
+      <c r="B98" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C98" s="0" t="s">
+      <c r="C98" s="1" t="s">
         <v>218</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E98" s="0" t="n">
+      <c r="E98" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F98" s="0" t="n">
+      <c r="F98" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G98" s="0" t="n">
+      <c r="G98" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H98" s="0" t="n">
+      <c r="H98" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="I98" s="0" t="n">
+      <c r="I98" s="1" t="n">
         <v>0.0175</v>
       </c>
-      <c r="J98" s="0" t="n">
+      <c r="J98" s="1" t="n">
         <v>0.0175</v>
       </c>
-      <c r="K98" s="0" t="n">
+      <c r="K98" s="1" t="n">
         <v>0.0175</v>
       </c>
-      <c r="L98" s="0"/>
-      <c r="M98" s="0"/>
-      <c r="N98" s="0"/>
-      <c r="O98" s="0" t="s">
+      <c r="O98" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P98" s="0" t="n">
+      <c r="P98" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="Q98" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R98" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S98" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T98" s="0" t="n">
+      <c r="Q98" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R98" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S98" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T98" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="n">
+      <c r="A99" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="0" t="n">
+      <c r="B99" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C99" s="0" t="s">
+      <c r="C99" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E99" s="0" t="n">
+      <c r="E99" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F99" s="0" t="n">
+      <c r="F99" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="G99" s="0" t="n">
+      <c r="G99" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="H99" s="0" t="n">
+      <c r="H99" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="I99" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J99" s="0"/>
-      <c r="K99" s="0"/>
-      <c r="L99" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M99" s="0"/>
-      <c r="N99" s="0"/>
-      <c r="O99" s="0" t="s">
+      <c r="I99" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L99" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O99" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P99" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q99" s="0"/>
-      <c r="R99" s="0"/>
-      <c r="S99" s="0"/>
-      <c r="T99" s="0"/>
+      <c r="P99" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="n">
+      <c r="A100" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="0" t="n">
+      <c r="B100" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C100" s="0" t="s">
+      <c r="C100" s="1" t="s">
         <v>222</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E100" s="0" t="n">
+      <c r="E100" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F100" s="0"/>
-      <c r="G100" s="0"/>
-      <c r="H100" s="0"/>
-      <c r="I100" s="0" t="n">
+      <c r="I100" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="J100" s="0"/>
-      <c r="K100" s="0"/>
-      <c r="L100" s="0"/>
-      <c r="M100" s="0"/>
-      <c r="N100" s="0"/>
-      <c r="O100" s="0"/>
-      <c r="P100" s="0"/>
-      <c r="Q100" s="0"/>
-      <c r="R100" s="0"/>
-      <c r="S100" s="0"/>
-      <c r="T100" s="0"/>
     </row>
     <row r="101" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="n">
+      <c r="A101" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="0" t="n">
+      <c r="B101" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C101" s="0" t="s">
+      <c r="C101" s="1" t="s">
         <v>224</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E101" s="0" t="n">
+      <c r="E101" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F101" s="0"/>
-      <c r="G101" s="0"/>
-      <c r="H101" s="0"/>
-      <c r="I101" s="0"/>
-      <c r="J101" s="0"/>
-      <c r="K101" s="0"/>
-      <c r="L101" s="0"/>
-      <c r="M101" s="0"/>
-      <c r="N101" s="0" t="n">
+      <c r="N101" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O101" s="0"/>
-      <c r="P101" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q101" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R101" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S101" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T101" s="0" t="n">
+      <c r="P101" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q101" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R101" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S101" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T101" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="n">
+      <c r="A102" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="0" t="n">
+      <c r="B102" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C102" s="0" t="s">
+      <c r="C102" s="1" t="s">
         <v>226</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="E102" s="0" t="n">
+      <c r="E102" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F102" s="0"/>
-      <c r="G102" s="0"/>
-      <c r="H102" s="0"/>
-      <c r="I102" s="0"/>
-      <c r="J102" s="0"/>
-      <c r="K102" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L102" s="0"/>
-      <c r="M102" s="0" t="n">
+      <c r="K102" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M102" s="1" t="n">
         <v>0.014</v>
       </c>
-      <c r="N102" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O102" s="0"/>
-      <c r="P102" s="0"/>
-      <c r="Q102" s="0"/>
-      <c r="R102" s="0"/>
-      <c r="S102" s="0"/>
-      <c r="T102" s="0"/>
+      <c r="N102" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="n">
+      <c r="A103" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="0" t="n">
+      <c r="B103" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C103" s="0" t="s">
+      <c r="C103" s="1" t="s">
         <v>228</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="E103" s="0" t="n">
+      <c r="E103" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F103" s="0" t="n">
+      <c r="F103" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G103" s="0" t="n">
+      <c r="G103" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H103" s="0" t="n">
+      <c r="H103" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I103" s="0"/>
-      <c r="J103" s="0"/>
-      <c r="K103" s="0"/>
-      <c r="L103" s="0"/>
-      <c r="M103" s="0"/>
-      <c r="N103" s="0"/>
-      <c r="O103" s="0" t="s">
+      <c r="O103" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P103" s="0"/>
-      <c r="Q103" s="0"/>
-      <c r="R103" s="0"/>
-      <c r="S103" s="0"/>
-      <c r="T103" s="0"/>
     </row>
     <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="n">
+      <c r="A104" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="0" t="n">
+      <c r="B104" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C104" s="0" t="s">
+      <c r="C104" s="1" t="s">
         <v>230</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E104" s="0" t="n">
+      <c r="E104" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F104" s="0" t="n">
+      <c r="F104" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G104" s="0" t="n">
+      <c r="G104" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H104" s="0" t="n">
+      <c r="H104" s="1" t="n">
         <v>0.18</v>
       </c>
-      <c r="I104" s="0"/>
-      <c r="J104" s="0"/>
-      <c r="K104" s="0"/>
-      <c r="L104" s="0" t="n">
+      <c r="L104" s="1" t="n">
         <v>0.0075</v>
       </c>
-      <c r="M104" s="0"/>
-      <c r="N104" s="0"/>
-      <c r="O104" s="0" t="s">
+      <c r="O104" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P104" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q104" s="0"/>
-      <c r="R104" s="0"/>
-      <c r="S104" s="0"/>
-      <c r="T104" s="0"/>
+      <c r="P104" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="n">
+      <c r="A105" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="0" t="n">
+      <c r="B105" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C105" s="0" t="s">
+      <c r="C105" s="1" t="s">
         <v>232</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E105" s="0" t="n">
+      <c r="E105" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F105" s="0" t="n">
+      <c r="F105" s="1" t="n">
         <v>15000</v>
       </c>
-      <c r="G105" s="0" t="n">
+      <c r="G105" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="H105" s="0" t="n">
+      <c r="H105" s="1" t="n">
         <v>0.12</v>
       </c>
-      <c r="I105" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J105" s="0"/>
-      <c r="K105" s="0"/>
-      <c r="L105" s="0" t="n">
+      <c r="I105" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L105" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="M105" s="0"/>
-      <c r="N105" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O105" s="0" t="s">
+      <c r="N105" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O105" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P105" s="0"/>
-      <c r="Q105" s="0"/>
-      <c r="R105" s="0"/>
-      <c r="S105" s="0"/>
-      <c r="T105" s="0"/>
     </row>
     <row r="106" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="n">
+      <c r="A106" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="0" t="n">
+      <c r="B106" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C106" s="0" t="s">
+      <c r="C106" s="1" t="s">
         <v>234</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E106" s="0" t="n">
+      <c r="E106" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F106" s="0" t="n">
+      <c r="F106" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="G106" s="0" t="n">
+      <c r="G106" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="H106" s="0" t="n">
+      <c r="H106" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I106" s="0"/>
-      <c r="J106" s="0"/>
-      <c r="K106" s="0"/>
-      <c r="L106" s="0"/>
-      <c r="M106" s="0"/>
-      <c r="N106" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O106" s="0" t="s">
+      <c r="N106" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O106" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P106" s="0"/>
-      <c r="Q106" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R106" s="0"/>
-      <c r="S106" s="0"/>
-      <c r="T106" s="0" t="n">
+      <c r="Q106" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T106" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="n">
+      <c r="A107" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="0" t="n">
+      <c r="B107" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C107" s="0" t="s">
+      <c r="C107" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E107" s="0" t="n">
+      <c r="E107" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F107" s="0" t="n">
+      <c r="F107" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G107" s="0" t="n">
+      <c r="G107" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H107" s="0" t="n">
+      <c r="H107" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I107" s="0"/>
-      <c r="J107" s="0"/>
-      <c r="K107" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L107" s="0"/>
-      <c r="M107" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N107" s="0"/>
-      <c r="O107" s="0" t="s">
+      <c r="K107" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M107" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O107" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="P107" s="0"/>
-      <c r="Q107" s="0"/>
-      <c r="R107" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S107" s="0"/>
-      <c r="T107" s="0"/>
+      <c r="R107" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="n">
+      <c r="A108" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="0" t="n">
+      <c r="B108" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C108" s="0" t="s">
+      <c r="C108" s="1" t="s">
         <v>238</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="E108" s="0" t="n">
+      <c r="E108" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F108" s="0" t="n">
+      <c r="F108" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="G108" s="0" t="n">
+      <c r="G108" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="H108" s="0" t="n">
+      <c r="H108" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I108" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J108" s="0"/>
-      <c r="K108" s="0"/>
-      <c r="L108" s="0"/>
-      <c r="M108" s="0"/>
-      <c r="N108" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O108" s="0" t="s">
+      <c r="I108" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N108" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O108" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P108" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q108" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R108" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S108" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T108" s="0" t="n">
+      <c r="P108" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q108" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R108" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S108" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T108" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="n">
+      <c r="A109" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="0" t="n">
+      <c r="B109" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C109" s="0" t="s">
+      <c r="C109" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E109" s="0" t="n">
+      <c r="E109" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="0"/>
-      <c r="G109" s="0"/>
-      <c r="H109" s="0"/>
-      <c r="I109" s="0" t="n">
+      <c r="I109" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="J109" s="0"/>
-      <c r="K109" s="0"/>
-      <c r="L109" s="0"/>
-      <c r="M109" s="0"/>
-      <c r="N109" s="0" t="n">
+      <c r="N109" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O109" s="0"/>
-      <c r="P109" s="0"/>
-      <c r="Q109" s="0"/>
-      <c r="R109" s="0"/>
-      <c r="S109" s="0"/>
-      <c r="T109" s="0"/>
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="n">
+      <c r="A110" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="0" t="n">
+      <c r="B110" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C110" s="0" t="s">
+      <c r="C110" s="1" t="s">
         <v>242</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E110" s="0" t="n">
+      <c r="E110" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F110" s="0"/>
-      <c r="G110" s="0"/>
-      <c r="H110" s="0"/>
-      <c r="I110" s="0" t="n">
+      <c r="I110" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="J110" s="0"/>
-      <c r="K110" s="0"/>
-      <c r="L110" s="0"/>
-      <c r="M110" s="0"/>
-      <c r="N110" s="0"/>
-      <c r="O110" s="0"/>
-      <c r="P110" s="0"/>
-      <c r="Q110" s="0"/>
-      <c r="R110" s="0"/>
-      <c r="S110" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T110" s="0"/>
+      <c r="S110" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="n">
+      <c r="A111" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="0" t="n">
+      <c r="B111" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C111" s="0" t="s">
+      <c r="C111" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E111" s="0" t="n">
+      <c r="E111" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F111" s="0"/>
-      <c r="G111" s="0"/>
-      <c r="H111" s="0"/>
-      <c r="I111" s="0"/>
-      <c r="J111" s="0"/>
-      <c r="K111" s="0"/>
-      <c r="L111" s="0"/>
-      <c r="M111" s="0"/>
-      <c r="N111" s="0" t="n">
+      <c r="N111" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="O111" s="0"/>
-      <c r="P111" s="0"/>
-      <c r="Q111" s="0"/>
-      <c r="R111" s="0"/>
-      <c r="S111" s="0"/>
-      <c r="T111" s="0" t="n">
+      <c r="T111" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="n">
+      <c r="A112" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="0" t="n">
+      <c r="B112" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C112" s="0" t="s">
+      <c r="C112" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="E112" s="0" t="n">
+      <c r="E112" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F112" s="0" t="n">
+      <c r="F112" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G112" s="0" t="n">
+      <c r="G112" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H112" s="0" t="n">
+      <c r="H112" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I112" s="0" t="n">
+      <c r="I112" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="J112" s="0"/>
-      <c r="K112" s="0"/>
-      <c r="L112" s="0"/>
-      <c r="M112" s="0"/>
-      <c r="N112" s="0"/>
-      <c r="O112" s="0" t="s">
+      <c r="O112" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P112" s="0"/>
-      <c r="Q112" s="0"/>
-      <c r="R112" s="0"/>
-      <c r="S112" s="0"/>
-      <c r="T112" s="0"/>
     </row>
     <row r="113" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="n">
+      <c r="A113" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="0" t="n">
+      <c r="B113" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C113" s="0" t="s">
+      <c r="C113" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E113" s="0" t="n">
+      <c r="E113" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F113" s="0" t="n">
+      <c r="F113" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G113" s="0" t="n">
+      <c r="G113" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H113" s="0" t="n">
+      <c r="H113" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I113" s="0"/>
-      <c r="J113" s="0"/>
-      <c r="K113" s="0"/>
-      <c r="L113" s="0"/>
-      <c r="M113" s="0"/>
-      <c r="N113" s="0"/>
-      <c r="O113" s="0" t="s">
+      <c r="O113" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P113" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q113" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R113" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S113" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T113" s="0" t="n">
+      <c r="P113" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q113" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R113" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S113" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T113" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="n">
+      <c r="A114" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="0" t="n">
+      <c r="B114" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C114" s="0" t="s">
+      <c r="C114" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="E114" s="0" t="n">
+      <c r="E114" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F114" s="0" t="n">
+      <c r="F114" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="G114" s="0" t="n">
+      <c r="G114" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="H114" s="0" t="n">
+      <c r="H114" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I114" s="0"/>
-      <c r="J114" s="0"/>
-      <c r="K114" s="0"/>
-      <c r="L114" s="0" t="n">
+      <c r="L114" s="1" t="n">
         <v>0.0125</v>
       </c>
-      <c r="M114" s="0"/>
-      <c r="N114" s="0"/>
-      <c r="O114" s="0" t="s">
+      <c r="O114" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P114" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q114" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R114" s="0"/>
-      <c r="S114" s="0"/>
-      <c r="T114" s="0"/>
+      <c r="P114" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q114" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="n">
+      <c r="A115" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="0" t="n">
+      <c r="B115" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C115" s="0" t="s">
+      <c r="C115" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E115" s="0" t="n">
+      <c r="E115" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F115" s="0" t="n">
+      <c r="F115" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="G115" s="0" t="n">
+      <c r="G115" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="H115" s="0" t="n">
+      <c r="H115" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I115" s="0"/>
-      <c r="J115" s="0"/>
-      <c r="K115" s="0"/>
-      <c r="L115" s="0"/>
-      <c r="M115" s="0"/>
-      <c r="N115" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O115" s="0" t="s">
+      <c r="N115" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O115" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P115" s="0"/>
-      <c r="Q115" s="0"/>
-      <c r="R115" s="0"/>
-      <c r="S115" s="0"/>
-      <c r="T115" s="0"/>
     </row>
     <row r="116" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="n">
+      <c r="A116" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="0" t="n">
+      <c r="B116" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C116" s="0" t="s">
+      <c r="C116" s="1" t="s">
         <v>254</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E116" s="0" t="n">
+      <c r="E116" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F116" s="0" t="n">
+      <c r="F116" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G116" s="0" t="n">
+      <c r="G116" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H116" s="0" t="n">
+      <c r="H116" s="1" t="n">
         <v>0.12</v>
       </c>
-      <c r="I116" s="0"/>
-      <c r="J116" s="0"/>
-      <c r="K116" s="0"/>
-      <c r="L116" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M116" s="0"/>
-      <c r="N116" s="0"/>
-      <c r="O116" s="0" t="s">
+      <c r="L116" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O116" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="P116" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q116" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R116" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S116" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T116" s="0" t="n">
+      <c r="P116" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q116" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R116" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S116" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T116" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="n">
+      <c r="A117" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="0" t="n">
+      <c r="B117" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C117" s="0" t="s">
+      <c r="C117" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="E117" s="0" t="n">
+      <c r="E117" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F117" s="0" t="n">
+      <c r="F117" s="1" t="n">
         <v>75000</v>
       </c>
-      <c r="G117" s="0" t="n">
+      <c r="G117" s="1" t="n">
         <v>750</v>
       </c>
-      <c r="H117" s="0" t="n">
+      <c r="H117" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I117" s="0"/>
-      <c r="J117" s="0"/>
-      <c r="K117" s="0"/>
-      <c r="L117" s="0"/>
-      <c r="M117" s="0"/>
-      <c r="N117" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O117" s="0" t="s">
+      <c r="N117" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O117" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P117" s="0"/>
-      <c r="Q117" s="0"/>
-      <c r="R117" s="0"/>
-      <c r="S117" s="0"/>
-      <c r="T117" s="0"/>
     </row>
     <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="n">
+      <c r="A118" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="0" t="n">
+      <c r="B118" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C118" s="0" t="s">
+      <c r="C118" s="1" t="s">
         <v>258</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="E118" s="0" t="n">
+      <c r="E118" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F118" s="0"/>
-      <c r="G118" s="0"/>
-      <c r="H118" s="0"/>
-      <c r="I118" s="0"/>
-      <c r="J118" s="0"/>
-      <c r="K118" s="0" t="n">
+      <c r="K118" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="L118" s="0"/>
-      <c r="M118" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N118" s="0"/>
-      <c r="O118" s="0"/>
-      <c r="P118" s="0"/>
-      <c r="Q118" s="0"/>
-      <c r="R118" s="0"/>
-      <c r="S118" s="0"/>
-      <c r="T118" s="0"/>
+      <c r="M118" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="n">
+      <c r="A119" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="0" t="n">
+      <c r="B119" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C119" s="0" t="s">
+      <c r="C119" s="1" t="s">
         <v>260</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E119" s="0" t="n">
+      <c r="E119" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F119" s="0"/>
-      <c r="G119" s="0"/>
-      <c r="H119" s="0"/>
-      <c r="I119" s="0" t="n">
+      <c r="I119" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="J119" s="0" t="n">
+      <c r="J119" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="K119" s="0" t="n">
+      <c r="K119" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="L119" s="0"/>
-      <c r="M119" s="0" t="n">
+      <c r="M119" s="1" t="n">
         <v>0.0075</v>
       </c>
-      <c r="N119" s="0" t="n">
+      <c r="N119" s="1" t="n">
         <v>0.0075</v>
       </c>
-      <c r="O119" s="0"/>
-      <c r="P119" s="0"/>
-      <c r="Q119" s="0"/>
-      <c r="R119" s="0"/>
-      <c r="S119" s="0"/>
-      <c r="T119" s="0"/>
     </row>
     <row r="120" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="n">
+      <c r="A120" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="0" t="n">
+      <c r="B120" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C120" s="0" t="s">
+      <c r="C120" s="1" t="s">
         <v>262</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="E120" s="0" t="n">
+      <c r="E120" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F120" s="0"/>
-      <c r="G120" s="0"/>
-      <c r="H120" s="0"/>
-      <c r="I120" s="0"/>
-      <c r="J120" s="0" t="n">
+      <c r="J120" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="K120" s="0" t="n">
+      <c r="K120" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="L120" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M120" s="0" t="n">
+      <c r="L120" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M120" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="N120" s="0" t="n">
+      <c r="N120" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O120" s="0"/>
-      <c r="P120" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q120" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R120" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S120" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T120" s="0" t="n">
+      <c r="P120" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q120" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R120" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S120" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T120" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="n">
+      <c r="A121" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="0" t="n">
+      <c r="B121" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C121" s="0" t="s">
+      <c r="C121" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E121" s="0" t="n">
+      <c r="E121" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F121" s="0" t="n">
+      <c r="F121" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G121" s="0" t="n">
+      <c r="G121" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H121" s="0" t="n">
+      <c r="H121" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="I121" s="0"/>
-      <c r="J121" s="0"/>
-      <c r="K121" s="0"/>
-      <c r="L121" s="0"/>
-      <c r="M121" s="0"/>
-      <c r="N121" s="0" t="n">
+      <c r="N121" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="O121" s="0" t="s">
+      <c r="O121" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P121" s="0"/>
-      <c r="Q121" s="0"/>
-      <c r="R121" s="0"/>
-      <c r="S121" s="0"/>
-      <c r="T121" s="0"/>
     </row>
     <row r="122" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="n">
+      <c r="A122" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="0" t="n">
+      <c r="B122" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C122" s="0" t="s">
+      <c r="C122" s="1" t="s">
         <v>266</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E122" s="0" t="n">
+      <c r="E122" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F122" s="0" t="n">
+      <c r="F122" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G122" s="0" t="n">
+      <c r="G122" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H122" s="0" t="n">
+      <c r="H122" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="I122" s="0"/>
-      <c r="J122" s="0"/>
-      <c r="K122" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L122" s="0"/>
-      <c r="M122" s="0" t="n">
+      <c r="K122" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M122" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="N122" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O122" s="0" t="s">
+      <c r="N122" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O122" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P122" s="0"/>
-      <c r="Q122" s="0"/>
-      <c r="R122" s="0"/>
-      <c r="S122" s="0"/>
-      <c r="T122" s="0"/>
     </row>
     <row r="123" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="n">
+      <c r="A123" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="0" t="n">
+      <c r="B123" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C123" s="0" t="s">
+      <c r="C123" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E123" s="0" t="n">
+      <c r="E123" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F123" s="0" t="n">
+      <c r="F123" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="G123" s="0" t="n">
+      <c r="G123" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="H123" s="0" t="n">
+      <c r="H123" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I123" s="0"/>
-      <c r="J123" s="0"/>
-      <c r="K123" s="0" t="n">
+      <c r="K123" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="L123" s="0" t="n">
+      <c r="L123" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="M123" s="0"/>
-      <c r="N123" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O123" s="0" t="s">
+      <c r="N123" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O123" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P123" s="0"/>
-      <c r="Q123" s="0"/>
-      <c r="R123" s="0"/>
-      <c r="S123" s="0"/>
-      <c r="T123" s="0"/>
     </row>
     <row r="124" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="n">
+      <c r="A124" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="0" t="n">
+      <c r="B124" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C124" s="0" t="s">
+      <c r="C124" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="E124" s="0" t="n">
+      <c r="E124" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F124" s="0" t="n">
+      <c r="F124" s="1" t="n">
         <v>40000</v>
       </c>
-      <c r="G124" s="0" t="n">
+      <c r="G124" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="H124" s="0" t="n">
+      <c r="H124" s="1" t="n">
         <v>0.18</v>
       </c>
-      <c r="I124" s="0"/>
-      <c r="J124" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K124" s="0"/>
-      <c r="L124" s="0"/>
-      <c r="M124" s="0"/>
-      <c r="N124" s="0"/>
-      <c r="O124" s="0" t="s">
+      <c r="J124" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O124" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P124" s="0"/>
-      <c r="Q124" s="0"/>
-      <c r="R124" s="0"/>
-      <c r="S124" s="0"/>
-      <c r="T124" s="0"/>
     </row>
     <row r="125" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="n">
+      <c r="A125" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="0" t="n">
+      <c r="B125" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C125" s="0" t="s">
+      <c r="C125" s="1" t="s">
         <v>272</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="E125" s="0" t="n">
+      <c r="E125" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F125" s="0" t="n">
+      <c r="F125" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="G125" s="0" t="n">
+      <c r="G125" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="H125" s="0" t="n">
+      <c r="H125" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="I125" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J125" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K125" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L125" s="0"/>
-      <c r="M125" s="0"/>
-      <c r="N125" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O125" s="0" t="s">
+      <c r="I125" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J125" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K125" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N125" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O125" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P125" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q125" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R125" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S125" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T125" s="0" t="n">
+      <c r="P125" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q125" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R125" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S125" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T125" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="n">
+      <c r="A126" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="0" t="n">
+      <c r="B126" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C126" s="0" t="s">
+      <c r="C126" s="1" t="s">
         <v>274</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E126" s="0" t="n">
+      <c r="E126" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F126" s="0" t="n">
+      <c r="F126" s="1" t="n">
         <v>75000</v>
       </c>
-      <c r="G126" s="0" t="n">
+      <c r="G126" s="1" t="n">
         <v>750</v>
       </c>
-      <c r="H126" s="0" t="n">
+      <c r="H126" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="I126" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J126" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K126" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L126" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M126" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N126" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O126" s="0" t="s">
+      <c r="I126" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J126" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K126" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L126" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M126" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N126" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O126" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P126" s="0"/>
-      <c r="Q126" s="0"/>
-      <c r="R126" s="0"/>
-      <c r="S126" s="0"/>
-      <c r="T126" s="0"/>
     </row>
     <row r="127" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="n">
+      <c r="A127" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="0" t="n">
+      <c r="B127" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C127" s="0" t="s">
+      <c r="C127" s="1" t="s">
         <v>276</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E127" s="0" t="n">
+      <c r="E127" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F127" s="0"/>
-      <c r="G127" s="0"/>
-      <c r="H127" s="0"/>
-      <c r="I127" s="0" t="n">
+      <c r="I127" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="J127" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="K127" s="0"/>
-      <c r="L127" s="0"/>
-      <c r="M127" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N127" s="0" t="n">
+      <c r="J127" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M127" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N127" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O127" s="0"/>
-      <c r="P127" s="0"/>
-      <c r="Q127" s="0"/>
-      <c r="R127" s="0"/>
-      <c r="S127" s="0"/>
-      <c r="T127" s="0"/>
     </row>
     <row r="128" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="n">
+      <c r="A128" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="0" t="n">
+      <c r="B128" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C128" s="0" t="s">
+      <c r="C128" s="1" t="s">
         <v>278</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E128" s="0" t="n">
+      <c r="E128" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F128" s="0"/>
-      <c r="G128" s="0"/>
-      <c r="H128" s="0"/>
-      <c r="I128" s="0"/>
-      <c r="J128" s="0"/>
-      <c r="K128" s="0"/>
-      <c r="L128" s="0"/>
-      <c r="M128" s="0"/>
-      <c r="N128" s="0"/>
-      <c r="O128" s="0"/>
-      <c r="P128" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q128" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R128" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S128" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T128" s="0" t="n">
+      <c r="P128" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q128" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R128" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S128" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T128" s="1" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="n">
+      <c r="A129" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="0" t="n">
+      <c r="B129" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C129" s="0" t="s">
+      <c r="C129" s="1" t="s">
         <v>280</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E129" s="0" t="n">
+      <c r="E129" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F129" s="0" t="n">
+      <c r="F129" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="G129" s="0" t="n">
+      <c r="G129" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H129" s="0" t="n">
+      <c r="H129" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="I129" s="0" t="n">
+      <c r="I129" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="J129" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="K129" s="0"/>
-      <c r="L129" s="0"/>
-      <c r="M129" s="0" t="n">
+      <c r="J129" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M129" s="1" t="n">
         <v>0.0075</v>
       </c>
-      <c r="N129" s="0" t="n">
+      <c r="N129" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O129" s="0" t="s">
+      <c r="O129" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P129" s="0"/>
-      <c r="Q129" s="0"/>
-      <c r="R129" s="0"/>
-      <c r="S129" s="0"/>
-      <c r="T129" s="0"/>
     </row>
     <row r="130" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="n">
+      <c r="A130" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="0" t="n">
+      <c r="B130" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C130" s="0" t="s">
+      <c r="C130" s="1" t="s">
         <v>282</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E130" s="0" t="n">
+      <c r="E130" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F130" s="0" t="n">
+      <c r="F130" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="G130" s="0" t="n">
+      <c r="G130" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="H130" s="0" t="n">
+      <c r="H130" s="1" t="n">
         <v>0.08</v>
       </c>
-      <c r="I130" s="0"/>
-      <c r="J130" s="0"/>
-      <c r="K130" s="0"/>
-      <c r="L130" s="0" t="n">
+      <c r="L130" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="M130" s="0"/>
-      <c r="N130" s="0"/>
-      <c r="O130" s="0" t="s">
+      <c r="O130" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P130" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q130" s="0"/>
-      <c r="R130" s="0"/>
-      <c r="S130" s="0"/>
-      <c r="T130" s="0"/>
+      <c r="P130" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="n">
+      <c r="A131" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="0" t="n">
+      <c r="B131" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C131" s="0" t="s">
+      <c r="C131" s="1" t="s">
         <v>284</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E131" s="0" t="n">
+      <c r="E131" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F131" s="0" t="n">
+      <c r="F131" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G131" s="0" t="n">
+      <c r="G131" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H131" s="0" t="n">
+      <c r="H131" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="I131" s="0" t="n">
+      <c r="I131" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="J131" s="0"/>
-      <c r="K131" s="0"/>
-      <c r="L131" s="0" t="n">
+      <c r="L131" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="M131" s="0"/>
-      <c r="N131" s="0"/>
-      <c r="O131" s="0" t="s">
+      <c r="O131" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P131" s="0"/>
-      <c r="Q131" s="0"/>
-      <c r="R131" s="0"/>
-      <c r="S131" s="0"/>
-      <c r="T131" s="0"/>
     </row>
     <row r="132" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="n">
+      <c r="A132" s="1" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="0" t="n">
+      <c r="B132" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C132" s="0" t="s">
+      <c r="C132" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="E132" s="0" t="n">
+      <c r="E132" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F132" s="0" t="n">
+      <c r="F132" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="G132" s="0" t="n">
+      <c r="G132" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="H132" s="0" t="n">
+      <c r="H132" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="I132" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J132" s="0"/>
-      <c r="K132" s="0"/>
-      <c r="L132" s="0"/>
-      <c r="M132" s="0"/>
-      <c r="N132" s="0"/>
-      <c r="O132" s="0" t="s">
+      <c r="I132" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O132" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P132" s="0"/>
-      <c r="Q132" s="0"/>
-      <c r="R132" s="0"/>
-      <c r="S132" s="0"/>
-      <c r="T132" s="0"/>
     </row>
     <row r="133" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="n">
+      <c r="A133" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="0" t="n">
+      <c r="B133" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C133" s="0" t="s">
+      <c r="C133" s="1" t="s">
         <v>288</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E133" s="0" t="n">
+      <c r="E133" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F133" s="0" t="n">
+      <c r="F133" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="G133" s="0" t="n">
+      <c r="G133" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="H133" s="0" t="n">
+      <c r="H133" s="1" t="n">
         <v>0.18</v>
       </c>
-      <c r="I133" s="0"/>
-      <c r="J133" s="0"/>
-      <c r="K133" s="0"/>
-      <c r="L133" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M133" s="0"/>
-      <c r="N133" s="0"/>
-      <c r="O133" s="0" t="s">
+      <c r="L133" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O133" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="P133" s="0"/>
-      <c r="Q133" s="0"/>
-      <c r="R133" s="0"/>
-      <c r="S133" s="0"/>
-      <c r="T133" s="0"/>
     </row>
     <row r="134" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="n">
+      <c r="A134" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="0" t="n">
+      <c r="B134" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C134" s="0" t="s">
+      <c r="C134" s="1" t="s">
         <v>290</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E134" s="0" t="n">
+      <c r="E134" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F134" s="0" t="n">
+      <c r="F134" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="G134" s="0" t="n">
+      <c r="G134" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H134" s="0" t="n">
+      <c r="H134" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I134" s="0"/>
-      <c r="J134" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K134" s="0"/>
-      <c r="L134" s="0"/>
-      <c r="M134" s="0"/>
-      <c r="N134" s="0"/>
-      <c r="O134" s="0" t="s">
+      <c r="J134" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O134" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P134" s="0"/>
-      <c r="Q134" s="0"/>
-      <c r="R134" s="0"/>
-      <c r="S134" s="0"/>
-      <c r="T134" s="0"/>
     </row>
     <row r="135" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="n">
+      <c r="A135" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="0" t="n">
+      <c r="B135" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C135" s="0" t="s">
+      <c r="C135" s="1" t="s">
         <v>292</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="E135" s="0" t="n">
+      <c r="E135" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F135" s="0" t="n">
+      <c r="F135" s="1" t="n">
         <v>75000</v>
       </c>
-      <c r="G135" s="0" t="n">
+      <c r="G135" s="1" t="n">
         <v>750</v>
       </c>
-      <c r="H135" s="0" t="n">
+      <c r="H135" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I135" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J135" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K135" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L135" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M135" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N135" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O135" s="0" t="s">
+      <c r="I135" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J135" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K135" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L135" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M135" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N135" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O135" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P135" s="0"/>
-      <c r="Q135" s="0"/>
-      <c r="R135" s="0"/>
-      <c r="S135" s="0"/>
-      <c r="T135" s="0"/>
     </row>
     <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="n">
+      <c r="A136" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="0" t="n">
+      <c r="B136" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C136" s="0" t="s">
+      <c r="C136" s="1" t="s">
         <v>294</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E136" s="0" t="n">
+      <c r="E136" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F136" s="0"/>
-      <c r="G136" s="0"/>
-      <c r="H136" s="0"/>
-      <c r="I136" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J136" s="0"/>
-      <c r="K136" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L136" s="0"/>
-      <c r="M136" s="0"/>
-      <c r="N136" s="0"/>
-      <c r="O136" s="0"/>
-      <c r="P136" s="0"/>
-      <c r="Q136" s="0"/>
-      <c r="R136" s="0"/>
-      <c r="S136" s="0"/>
-      <c r="T136" s="0"/>
+      <c r="I136" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K136" s="1" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="0" t="n">
+      <c r="A137" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="0" t="n">
+      <c r="B137" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C137" s="0" t="s">
+      <c r="C137" s="1" t="s">
         <v>296</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E137" s="0" t="n">
+      <c r="E137" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F137" s="0"/>
-      <c r="G137" s="0"/>
-      <c r="H137" s="0"/>
-      <c r="I137" s="0"/>
-      <c r="J137" s="0"/>
-      <c r="K137" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L137" s="0"/>
-      <c r="M137" s="0"/>
-      <c r="N137" s="0"/>
-      <c r="O137" s="0"/>
-      <c r="P137" s="0"/>
-      <c r="Q137" s="0"/>
-      <c r="R137" s="0"/>
-      <c r="S137" s="0"/>
-      <c r="T137" s="0"/>
+      <c r="K137" s="1" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="0" t="n">
+      <c r="A138" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="0" t="n">
+      <c r="B138" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C138" s="0" t="s">
+      <c r="C138" s="1" t="s">
         <v>298</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="E138" s="0" t="n">
+      <c r="E138" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F138" s="0"/>
-      <c r="G138" s="0"/>
-      <c r="H138" s="0"/>
-      <c r="I138" s="0" t="n">
+      <c r="I138" s="1" t="n">
         <v>0.0075</v>
       </c>
-      <c r="J138" s="0" t="n">
+      <c r="J138" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="K138" s="0" t="n">
+      <c r="K138" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="L138" s="0"/>
-      <c r="M138" s="0"/>
-      <c r="N138" s="0"/>
-      <c r="O138" s="0"/>
-      <c r="P138" s="0"/>
-      <c r="Q138" s="0"/>
-      <c r="R138" s="0"/>
-      <c r="S138" s="0"/>
-      <c r="T138" s="0"/>
     </row>
     <row r="139" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="0" t="n">
+      <c r="A139" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="0" t="n">
+      <c r="B139" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C139" s="0" t="s">
+      <c r="C139" s="1" t="s">
         <v>300</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E139" s="0" t="n">
+      <c r="E139" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F139" s="0"/>
-      <c r="G139" s="0"/>
-      <c r="H139" s="0"/>
-      <c r="I139" s="0"/>
-      <c r="J139" s="0"/>
-      <c r="K139" s="0" t="n">
+      <c r="K139" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="L139" s="0"/>
-      <c r="M139" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N139" s="0" t="n">
+      <c r="M139" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N139" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O139" s="0"/>
-      <c r="P139" s="0"/>
-      <c r="Q139" s="0"/>
-      <c r="R139" s="0"/>
-      <c r="S139" s="0"/>
-      <c r="T139" s="0"/>
     </row>
     <row r="140" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="0" t="n">
+      <c r="A140" s="1" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="0" t="n">
+      <c r="B140" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C140" s="0" t="s">
+      <c r="C140" s="1" t="s">
         <v>302</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="E140" s="0" t="n">
+      <c r="E140" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F140" s="0"/>
-      <c r="G140" s="0"/>
-      <c r="H140" s="0"/>
-      <c r="I140" s="0"/>
-      <c r="J140" s="0"/>
-      <c r="K140" s="0"/>
-      <c r="L140" s="0"/>
-      <c r="M140" s="0"/>
-      <c r="N140" s="0" t="n">
+      <c r="N140" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="O140" s="0"/>
-      <c r="P140" s="0"/>
-      <c r="Q140" s="0"/>
-      <c r="R140" s="0"/>
-      <c r="S140" s="0"/>
-      <c r="T140" s="0"/>
     </row>
     <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="0" t="n">
+      <c r="A141" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="0" t="n">
+      <c r="B141" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C141" s="0" t="s">
+      <c r="C141" s="1" t="s">
         <v>304</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="E141" s="0" t="n">
+      <c r="E141" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F141" s="0"/>
-      <c r="G141" s="0"/>
-      <c r="H141" s="0"/>
-      <c r="I141" s="0"/>
-      <c r="J141" s="0"/>
-      <c r="K141" s="0" t="n">
+      <c r="K141" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="L141" s="0" t="n">
+      <c r="L141" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="M141" s="0"/>
-      <c r="N141" s="0"/>
-      <c r="O141" s="0"/>
-      <c r="P141" s="0"/>
-      <c r="Q141" s="0"/>
-      <c r="R141" s="0"/>
-      <c r="S141" s="0"/>
-      <c r="T141" s="0"/>
     </row>
     <row r="142" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="0" t="n">
+      <c r="A142" s="1" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="0" t="n">
+      <c r="B142" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C142" s="0" t="s">
+      <c r="C142" s="1" t="s">
         <v>306</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="E142" s="0" t="n">
+      <c r="E142" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F142" s="0" t="n">
+      <c r="F142" s="1" t="n">
         <v>2500</v>
       </c>
-      <c r="G142" s="0" t="n">
+      <c r="G142" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="H142" s="0" t="n">
+      <c r="H142" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="I142" s="0"/>
-      <c r="J142" s="0"/>
-      <c r="K142" s="0"/>
-      <c r="L142" s="0"/>
-      <c r="M142" s="0"/>
-      <c r="N142" s="0"/>
-      <c r="O142" s="0" t="s">
+      <c r="O142" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P142" s="0"/>
-      <c r="Q142" s="0"/>
-      <c r="R142" s="0"/>
-      <c r="S142" s="0"/>
-      <c r="T142" s="0"/>
     </row>
     <row r="143" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="0" t="n">
+      <c r="A143" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="0" t="n">
+      <c r="B143" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C143" s="0" t="s">
+      <c r="C143" s="1" t="s">
         <v>308</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E143" s="0" t="n">
+      <c r="E143" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="F143" s="0" t="n">
+      <c r="F143" s="1" t="n">
         <v>8000</v>
       </c>
-      <c r="G143" s="0" t="n">
+      <c r="G143" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="H143" s="0" t="n">
+      <c r="H143" s="1" t="n">
         <v>0.06</v>
       </c>
-      <c r="I143" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J143" s="0"/>
-      <c r="K143" s="0"/>
-      <c r="L143" s="0"/>
-      <c r="M143" s="0"/>
-      <c r="N143" s="0"/>
-      <c r="O143" s="0" t="s">
+      <c r="I143" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O143" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P143" s="0"/>
-      <c r="Q143" s="0"/>
-      <c r="R143" s="0"/>
-      <c r="S143" s="0"/>
-      <c r="T143" s="0"/>
     </row>
     <row r="144" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="0" t="n">
+      <c r="A144" s="1" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="0" t="n">
+      <c r="B144" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C144" s="0" t="s">
+      <c r="C144" s="1" t="s">
         <v>310</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="E144" s="0" t="n">
+      <c r="E144" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F144" s="0" t="n">
+      <c r="F144" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="G144" s="0" t="n">
+      <c r="G144" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="H144" s="0" t="n">
+      <c r="H144" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I144" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J144" s="0"/>
-      <c r="K144" s="0"/>
-      <c r="L144" s="0"/>
-      <c r="M144" s="0"/>
-      <c r="N144" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O144" s="0" t="s">
+      <c r="I144" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N144" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O144" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="P144" s="0"/>
-      <c r="Q144" s="0"/>
-      <c r="R144" s="0"/>
-      <c r="S144" s="0"/>
-      <c r="T144" s="0"/>
+    </row>
+    <row r="145" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B145" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+      <c r="H145" s="5"/>
+      <c r="I145" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J145" s="5"/>
+      <c r="K145" s="5"/>
+      <c r="L145" s="5"/>
+      <c r="M145" s="5"/>
+      <c r="N145" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O145" s="3"/>
+      <c r="P145" s="5"/>
+      <c r="Q145" s="5"/>
+      <c r="R145" s="5"/>
+      <c r="S145" s="5"/>
+      <c r="T145" s="5"/>
+    </row>
+    <row r="146" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="H146" s="5"/>
+      <c r="I146" s="5"/>
+      <c r="J146" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K146" s="5"/>
+      <c r="L146" s="5"/>
+      <c r="M146" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N146" s="5"/>
+      <c r="O146" s="3"/>
+      <c r="P146" s="5"/>
+      <c r="Q146" s="5"/>
+      <c r="R146" s="5"/>
+      <c r="S146" s="5"/>
+      <c r="T146" s="5"/>
+    </row>
+    <row r="147" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="J147" s="5"/>
+      <c r="K147" s="5"/>
+      <c r="L147" s="5"/>
+      <c r="M147" s="5"/>
+      <c r="N147" s="5"/>
+      <c r="O147" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P147" s="5"/>
+      <c r="Q147" s="5"/>
+      <c r="R147" s="5"/>
+      <c r="S147" s="5"/>
+      <c r="T147" s="5"/>
+    </row>
+    <row r="148" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5"/>
+      <c r="K148" s="5"/>
+      <c r="L148" s="5"/>
+      <c r="M148" s="5"/>
+      <c r="N148" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O148" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P148" s="5"/>
+      <c r="Q148" s="5"/>
+      <c r="R148" s="5"/>
+      <c r="S148" s="5"/>
+      <c r="T148" s="5"/>
+    </row>
+    <row r="149" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B149" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
+      <c r="H149" s="5"/>
+      <c r="I149" s="5"/>
+      <c r="J149" s="5"/>
+      <c r="K149" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L149" s="5"/>
+      <c r="M149" s="5" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="N149" s="5"/>
+      <c r="O149" s="3"/>
+      <c r="P149" s="5"/>
+      <c r="Q149" s="5"/>
+      <c r="R149" s="5"/>
+      <c r="S149" s="5"/>
+      <c r="T149" s="5"/>
+    </row>
+    <row r="150" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B150" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="5"/>
+      <c r="J150" s="5"/>
+      <c r="K150" s="5"/>
+      <c r="L150" s="5"/>
+      <c r="M150" s="5"/>
+      <c r="N150" s="5"/>
+      <c r="O150" s="3"/>
+      <c r="P150" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q150" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R150" s="5"/>
+      <c r="S150" s="5"/>
+      <c r="T150" s="5" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B151" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J151" s="5"/>
+      <c r="K151" s="5"/>
+      <c r="L151" s="5"/>
+      <c r="M151" s="5"/>
+      <c r="N151" s="5"/>
+      <c r="O151" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P151" s="5"/>
+      <c r="Q151" s="5"/>
+      <c r="R151" s="5"/>
+      <c r="S151" s="5"/>
+      <c r="T151" s="5"/>
+    </row>
+    <row r="152" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B152" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+      <c r="H152" s="5"/>
+      <c r="I152" s="5"/>
+      <c r="J152" s="5"/>
+      <c r="K152" s="5"/>
+      <c r="L152" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M152" s="5"/>
+      <c r="N152" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="O152" s="3"/>
+      <c r="P152" s="5"/>
+      <c r="Q152" s="5"/>
+      <c r="R152" s="5"/>
+      <c r="S152" s="5"/>
+      <c r="T152" s="5"/>
+    </row>
+    <row r="153" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B153" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+      <c r="H153" s="5"/>
+      <c r="I153" s="5"/>
+      <c r="J153" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K153" s="5"/>
+      <c r="L153" s="5"/>
+      <c r="M153" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N153" s="5"/>
+      <c r="O153" s="3"/>
+      <c r="P153" s="5"/>
+      <c r="Q153" s="5"/>
+      <c r="R153" s="5"/>
+      <c r="S153" s="5"/>
+      <c r="T153" s="5" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B154" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
+      <c r="H154" s="5"/>
+      <c r="I154" s="5"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="5"/>
+      <c r="L154" s="5"/>
+      <c r="M154" s="5"/>
+      <c r="N154" s="5"/>
+      <c r="O154" s="3"/>
+      <c r="P154" s="5"/>
+      <c r="Q154" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R154" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S154" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T154" s="5"/>
+    </row>
+    <row r="155" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B155" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="J155" s="5"/>
+      <c r="K155" s="5"/>
+      <c r="L155" s="5"/>
+      <c r="M155" s="5"/>
+      <c r="N155" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="O155" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P155" s="5"/>
+      <c r="Q155" s="5"/>
+      <c r="R155" s="5"/>
+      <c r="S155" s="5"/>
+      <c r="T155" s="5"/>
+    </row>
+    <row r="156" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B156" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>75000</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J156" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K156" s="5"/>
+      <c r="L156" s="5"/>
+      <c r="M156" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N156" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O156" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P156" s="5"/>
+      <c r="Q156" s="5"/>
+      <c r="R156" s="5"/>
+      <c r="S156" s="5"/>
+      <c r="T156" s="5"/>
+    </row>
+    <row r="157" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B157" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="E157" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" s="8"/>
+      <c r="G157" s="8"/>
+      <c r="H157" s="9"/>
+      <c r="I157" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J157" s="9"/>
+      <c r="K157" s="9"/>
+      <c r="L157" s="9"/>
+      <c r="M157" s="9"/>
+      <c r="N157" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O157" s="6"/>
+      <c r="P157" s="9"/>
+      <c r="Q157" s="9"/>
+      <c r="R157" s="9"/>
+      <c r="S157" s="9"/>
+      <c r="T157" s="9"/>
+    </row>
+    <row r="158" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B158" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E158" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F158" s="8"/>
+      <c r="G158" s="8"/>
+      <c r="H158" s="9"/>
+      <c r="I158" s="9"/>
+      <c r="J158" s="9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K158" s="9"/>
+      <c r="L158" s="9"/>
+      <c r="M158" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N158" s="9"/>
+      <c r="O158" s="6"/>
+      <c r="P158" s="9"/>
+      <c r="Q158" s="9"/>
+      <c r="R158" s="9"/>
+      <c r="S158" s="9"/>
+      <c r="T158" s="9"/>
+    </row>
+    <row r="159" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B159" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="E159" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F159" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G159" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H159" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I159" s="9" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="J159" s="9"/>
+      <c r="K159" s="9"/>
+      <c r="L159" s="9"/>
+      <c r="M159" s="9"/>
+      <c r="N159" s="9"/>
+      <c r="O159" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P159" s="9"/>
+      <c r="Q159" s="9"/>
+      <c r="R159" s="9"/>
+      <c r="S159" s="9"/>
+      <c r="T159" s="9"/>
+    </row>
+    <row r="160" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B160" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="E160" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F160" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G160" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H160" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I160" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J160" s="9"/>
+      <c r="K160" s="9"/>
+      <c r="L160" s="9"/>
+      <c r="M160" s="9"/>
+      <c r="N160" s="9"/>
+      <c r="O160" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P160" s="9"/>
+      <c r="Q160" s="9"/>
+      <c r="R160" s="9"/>
+      <c r="S160" s="9"/>
+      <c r="T160" s="9"/>
+    </row>
+    <row r="161" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B161" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E161" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F161" s="8"/>
+      <c r="G161" s="8"/>
+      <c r="H161" s="9"/>
+      <c r="I161" s="9"/>
+      <c r="J161" s="9"/>
+      <c r="K161" s="9"/>
+      <c r="L161" s="9"/>
+      <c r="M161" s="9"/>
+      <c r="N161" s="9"/>
+      <c r="O161" s="6"/>
+      <c r="P161" s="9"/>
+      <c r="Q161" s="9"/>
+      <c r="R161" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S161" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T161" s="9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B162" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="E162" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F162" s="8"/>
+      <c r="G162" s="8"/>
+      <c r="H162" s="9"/>
+      <c r="I162" s="9"/>
+      <c r="J162" s="9"/>
+      <c r="K162" s="9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L162" s="9"/>
+      <c r="M162" s="9" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="N162" s="9"/>
+      <c r="O162" s="6"/>
+      <c r="P162" s="9"/>
+      <c r="Q162" s="9"/>
+      <c r="R162" s="9"/>
+      <c r="S162" s="9"/>
+      <c r="T162" s="9"/>
+    </row>
+    <row r="163" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B163" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="E163" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F163" s="8"/>
+      <c r="G163" s="8"/>
+      <c r="H163" s="9"/>
+      <c r="I163" s="9" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J163" s="9"/>
+      <c r="K163" s="9"/>
+      <c r="L163" s="9"/>
+      <c r="M163" s="9"/>
+      <c r="N163" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O163" s="6"/>
+      <c r="P163" s="9"/>
+      <c r="Q163" s="9"/>
+      <c r="R163" s="9"/>
+      <c r="S163" s="9"/>
+      <c r="T163" s="9"/>
+    </row>
+    <row r="164" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B164" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="E164" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="F164" s="8"/>
+      <c r="G164" s="8"/>
+      <c r="H164" s="9"/>
+      <c r="I164" s="9"/>
+      <c r="J164" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K164" s="9"/>
+      <c r="L164" s="9"/>
+      <c r="M164" s="9"/>
+      <c r="N164" s="9"/>
+      <c r="O164" s="6"/>
+      <c r="P164" s="9"/>
+      <c r="Q164" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R164" s="9"/>
+      <c r="S164" s="9"/>
+      <c r="T164" s="9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B165" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="E165" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="F165" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G165" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H165" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I165" s="9" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J165" s="9"/>
+      <c r="K165" s="9"/>
+      <c r="L165" s="9"/>
+      <c r="M165" s="9"/>
+      <c r="N165" s="9"/>
+      <c r="O165" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P165" s="9"/>
+      <c r="Q165" s="9"/>
+      <c r="R165" s="9"/>
+      <c r="S165" s="9"/>
+      <c r="T165" s="9"/>
+    </row>
+    <row r="166" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B166" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E166" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="F166" s="8"/>
+      <c r="G166" s="8"/>
+      <c r="H166" s="9"/>
+      <c r="I166" s="9"/>
+      <c r="J166" s="9"/>
+      <c r="K166" s="9"/>
+      <c r="L166" s="9"/>
+      <c r="M166" s="9"/>
+      <c r="N166" s="9"/>
+      <c r="O166" s="6"/>
+      <c r="P166" s="9" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="Q166" s="9"/>
+      <c r="R166" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S166" s="9" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="T166" s="9"/>
+    </row>
+    <row r="167" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B167" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="E167" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="F167" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G167" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="H167" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I167" s="9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="J167" s="9"/>
+      <c r="K167" s="9"/>
+      <c r="L167" s="9"/>
+      <c r="M167" s="9"/>
+      <c r="N167" s="9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="O167" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P167" s="9"/>
+      <c r="Q167" s="9"/>
+      <c r="R167" s="9"/>
+      <c r="S167" s="9"/>
+      <c r="T167" s="9"/>
+    </row>
+    <row r="168" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B168" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="E168" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F168" s="8" t="n">
+        <v>75000</v>
+      </c>
+      <c r="G168" s="8" t="n">
+        <v>750</v>
+      </c>
+      <c r="H168" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I168" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K168" s="9"/>
+      <c r="L168" s="9"/>
+      <c r="M168" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N168" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O168" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P168" s="9"/>
+      <c r="Q168" s="9"/>
+      <c r="R168" s="9"/>
+      <c r="S168" s="9"/>
+      <c r="T168" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
